--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -1269,120 +1269,120 @@
     <t>R$ 14.015,81</t>
   </si>
   <si>
+    <t>92001/1</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  346,86</t>
+  </si>
+  <si>
+    <t>92001LUCIANALS</t>
+  </si>
+  <si>
+    <t>87601/1</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  620,43</t>
+  </si>
+  <si>
+    <t>87601CleitonS</t>
+  </si>
+  <si>
+    <t>87301/1</t>
+  </si>
+  <si>
+    <t>R$  469,36</t>
+  </si>
+  <si>
+    <t>87301PatriciaSS</t>
+  </si>
+  <si>
+    <t>R$  746,58</t>
+  </si>
+  <si>
+    <t>R$  455,29</t>
+  </si>
+  <si>
+    <t>R$  1.059,03</t>
+  </si>
+  <si>
+    <t>97601/1</t>
+  </si>
+  <si>
+    <t>R$  146,38</t>
+  </si>
+  <si>
+    <t>97601FELIPEVS</t>
+  </si>
+  <si>
+    <t>83201/1</t>
+  </si>
+  <si>
+    <t>R$  4.535,18</t>
+  </si>
+  <si>
+    <t>83201ElaineMH</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  114,28</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  505,46</t>
+  </si>
+  <si>
+    <t>88001/1</t>
+  </si>
+  <si>
+    <t>R$  237,08</t>
+  </si>
+  <si>
+    <t>88001brunoV</t>
+  </si>
+  <si>
+    <t>R$  579,19</t>
+  </si>
+  <si>
+    <t>101701/2</t>
+  </si>
+  <si>
+    <t>56901/1</t>
+  </si>
+  <si>
+    <t>R$  170,33</t>
+  </si>
+  <si>
+    <t>56901BIANCARMS</t>
+  </si>
+  <si>
+    <t>R$  285,72</t>
+  </si>
+  <si>
     <t>R$  714,32</t>
   </si>
   <si>
-    <t>R$  746,58</t>
-  </si>
-  <si>
-    <t>R$  455,29</t>
-  </si>
-  <si>
-    <t>88001/1</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  237,08</t>
-  </si>
-  <si>
-    <t>88001brunoV</t>
-  </si>
-  <si>
-    <t>R$  114,28</t>
-  </si>
-  <si>
-    <t>87601/1</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  620,43</t>
-  </si>
-  <si>
-    <t>87601CleitonS</t>
-  </si>
-  <si>
-    <t>87301/1</t>
-  </si>
-  <si>
-    <t>R$  469,36</t>
-  </si>
-  <si>
-    <t>87301PatriciaSS</t>
-  </si>
-  <si>
-    <t>92001/1</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>R$  346,86</t>
-  </si>
-  <si>
-    <t>92001LUCIANALS</t>
-  </si>
-  <si>
-    <t>56901/1</t>
-  </si>
-  <si>
-    <t>R$  170,33</t>
-  </si>
-  <si>
-    <t>56901BIANCARMS</t>
-  </si>
-  <si>
-    <t>83201/1</t>
-  </si>
-  <si>
-    <t>R$  4.535,18</t>
-  </si>
-  <si>
-    <t>83201ElaineMH</t>
-  </si>
-  <si>
-    <t>101701/2</t>
-  </si>
-  <si>
-    <t>97601/1</t>
-  </si>
-  <si>
-    <t>R$  146,38</t>
-  </si>
-  <si>
-    <t>97601FELIPEVS</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>R$  579,19</t>
-  </si>
-  <si>
-    <t>R$  285,72</t>
+    <t>99401/2</t>
   </si>
   <si>
     <t>R$  173,64</t>
   </si>
   <si>
-    <t>R$  505,46</t>
+    <t>98701/2</t>
   </si>
   <si>
     <t>56102/2</t>
   </si>
   <si>
-    <t>98701/2</t>
-  </si>
-  <si>
-    <t>99401/2</t>
-  </si>
-  <si>
-    <t>R$  1.059,03</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1620,9 +1620,30 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Fixo set26/1</t>
+  </si>
+  <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  3.276,49</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.720,72</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>Danielle Martins da Silva</t>
   </si>
   <si>
@@ -1632,6 +1653,24 @@
     <t>Danielle - Pagamento 2026</t>
   </si>
   <si>
+    <t>Carina Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  6.500,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
     <t>R$  2.536,00</t>
   </si>
   <si>
@@ -1641,6 +1680,24 @@
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.479,65</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Estorno emp set26/1</t>
+  </si>
+  <si>
+    <t>R$  282,79</t>
+  </si>
+  <si>
+    <t>Estorno desconto emprestimo</t>
+  </si>
+  <si>
     <t>R$  1.500,00</t>
   </si>
   <si>
@@ -1650,73 +1707,16 @@
     <t>Fernanda Dochvat - Fixo 2026</t>
   </si>
   <si>
-    <t>Estorno emp set26/1</t>
-  </si>
-  <si>
-    <t>R$  282,79</t>
-  </si>
-  <si>
-    <t>Estorno desconto emprestimo</t>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/09/26</t>
   </si>
   <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
   </si>
   <si>
     <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Fixo set26/1</t>
-  </si>
-  <si>
-    <t>R$  1.720,72</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  3.276,49</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Carina Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  6.500,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.479,65</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/09/26</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -13290,25 +13290,25 @@
         <v>33</v>
       </c>
       <c r="E204" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="F204" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
       </c>
       <c r="H204" t="s">
-        <v>182</v>
+        <v>419</v>
       </c>
       <c r="I204" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J204" t="s">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="K204" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="L204" t="s">
         <v>34</v>
@@ -13320,13 +13320,13 @@
         <v>45</v>
       </c>
       <c r="O204" t="s">
-        <v>34</v>
+        <v>421</v>
       </c>
       <c r="P204" t="s">
-        <v>34</v>
+        <v>420</v>
       </c>
       <c r="Q204" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R204" t="s">
         <v>34</v>
@@ -13346,25 +13346,25 @@
         <v>34</v>
       </c>
       <c r="E205" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="F205" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
       </c>
       <c r="H205" t="s">
-        <v>182</v>
+        <v>423</v>
       </c>
       <c r="I205" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J205" t="s">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="K205" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="L205" t="s">
         <v>34</v>
@@ -13376,13 +13376,13 @@
         <v>45</v>
       </c>
       <c r="O205" t="s">
-        <v>34</v>
+        <v>425</v>
       </c>
       <c r="P205" t="s">
-        <v>34</v>
+        <v>424</v>
       </c>
       <c r="Q205" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R205" t="s">
         <v>34</v>
@@ -13402,25 +13402,25 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>298</v>
+        <v>426</v>
       </c>
       <c r="F206" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
       </c>
       <c r="H206" t="s">
-        <v>182</v>
+        <v>423</v>
       </c>
       <c r="I206" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="J206" t="s">
-        <v>91</v>
+        <v>252</v>
       </c>
       <c r="K206" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13432,13 +13432,13 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>34</v>
+        <v>428</v>
       </c>
       <c r="P206" t="s">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="Q206" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R206" t="s">
         <v>34</v>
@@ -13458,7 +13458,7 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="F207" t="s">
         <v>345</v>
@@ -13470,13 +13470,13 @@
         <v>182</v>
       </c>
       <c r="I207" t="s">
-        <v>358</v>
+        <v>429</v>
       </c>
       <c r="J207" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="K207" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13514,25 +13514,25 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>421</v>
+        <v>298</v>
       </c>
       <c r="F208" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
       </c>
       <c r="H208" t="s">
-        <v>422</v>
+        <v>182</v>
       </c>
       <c r="I208" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="J208" t="s">
-        <v>252</v>
+        <v>91</v>
       </c>
       <c r="K208" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13544,13 +13544,13 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>424</v>
+        <v>34</v>
       </c>
       <c r="P208" t="s">
-        <v>423</v>
+        <v>34</v>
       </c>
       <c r="Q208" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R208" t="s">
         <v>34</v>
@@ -13570,7 +13570,7 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="F209" t="s">
         <v>345</v>
@@ -13582,13 +13582,13 @@
         <v>182</v>
       </c>
       <c r="I209" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J209" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="K209" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13626,7 +13626,7 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="F210" t="s">
         <v>345</v>
@@ -13635,16 +13635,16 @@
         <v>41</v>
       </c>
       <c r="H210" t="s">
-        <v>422</v>
+        <v>182</v>
       </c>
       <c r="I210" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="J210" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K210" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13682,7 +13682,7 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F211" t="s">
         <v>194</v>
@@ -13691,10 +13691,10 @@
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="I211" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J211" t="s">
         <v>252</v>
@@ -13712,10 +13712,10 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="P211" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q211" t="s">
         <v>45</v>
@@ -13738,7 +13738,7 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F212" t="s">
         <v>194</v>
@@ -13747,10 +13747,10 @@
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I212" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J212" t="s">
         <v>252</v>
@@ -13768,10 +13768,10 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="P212" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Q212" t="s">
         <v>45</v>
@@ -13794,25 +13794,25 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>433</v>
+        <v>317</v>
       </c>
       <c r="F213" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>434</v>
+        <v>182</v>
       </c>
       <c r="I213" t="s">
-        <v>435</v>
+        <v>356</v>
       </c>
       <c r="J213" t="s">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="K213" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="L213" t="s">
         <v>34</v>
@@ -13824,13 +13824,13 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>436</v>
+        <v>34</v>
       </c>
       <c r="P213" t="s">
-        <v>435</v>
+        <v>34</v>
       </c>
       <c r="Q213" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R213" t="s">
         <v>34</v>
@@ -13850,25 +13850,25 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>437</v>
+        <v>333</v>
       </c>
       <c r="F214" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
       </c>
       <c r="H214" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I214" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J214" t="s">
-        <v>252</v>
+        <v>90</v>
       </c>
       <c r="K214" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="L214" t="s">
         <v>34</v>
@@ -13880,13 +13880,13 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>439</v>
+        <v>34</v>
       </c>
       <c r="P214" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="Q214" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R214" t="s">
         <v>34</v>
@@ -13906,7 +13906,7 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>440</v>
+        <v>193</v>
       </c>
       <c r="F215" t="s">
         <v>194</v>
@@ -13915,10 +13915,10 @@
         <v>41</v>
       </c>
       <c r="H215" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="I215" t="s">
-        <v>441</v>
+        <v>359</v>
       </c>
       <c r="J215" t="s">
         <v>252</v>
@@ -13936,10 +13936,10 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>442</v>
+        <v>64</v>
       </c>
       <c r="P215" t="s">
-        <v>441</v>
+        <v>359</v>
       </c>
       <c r="Q215" t="s">
         <v>45</v>
@@ -13962,7 +13962,7 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>443</v>
+        <v>290</v>
       </c>
       <c r="F216" t="s">
         <v>345</v>
@@ -13971,16 +13971,16 @@
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>182</v>
+        <v>423</v>
       </c>
       <c r="I216" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="J216" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="K216" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="L216" t="s">
         <v>34</v>
@@ -14018,7 +14018,7 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F217" t="s">
         <v>194</v>
@@ -14027,10 +14027,10 @@
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="I217" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J217" t="s">
         <v>252</v>
@@ -14048,10 +14048,10 @@
         <v>45</v>
       </c>
       <c r="O217" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P217" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="Q217" t="s">
         <v>45</v>
@@ -14074,25 +14074,25 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>193</v>
+        <v>294</v>
       </c>
       <c r="F218" t="s">
-        <v>194</v>
+        <v>345</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
       </c>
       <c r="H218" t="s">
-        <v>447</v>
+        <v>182</v>
       </c>
       <c r="I218" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="J218" t="s">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="K218" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="L218" t="s">
         <v>34</v>
@@ -14104,13 +14104,13 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P218" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="Q218" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R218" t="s">
         <v>34</v>
@@ -14130,7 +14130,7 @@
         <v>34</v>
       </c>
       <c r="E219" t="s">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="F219" t="s">
         <v>345</v>
@@ -14142,13 +14142,13 @@
         <v>182</v>
       </c>
       <c r="I219" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="J219" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K219" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L219" t="s">
         <v>34</v>
@@ -14186,7 +14186,7 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>226</v>
+        <v>446</v>
       </c>
       <c r="F220" t="s">
         <v>345</v>
@@ -14198,13 +14198,13 @@
         <v>182</v>
       </c>
       <c r="I220" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="J220" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K220" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L220" t="s">
         <v>34</v>
@@ -14242,25 +14242,25 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>286</v>
+        <v>447</v>
       </c>
       <c r="F221" t="s">
-        <v>345</v>
+        <v>194</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
       </c>
       <c r="H221" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="I221" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="J221" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="K221" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14272,13 +14272,13 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>34</v>
+        <v>449</v>
       </c>
       <c r="P221" t="s">
-        <v>34</v>
+        <v>448</v>
       </c>
       <c r="Q221" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R221" t="s">
         <v>34</v>
@@ -14298,7 +14298,7 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F222" t="s">
         <v>345</v>
@@ -14307,16 +14307,16 @@
         <v>41</v>
       </c>
       <c r="H222" t="s">
-        <v>182</v>
+        <v>440</v>
       </c>
       <c r="I222" t="s">
-        <v>449</v>
+        <v>359</v>
       </c>
       <c r="J222" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="K222" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L222" t="s">
         <v>34</v>
@@ -14354,7 +14354,7 @@
         <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F223" t="s">
         <v>345</v>
@@ -14363,16 +14363,16 @@
         <v>41</v>
       </c>
       <c r="H223" t="s">
-        <v>422</v>
+        <v>182</v>
       </c>
       <c r="I223" t="s">
         <v>450</v>
       </c>
       <c r="J223" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="K223" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="L223" t="s">
         <v>34</v>
@@ -14410,7 +14410,7 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
       <c r="F224" t="s">
         <v>345</v>
@@ -14419,16 +14419,16 @@
         <v>41</v>
       </c>
       <c r="H224" t="s">
-        <v>427</v>
+        <v>182</v>
       </c>
       <c r="I224" t="s">
         <v>451</v>
       </c>
       <c r="J224" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="K224" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14478,7 +14478,7 @@
         <v>182</v>
       </c>
       <c r="I225" t="s">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="J225" t="s">
         <v>44</v>
@@ -14522,7 +14522,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>453</v>
+        <v>275</v>
       </c>
       <c r="F226" t="s">
         <v>345</v>
@@ -14531,16 +14531,16 @@
         <v>41</v>
       </c>
       <c r="H226" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="I226" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="J226" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="K226" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14590,7 +14590,7 @@
         <v>182</v>
       </c>
       <c r="I227" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J227" t="s">
         <v>44</v>
@@ -14634,7 +14634,7 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>306</v>
+        <v>455</v>
       </c>
       <c r="F228" t="s">
         <v>345</v>
@@ -14646,13 +14646,13 @@
         <v>182</v>
       </c>
       <c r="I228" t="s">
-        <v>455</v>
+        <v>365</v>
       </c>
       <c r="J228" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="K228" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -17658,28 +17658,28 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="F282" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G282" t="s">
         <v>41</v>
       </c>
       <c r="H282" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I282" t="s">
         <v>166</v>
       </c>
       <c r="J282" t="s">
-        <v>514</v>
+        <v>44</v>
       </c>
       <c r="K282" t="s">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="L282" t="s">
-        <v>535</v>
+        <v>34</v>
       </c>
       <c r="M282" t="s">
         <v>534</v>
@@ -17723,19 +17723,19 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>536</v>
+        <v>423</v>
       </c>
       <c r="I283" t="s">
-        <v>537</v>
+        <v>166</v>
       </c>
       <c r="J283" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="K283" t="s">
         <v>258</v>
       </c>
       <c r="L283" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="M283" t="s">
         <v>534</v>
@@ -17747,7 +17747,7 @@
         <v>54</v>
       </c>
       <c r="P283" t="s">
-        <v>537</v>
+        <v>166</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -17770,7 +17770,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>145</v>
+        <v>507</v>
       </c>
       <c r="F284" t="s">
         <v>254</v>
@@ -17779,19 +17779,19 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>377</v>
+        <v>537</v>
       </c>
       <c r="I284" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J284" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K284" t="s">
         <v>258</v>
       </c>
       <c r="L284" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="M284" t="s">
         <v>534</v>
@@ -17803,7 +17803,7 @@
         <v>54</v>
       </c>
       <c r="P284" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q284" t="s">
         <v>45</v>
@@ -17826,7 +17826,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>145</v>
+        <v>516</v>
       </c>
       <c r="F285" t="s">
         <v>254</v>
@@ -17835,19 +17835,19 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>447</v>
+        <v>346</v>
       </c>
       <c r="I285" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J285" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K285" t="s">
         <v>258</v>
       </c>
       <c r="L285" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M285" t="s">
         <v>534</v>
@@ -17859,7 +17859,7 @@
         <v>54</v>
       </c>
       <c r="P285" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17882,28 +17882,28 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
+        <v>507</v>
+      </c>
+      <c r="F286" t="s">
+        <v>254</v>
+      </c>
+      <c r="G286" t="s">
+        <v>41</v>
+      </c>
+      <c r="H286" t="s">
+        <v>543</v>
+      </c>
+      <c r="I286" t="s">
+        <v>544</v>
+      </c>
+      <c r="J286" t="s">
+        <v>510</v>
+      </c>
+      <c r="K286" t="s">
+        <v>258</v>
+      </c>
+      <c r="L286" t="s">
         <v>545</v>
-      </c>
-      <c r="F286" t="s">
-        <v>245</v>
-      </c>
-      <c r="G286" t="s">
-        <v>41</v>
-      </c>
-      <c r="H286" t="s">
-        <v>477</v>
-      </c>
-      <c r="I286" t="s">
-        <v>546</v>
-      </c>
-      <c r="J286" t="s">
-        <v>479</v>
-      </c>
-      <c r="K286" t="s">
-        <v>479</v>
-      </c>
-      <c r="L286" t="s">
-        <v>547</v>
       </c>
       <c r="M286" t="s">
         <v>534</v>
@@ -17915,7 +17915,7 @@
         <v>54</v>
       </c>
       <c r="P286" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -17947,10 +17947,10 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I287" t="s">
-        <v>166</v>
+        <v>547</v>
       </c>
       <c r="J287" t="s">
         <v>510</v>
@@ -17959,7 +17959,7 @@
         <v>258</v>
       </c>
       <c r="L287" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M287" t="s">
         <v>534</v>
@@ -17971,7 +17971,7 @@
         <v>54</v>
       </c>
       <c r="P287" t="s">
-        <v>166</v>
+        <v>547</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -17994,28 +17994,28 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
+        <v>507</v>
+      </c>
+      <c r="F288" t="s">
+        <v>254</v>
+      </c>
+      <c r="G288" t="s">
+        <v>41</v>
+      </c>
+      <c r="H288" t="s">
+        <v>549</v>
+      </c>
+      <c r="I288" t="s">
         <v>550</v>
       </c>
-      <c r="F288" t="s">
-        <v>245</v>
-      </c>
-      <c r="G288" t="s">
-        <v>41</v>
-      </c>
-      <c r="H288" t="s">
-        <v>434</v>
-      </c>
-      <c r="I288" t="s">
-        <v>166</v>
-      </c>
       <c r="J288" t="s">
-        <v>44</v>
+        <v>510</v>
       </c>
       <c r="K288" t="s">
-        <v>44</v>
+        <v>258</v>
       </c>
       <c r="L288" t="s">
-        <v>34</v>
+        <v>551</v>
       </c>
       <c r="M288" t="s">
         <v>534</v>
@@ -18027,7 +18027,7 @@
         <v>54</v>
       </c>
       <c r="P288" t="s">
-        <v>166</v>
+        <v>550</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18050,7 +18050,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>516</v>
+        <v>145</v>
       </c>
       <c r="F289" t="s">
         <v>254</v>
@@ -18059,19 +18059,19 @@
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="I289" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J289" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K289" t="s">
         <v>258</v>
       </c>
       <c r="L289" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M289" t="s">
         <v>534</v>
@@ -18083,7 +18083,7 @@
         <v>54</v>
       </c>
       <c r="P289" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18115,10 +18115,10 @@
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J290" t="s">
         <v>510</v>
@@ -18127,7 +18127,7 @@
         <v>258</v>
       </c>
       <c r="L290" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M290" t="s">
         <v>534</v>
@@ -18139,7 +18139,7 @@
         <v>54</v>
       </c>
       <c r="P290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q290" t="s">
         <v>45</v>
@@ -18162,28 +18162,28 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>507</v>
+        <v>558</v>
       </c>
       <c r="F291" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>557</v>
+        <v>477</v>
       </c>
       <c r="I291" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J291" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="K291" t="s">
-        <v>258</v>
+        <v>479</v>
       </c>
       <c r="L291" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M291" t="s">
         <v>534</v>
@@ -18195,7 +18195,7 @@
         <v>54</v>
       </c>
       <c r="P291" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18218,7 +18218,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>507</v>
+        <v>145</v>
       </c>
       <c r="F292" t="s">
         <v>254</v>
@@ -18227,19 +18227,19 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>560</v>
+        <v>440</v>
       </c>
       <c r="I292" t="s">
         <v>561</v>
       </c>
       <c r="J292" t="s">
-        <v>510</v>
+        <v>562</v>
       </c>
       <c r="K292" t="s">
         <v>258</v>
       </c>
       <c r="L292" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M292" t="s">
         <v>534</v>
@@ -18274,28 +18274,28 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="F293" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G293" t="s">
         <v>41</v>
       </c>
       <c r="H293" t="s">
-        <v>563</v>
+        <v>385</v>
       </c>
       <c r="I293" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="J293" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="K293" t="s">
-        <v>258</v>
+        <v>479</v>
       </c>
       <c r="L293" t="s">
-        <v>565</v>
+        <v>34</v>
       </c>
       <c r="M293" t="s">
         <v>534</v>
@@ -18307,7 +18307,7 @@
         <v>54</v>
       </c>
       <c r="P293" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="Q293" t="s">
         <v>45</v>
@@ -18330,25 +18330,25 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>550</v>
+        <v>145</v>
       </c>
       <c r="F294" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="G294" t="s">
         <v>41</v>
       </c>
       <c r="H294" t="s">
-        <v>385</v>
+        <v>564</v>
       </c>
       <c r="I294" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="J294" t="s">
-        <v>479</v>
+        <v>553</v>
       </c>
       <c r="K294" t="s">
-        <v>479</v>
+        <v>565</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -18360,13 +18360,13 @@
         <v>45</v>
       </c>
       <c r="O294" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P294" t="s">
-        <v>539</v>
+        <v>34</v>
       </c>
       <c r="Q294" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R294" t="s">
         <v>34</v>
@@ -18386,10 +18386,10 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>145</v>
+        <v>507</v>
       </c>
       <c r="F295" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="G295" t="s">
         <v>41</v>
@@ -18398,16 +18398,16 @@
         <v>566</v>
       </c>
       <c r="I295" t="s">
-        <v>539</v>
+        <v>166</v>
       </c>
       <c r="J295" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="K295" t="s">
+        <v>258</v>
+      </c>
+      <c r="L295" t="s">
         <v>567</v>
-      </c>
-      <c r="L295" t="s">
-        <v>34</v>
       </c>
       <c r="M295" t="s">
         <v>534</v>
@@ -18416,13 +18416,13 @@
         <v>45</v>
       </c>
       <c r="O295" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P295" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="Q295" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R295" t="s">
         <v>34</v>
@@ -18622,7 +18622,7 @@
         <v>576</v>
       </c>
       <c r="I299" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="J299" t="s">
         <v>161</v>

--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7816" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7816" uniqueCount="873">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -471,7 +471,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 400.528,06</t>
+    <t>R$ 400.623,41</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -1275,120 +1275,120 @@
     <t>R$ 14.015,81</t>
   </si>
   <si>
+    <t>R$  714,32</t>
+  </si>
+  <si>
+    <t>R$  746,58</t>
+  </si>
+  <si>
+    <t>R$  455,29</t>
+  </si>
+  <si>
+    <t>88001/1</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  237,08</t>
+  </si>
+  <si>
+    <t>88001brunoV</t>
+  </si>
+  <si>
+    <t>R$  114,28</t>
+  </si>
+  <si>
+    <t>87601/1</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  620,43</t>
+  </si>
+  <si>
+    <t>87601CleitonS</t>
+  </si>
+  <si>
+    <t>87301/1</t>
+  </si>
+  <si>
+    <t>R$  469,36</t>
+  </si>
+  <si>
+    <t>87301PatriciaSS</t>
+  </si>
+  <si>
+    <t>92001/1</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  346,86</t>
+  </si>
+  <si>
+    <t>92001LUCIANALS</t>
+  </si>
+  <si>
+    <t>56901/1</t>
+  </si>
+  <si>
+    <t>R$  170,33</t>
+  </si>
+  <si>
+    <t>56901BIANCARMS</t>
+  </si>
+  <si>
+    <t>83201/1</t>
+  </si>
+  <si>
+    <t>R$  4.535,18</t>
+  </si>
+  <si>
+    <t>83201ElaineMH</t>
+  </si>
+  <si>
+    <t>101701/2</t>
+  </si>
+  <si>
+    <t>97601/1</t>
+  </si>
+  <si>
+    <t>R$  146,38</t>
+  </si>
+  <si>
+    <t>97601FELIPEVS</t>
+  </si>
+  <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
     <t>R$  579,19</t>
   </si>
   <si>
-    <t>92001/1</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>R$  346,86</t>
-  </si>
-  <si>
-    <t>92001LUCIANALS</t>
-  </si>
-  <si>
-    <t>87601/1</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  620,43</t>
-  </si>
-  <si>
-    <t>87601CleitonS</t>
-  </si>
-  <si>
-    <t>87301/1</t>
-  </si>
-  <si>
-    <t>R$  469,36</t>
-  </si>
-  <si>
-    <t>87301PatriciaSS</t>
-  </si>
-  <si>
-    <t>R$  746,58</t>
-  </si>
-  <si>
-    <t>R$  455,29</t>
+    <t>R$  285,72</t>
+  </si>
+  <si>
+    <t>R$  173,64</t>
+  </si>
+  <si>
+    <t>R$  505,46</t>
+  </si>
+  <si>
+    <t>56102/2</t>
+  </si>
+  <si>
+    <t>98701/2</t>
+  </si>
+  <si>
+    <t>99401/2</t>
   </si>
   <si>
     <t>R$  1.059,03</t>
   </si>
   <si>
-    <t>97601/1</t>
-  </si>
-  <si>
-    <t>R$  146,38</t>
-  </si>
-  <si>
-    <t>97601FELIPEVS</t>
-  </si>
-  <si>
-    <t>83201/1</t>
-  </si>
-  <si>
-    <t>R$  4.535,18</t>
-  </si>
-  <si>
-    <t>83201ElaineMH</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  114,28</t>
-  </si>
-  <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>R$  505,46</t>
-  </si>
-  <si>
-    <t>88001/1</t>
-  </si>
-  <si>
-    <t>R$  237,08</t>
-  </si>
-  <si>
-    <t>88001brunoV</t>
-  </si>
-  <si>
-    <t>101701/2</t>
-  </si>
-  <si>
-    <t>56901/1</t>
-  </si>
-  <si>
-    <t>R$  170,33</t>
-  </si>
-  <si>
-    <t>56901BIANCARMS</t>
-  </si>
-  <si>
-    <t>R$  285,72</t>
-  </si>
-  <si>
-    <t>R$  714,32</t>
-  </si>
-  <si>
-    <t>99401/2</t>
-  </si>
-  <si>
-    <t>R$  173,64</t>
-  </si>
-  <si>
-    <t>98701/2</t>
-  </si>
-  <si>
-    <t>56102/2</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1452,18 +1452,18 @@
     <t>DSR set26/1</t>
   </si>
   <si>
+    <t>R$  592,53</t>
+  </si>
+  <si>
+    <t>07/09/26</t>
+  </si>
+  <si>
     <t>Rosangela Pacheco</t>
   </si>
   <si>
     <t>R$  1.046,14</t>
   </si>
   <si>
-    <t>07/09/26</t>
-  </si>
-  <si>
-    <t>R$  592,53</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1533,6 +1533,12 @@
     <t>Brindes clientes</t>
   </si>
   <si>
+    <t>766/1</t>
+  </si>
+  <si>
+    <t>vinho para clientes 1/3</t>
+  </si>
+  <si>
     <t>66/3</t>
   </si>
   <si>
@@ -1542,12 +1548,6 @@
     <t>Licoretto brinde clientes</t>
   </si>
   <si>
-    <t>766/1</t>
-  </si>
-  <si>
-    <t>vinho para clientes 1/3</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1608,7 +1608,7 @@
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
-    <t>R$ 87.270,58</t>
+    <t>R$ 87.365,93</t>
   </si>
   <si>
     <t>4.04.01 REMUNERAÇÃO FIXA</t>
@@ -1641,10 +1641,61 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Estorno emp set26/1</t>
+  </si>
+  <si>
+    <t>R$  282,79</t>
+  </si>
+  <si>
+    <t>Estorno desconto emprestimo</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
     <t>Fixo set26/1</t>
   </si>
   <si>
-    <t>Rubens - Pagamento 2026</t>
+    <t>R$  1.720,72</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
   </si>
   <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
@@ -1656,25 +1707,7 @@
     <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  1.720,72</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Carina Pereira</t>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>R$  2.365,00</t>
@@ -1692,15 +1725,6 @@
     <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -1710,36 +1734,12 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>Estorno emp set26/1</t>
-  </si>
-  <si>
-    <t>R$  282,79</t>
-  </si>
-  <si>
-    <t>Estorno desconto emprestimo</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
     <t>19/09/26</t>
   </si>
   <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1806,21 +1806,21 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT set26/1</t>
+  </si>
+  <si>
+    <t>R$  287,31</t>
+  </si>
+  <si>
+    <t>28/08/26</t>
+  </si>
+  <si>
     <t>VT set 26/1</t>
   </si>
   <si>
     <t>R$  413,84</t>
   </si>
   <si>
-    <t>VT set26/1</t>
-  </si>
-  <si>
-    <t>R$  287,31</t>
-  </si>
-  <si>
-    <t>28/08/26</t>
-  </si>
-  <si>
     <t>4.04.01.06 Assistência médica e hospitalar</t>
   </si>
   <si>
@@ -1845,7 +1845,7 @@
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
-    <t>R$ 32.476,78</t>
+    <t>R$ 32.572,13</t>
   </si>
   <si>
     <t>4.04.02.01 Aluguel / condomínio</t>
@@ -1872,7 +1872,7 @@
     <t>4.04.02.02 Energia elétrica</t>
   </si>
   <si>
-    <t>R$ 750,00</t>
+    <t>R$ 845,35</t>
   </si>
   <si>
     <t>4.04.02.02.01 Energia elétrica loja</t>
@@ -1884,12 +1884,15 @@
     <t>Enel</t>
   </si>
   <si>
-    <t>R$  750,00</t>
+    <t>R$  845,35</t>
   </si>
   <si>
     <t>21/01/26</t>
   </si>
   <si>
+    <t>Enel/2026</t>
+  </si>
+  <si>
     <t>4.04.02.03 Água</t>
   </si>
   <si>
@@ -1966,6 +1969,30 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
+  </si>
+  <si>
+    <t>761/1</t>
+  </si>
+  <si>
+    <t>R$  31,70</t>
+  </si>
+  <si>
+    <t>02/10/26</t>
+  </si>
+  <si>
+    <t>águas</t>
+  </si>
+  <si>
+    <t>738/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  92,00</t>
+  </si>
+  <si>
+    <t>Bolo Rosangela</t>
   </si>
   <si>
     <t>768/1</t>
@@ -1983,30 +2010,6 @@
 </t>
   </si>
   <si>
-    <t>738/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  92,00</t>
-  </si>
-  <si>
-    <t>Bolo Rosangela</t>
-  </si>
-  <si>
-    <t>761/1</t>
-  </si>
-  <si>
-    <t>R$  31,70</t>
-  </si>
-  <si>
-    <t>02/10/26</t>
-  </si>
-  <si>
-    <t>águas</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2049,51 +2052,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>Promob</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>63/4</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>70/1</t>
+  </si>
+  <si>
+    <t>R$  188,19</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>62/4</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
     <t>767/1</t>
   </si>
   <si>
-    <t>Promob</t>
-  </si>
-  <si>
     <t>R$  4.516,62</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>63/4</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/1</t>
-  </si>
-  <si>
-    <t>R$  188,19</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
-  </si>
-  <si>
-    <t>62/4</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
     <t>3/8</t>
   </si>
   <si>
@@ -2106,6 +2109,15 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>61/5</t>
   </si>
   <si>
@@ -2118,15 +2130,6 @@
     <t>21/05/26</t>
   </si>
   <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>64/4</t>
   </si>
   <si>
@@ -2364,7 +2367,7 @@
     <t>7.06 (-) DESPESAS REGULARES</t>
   </si>
   <si>
-    <t>R$ 185.944,60</t>
+    <t>R$ 186.039,95</t>
   </si>
   <si>
     <t>7.06.01 DESPESAS DE VENDAS</t>
@@ -2451,7 +2454,7 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 58.806,80</t>
+    <t>R$ 58.711,45</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
@@ -2475,7 +2478,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 35.184,60</t>
+    <t>R$ 35.089,25</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2508,7 +2511,7 @@
     <t>7.50.03 TOTAL DOS CUSTOS FIXOS</t>
   </si>
   <si>
-    <t>R$ 87.277,40</t>
+    <t>R$ 87.372,75</t>
   </si>
   <si>
     <t>7.50.03.01 Despesas administrativas</t>
@@ -2553,7 +2556,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 310.527,90</t>
+    <t>R$ 310.867,15</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -13394,7 +13397,7 @@
         <v>33</v>
       </c>
       <c r="E205" t="s">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="F205" t="s">
         <v>347</v>
@@ -13450,25 +13453,25 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
+        <v>327</v>
+      </c>
+      <c r="F206" t="s">
+        <v>347</v>
+      </c>
+      <c r="G206" t="s">
+        <v>41</v>
+      </c>
+      <c r="H206" t="s">
+        <v>182</v>
+      </c>
+      <c r="I206" t="s">
         <v>421</v>
       </c>
-      <c r="F206" t="s">
-        <v>189</v>
-      </c>
-      <c r="G206" t="s">
-        <v>41</v>
-      </c>
-      <c r="H206" t="s">
-        <v>422</v>
-      </c>
-      <c r="I206" t="s">
-        <v>423</v>
-      </c>
       <c r="J206" t="s">
-        <v>257</v>
+        <v>99</v>
       </c>
       <c r="K206" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13480,13 +13483,13 @@
         <v>45</v>
       </c>
       <c r="O206" t="s">
-        <v>424</v>
+        <v>34</v>
       </c>
       <c r="P206" t="s">
-        <v>423</v>
+        <v>34</v>
       </c>
       <c r="Q206" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R206" t="s">
         <v>34</v>
@@ -13506,25 +13509,25 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="F207" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>426</v>
+        <v>182</v>
       </c>
       <c r="I207" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J207" t="s">
-        <v>257</v>
+        <v>91</v>
       </c>
       <c r="K207" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13536,13 +13539,13 @@
         <v>45</v>
       </c>
       <c r="O207" t="s">
-        <v>428</v>
+        <v>34</v>
       </c>
       <c r="P207" t="s">
-        <v>427</v>
+        <v>34</v>
       </c>
       <c r="Q207" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R207" t="s">
         <v>34</v>
@@ -13562,25 +13565,25 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>429</v>
+        <v>304</v>
       </c>
       <c r="F208" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
       </c>
       <c r="H208" t="s">
-        <v>426</v>
+        <v>182</v>
       </c>
       <c r="I208" t="s">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="J208" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="K208" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13592,13 +13595,13 @@
         <v>45</v>
       </c>
       <c r="O208" t="s">
-        <v>431</v>
+        <v>34</v>
       </c>
       <c r="P208" t="s">
-        <v>430</v>
+        <v>34</v>
       </c>
       <c r="Q208" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R208" t="s">
         <v>34</v>
@@ -13618,25 +13621,25 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>327</v>
+        <v>423</v>
       </c>
       <c r="F209" t="s">
-        <v>347</v>
+        <v>189</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
       </c>
       <c r="H209" t="s">
-        <v>182</v>
+        <v>424</v>
       </c>
       <c r="I209" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="J209" t="s">
-        <v>99</v>
+        <v>257</v>
       </c>
       <c r="K209" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13648,13 +13651,13 @@
         <v>45</v>
       </c>
       <c r="O209" t="s">
-        <v>34</v>
+        <v>426</v>
       </c>
       <c r="P209" t="s">
-        <v>34</v>
+        <v>425</v>
       </c>
       <c r="Q209" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R209" t="s">
         <v>34</v>
@@ -13674,7 +13677,7 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="F210" t="s">
         <v>347</v>
@@ -13686,13 +13689,13 @@
         <v>182</v>
       </c>
       <c r="I210" t="s">
-        <v>433</v>
+        <v>358</v>
       </c>
       <c r="J210" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="K210" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13730,7 +13733,7 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="F211" t="s">
         <v>347</v>
@@ -13739,16 +13742,16 @@
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>182</v>
+        <v>424</v>
       </c>
       <c r="I211" t="s">
-        <v>360</v>
+        <v>427</v>
       </c>
       <c r="J211" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="K211" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -13786,25 +13789,25 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>308</v>
+        <v>428</v>
       </c>
       <c r="F212" t="s">
-        <v>347</v>
+        <v>189</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="I212" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J212" t="s">
-        <v>104</v>
+        <v>257</v>
       </c>
       <c r="K212" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -13816,13 +13819,13 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>34</v>
+        <v>431</v>
       </c>
       <c r="P212" t="s">
-        <v>34</v>
+        <v>430</v>
       </c>
       <c r="Q212" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R212" t="s">
         <v>34</v>
@@ -13842,7 +13845,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F213" t="s">
         <v>189</v>
@@ -13851,10 +13854,10 @@
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I213" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J213" t="s">
         <v>257</v>
@@ -13872,10 +13875,10 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="P213" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q213" t="s">
         <v>45</v>
@@ -13898,7 +13901,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F214" t="s">
         <v>189</v>
@@ -13907,10 +13910,10 @@
         <v>41</v>
       </c>
       <c r="H214" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="I214" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J214" t="s">
         <v>257</v>
@@ -13928,10 +13931,10 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P214" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q214" t="s">
         <v>45</v>
@@ -13954,25 +13957,25 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>319</v>
+        <v>439</v>
       </c>
       <c r="F215" t="s">
-        <v>347</v>
+        <v>189</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
       </c>
       <c r="H215" t="s">
-        <v>182</v>
+        <v>436</v>
       </c>
       <c r="I215" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="J215" t="s">
-        <v>117</v>
+        <v>257</v>
       </c>
       <c r="K215" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -13984,13 +13987,13 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>34</v>
+        <v>441</v>
       </c>
       <c r="P215" t="s">
-        <v>34</v>
+        <v>440</v>
       </c>
       <c r="Q215" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R215" t="s">
         <v>34</v>
@@ -14010,25 +14013,25 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>335</v>
+        <v>442</v>
       </c>
       <c r="F216" t="s">
-        <v>347</v>
+        <v>189</v>
       </c>
       <c r="G216" t="s">
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="I216" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J216" t="s">
-        <v>90</v>
+        <v>257</v>
       </c>
       <c r="K216" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="L216" t="s">
         <v>34</v>
@@ -14040,13 +14043,13 @@
         <v>45</v>
       </c>
       <c r="O216" t="s">
-        <v>34</v>
+        <v>444</v>
       </c>
       <c r="P216" t="s">
-        <v>34</v>
+        <v>443</v>
       </c>
       <c r="Q216" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R216" t="s">
         <v>34</v>
@@ -14066,25 +14069,25 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>188</v>
+        <v>445</v>
       </c>
       <c r="F217" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="G217" t="s">
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>443</v>
+        <v>182</v>
       </c>
       <c r="I217" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="J217" t="s">
-        <v>257</v>
+        <v>121</v>
       </c>
       <c r="K217" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="L217" t="s">
         <v>34</v>
@@ -14096,13 +14099,13 @@
         <v>45</v>
       </c>
       <c r="O217" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P217" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="Q217" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R217" t="s">
         <v>34</v>
@@ -14122,25 +14125,25 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>292</v>
+        <v>446</v>
       </c>
       <c r="F218" t="s">
-        <v>347</v>
+        <v>189</v>
       </c>
       <c r="G218" t="s">
         <v>41</v>
       </c>
       <c r="H218" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I218" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J218" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="K218" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="L218" t="s">
         <v>34</v>
@@ -14152,13 +14155,13 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>34</v>
+        <v>448</v>
       </c>
       <c r="P218" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="Q218" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R218" t="s">
         <v>34</v>
@@ -14178,7 +14181,7 @@
         <v>34</v>
       </c>
       <c r="E219" t="s">
-        <v>445</v>
+        <v>188</v>
       </c>
       <c r="F219" t="s">
         <v>189</v>
@@ -14187,10 +14190,10 @@
         <v>41</v>
       </c>
       <c r="H219" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="I219" t="s">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="J219" t="s">
         <v>257</v>
@@ -14208,10 +14211,10 @@
         <v>45</v>
       </c>
       <c r="O219" t="s">
-        <v>447</v>
+        <v>64</v>
       </c>
       <c r="P219" t="s">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="Q219" t="s">
         <v>45</v>
@@ -14234,7 +14237,7 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>448</v>
+        <v>296</v>
       </c>
       <c r="F220" t="s">
         <v>347</v>
@@ -14246,13 +14249,13 @@
         <v>182</v>
       </c>
       <c r="I220" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="J220" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K220" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L220" t="s">
         <v>34</v>
@@ -14290,25 +14293,25 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>449</v>
+        <v>222</v>
       </c>
       <c r="F221" t="s">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
       </c>
       <c r="H221" t="s">
-        <v>422</v>
+        <v>182</v>
       </c>
       <c r="I221" t="s">
         <v>450</v>
       </c>
       <c r="J221" t="s">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="K221" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14320,13 +14323,13 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>451</v>
+        <v>34</v>
       </c>
       <c r="P221" t="s">
-        <v>450</v>
+        <v>34</v>
       </c>
       <c r="Q221" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R221" t="s">
         <v>34</v>
@@ -14355,7 +14358,7 @@
         <v>41</v>
       </c>
       <c r="H222" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="I222" t="s">
         <v>361</v>
@@ -14414,7 +14417,7 @@
         <v>182</v>
       </c>
       <c r="I223" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J223" t="s">
         <v>80</v>
@@ -14458,7 +14461,7 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="F224" t="s">
         <v>347</v>
@@ -14467,16 +14470,16 @@
         <v>41</v>
       </c>
       <c r="H224" t="s">
-        <v>182</v>
+        <v>424</v>
       </c>
       <c r="I224" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J224" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="K224" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14514,7 +14517,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>454</v>
+        <v>292</v>
       </c>
       <c r="F225" t="s">
         <v>347</v>
@@ -14523,16 +14526,16 @@
         <v>41</v>
       </c>
       <c r="H225" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="I225" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="J225" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K225" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14570,7 +14573,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>277</v>
+        <v>454</v>
       </c>
       <c r="F226" t="s">
         <v>347</v>
@@ -14579,16 +14582,16 @@
         <v>41</v>
       </c>
       <c r="H226" t="s">
-        <v>441</v>
+        <v>182</v>
       </c>
       <c r="I226" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
       <c r="J226" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K226" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14626,7 +14629,7 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>296</v>
+        <v>455</v>
       </c>
       <c r="F227" t="s">
         <v>347</v>
@@ -14638,13 +14641,13 @@
         <v>182</v>
       </c>
       <c r="I227" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="J227" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K227" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14694,7 +14697,7 @@
         <v>182</v>
       </c>
       <c r="I228" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J228" t="s">
         <v>44</v>
@@ -14738,7 +14741,7 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>457</v>
+        <v>308</v>
       </c>
       <c r="F229" t="s">
         <v>347</v>
@@ -14750,13 +14753,13 @@
         <v>182</v>
       </c>
       <c r="I229" t="s">
-        <v>367</v>
+        <v>457</v>
       </c>
       <c r="J229" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K229" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -15755,16 +15758,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
+        <v>348</v>
+      </c>
+      <c r="I247" t="s">
         <v>479</v>
       </c>
-      <c r="I247" t="s">
+      <c r="J247" t="s">
         <v>480</v>
       </c>
-      <c r="J247" t="s">
-        <v>481</v>
-      </c>
       <c r="K247" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -15779,7 +15782,7 @@
         <v>54</v>
       </c>
       <c r="P247" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -15811,16 +15814,16 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>348</v>
+        <v>481</v>
       </c>
       <c r="I248" t="s">
         <v>482</v>
       </c>
       <c r="J248" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K248" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16026,10 +16029,10 @@
         <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F252" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
@@ -16041,10 +16044,10 @@
         <v>490</v>
       </c>
       <c r="J252" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="K252" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16056,13 +16059,13 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="P252" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="Q252" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R252" t="s">
         <v>34</v>
@@ -16082,7 +16085,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>188</v>
+        <v>351</v>
       </c>
       <c r="F253" t="s">
         <v>249</v>
@@ -16097,10 +16100,10 @@
         <v>490</v>
       </c>
       <c r="J253" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K253" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16112,7 +16115,7 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="P253" t="s">
         <v>490</v>
@@ -16138,10 +16141,10 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="F254" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
@@ -16153,10 +16156,10 @@
         <v>490</v>
       </c>
       <c r="J254" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="K254" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16168,7 +16171,7 @@
         <v>45</v>
       </c>
       <c r="O254" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="P254" t="s">
         <v>490</v>
@@ -16194,10 +16197,10 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="F255" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
@@ -16209,10 +16212,10 @@
         <v>490</v>
       </c>
       <c r="J255" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K255" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16224,13 +16227,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P255" t="s">
-        <v>490</v>
+        <v>34</v>
       </c>
       <c r="Q255" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16250,7 +16253,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F256" t="s">
         <v>244</v>
@@ -16265,10 +16268,10 @@
         <v>490</v>
       </c>
       <c r="J256" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="K256" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16280,7 +16283,7 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="P256" t="s">
         <v>490</v>
@@ -16306,10 +16309,10 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>69</v>
+        <v>238</v>
       </c>
       <c r="F257" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="G257" t="s">
         <v>41</v>
@@ -16321,10 +16324,10 @@
         <v>490</v>
       </c>
       <c r="J257" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="K257" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L257" t="s">
         <v>34</v>
@@ -16336,13 +16339,13 @@
         <v>45</v>
       </c>
       <c r="O257" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="P257" t="s">
-        <v>490</v>
+        <v>34</v>
       </c>
       <c r="Q257" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R257" t="s">
         <v>34</v>
@@ -16362,10 +16365,10 @@
         <v>34</v>
       </c>
       <c r="E258" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="F258" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
@@ -16377,10 +16380,10 @@
         <v>490</v>
       </c>
       <c r="J258" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="K258" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="L258" t="s">
         <v>34</v>
@@ -16392,7 +16395,7 @@
         <v>45</v>
       </c>
       <c r="O258" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="P258" t="s">
         <v>490</v>
@@ -16418,10 +16421,10 @@
         <v>34</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>226</v>
       </c>
       <c r="F259" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -16433,10 +16436,10 @@
         <v>490</v>
       </c>
       <c r="J259" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K259" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L259" t="s">
         <v>34</v>
@@ -16448,13 +16451,13 @@
         <v>45</v>
       </c>
       <c r="O259" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P259" t="s">
-        <v>490</v>
+        <v>34</v>
       </c>
       <c r="Q259" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R259" t="s">
         <v>34</v>
@@ -16474,7 +16477,7 @@
         <v>34</v>
       </c>
       <c r="E260" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="F260" t="s">
         <v>159</v>
@@ -16489,10 +16492,10 @@
         <v>490</v>
       </c>
       <c r="J260" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K260" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L260" t="s">
         <v>34</v>
@@ -16530,7 +16533,7 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F261" t="s">
         <v>159</v>
@@ -16545,10 +16548,10 @@
         <v>490</v>
       </c>
       <c r="J261" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="K261" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="L261" t="s">
         <v>34</v>
@@ -16586,7 +16589,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F262" t="s">
         <v>159</v>
@@ -16601,10 +16604,10 @@
         <v>490</v>
       </c>
       <c r="J262" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="K262" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="L262" t="s">
         <v>34</v>
@@ -16642,10 +16645,10 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>351</v>
+        <v>196</v>
       </c>
       <c r="F263" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
@@ -16654,13 +16657,13 @@
         <v>489</v>
       </c>
       <c r="I263" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J263" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="K263" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="L263" t="s">
         <v>34</v>
@@ -16672,13 +16675,13 @@
         <v>45</v>
       </c>
       <c r="O263" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="P263" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="Q263" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R263" t="s">
         <v>34</v>
@@ -16698,10 +16701,10 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="F264" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="G264" t="s">
         <v>41</v>
@@ -16713,10 +16716,10 @@
         <v>490</v>
       </c>
       <c r="J264" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="K264" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -16728,13 +16731,13 @@
         <v>45</v>
       </c>
       <c r="O264" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="P264" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="Q264" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R264" t="s">
         <v>34</v>
@@ -16754,10 +16757,10 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>217</v>
+        <v>351</v>
       </c>
       <c r="F265" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="G265" t="s">
         <v>41</v>
@@ -16766,13 +16769,13 @@
         <v>489</v>
       </c>
       <c r="I265" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J265" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K265" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -16810,7 +16813,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="F266" t="s">
         <v>159</v>
@@ -16825,10 +16828,10 @@
         <v>490</v>
       </c>
       <c r="J266" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="K266" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -16866,7 +16869,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="F267" t="s">
         <v>159</v>
@@ -16881,10 +16884,10 @@
         <v>490</v>
       </c>
       <c r="J267" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="K267" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17149,7 +17152,7 @@
         <v>506</v>
       </c>
       <c r="F272" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
@@ -17158,16 +17161,16 @@
         <v>503</v>
       </c>
       <c r="I272" t="s">
+        <v>504</v>
+      </c>
+      <c r="J272" t="s">
+        <v>257</v>
+      </c>
+      <c r="K272" t="s">
+        <v>480</v>
+      </c>
+      <c r="L272" t="s">
         <v>507</v>
-      </c>
-      <c r="J272" t="s">
-        <v>271</v>
-      </c>
-      <c r="K272" t="s">
-        <v>253</v>
-      </c>
-      <c r="L272" t="s">
-        <v>508</v>
       </c>
       <c r="M272" t="s">
         <v>501</v>
@@ -17179,7 +17182,7 @@
         <v>54</v>
       </c>
       <c r="P272" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17202,10 +17205,10 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F273" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17214,13 +17217,13 @@
         <v>503</v>
       </c>
       <c r="I273" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="J273" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="K273" t="s">
-        <v>481</v>
+        <v>253</v>
       </c>
       <c r="L273" t="s">
         <v>510</v>
@@ -17235,7 +17238,7 @@
         <v>54</v>
       </c>
       <c r="P273" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17874,28 +17877,28 @@
         <v>33</v>
       </c>
       <c r="E285" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="F285" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G285" t="s">
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="I285" t="s">
         <v>166</v>
       </c>
       <c r="J285" t="s">
-        <v>44</v>
+        <v>521</v>
       </c>
       <c r="K285" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="L285" t="s">
-        <v>34</v>
+        <v>542</v>
       </c>
       <c r="M285" t="s">
         <v>541</v>
@@ -17939,19 +17942,19 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>426</v>
+        <v>543</v>
       </c>
       <c r="I286" t="s">
-        <v>166</v>
+        <v>544</v>
       </c>
       <c r="J286" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="K286" t="s">
         <v>253</v>
       </c>
       <c r="L286" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M286" t="s">
         <v>541</v>
@@ -17963,7 +17966,7 @@
         <v>54</v>
       </c>
       <c r="P286" t="s">
-        <v>166</v>
+        <v>544</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -17986,7 +17989,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>514</v>
+        <v>145</v>
       </c>
       <c r="F287" t="s">
         <v>249</v>
@@ -17995,19 +17998,19 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>544</v>
+        <v>379</v>
       </c>
       <c r="I287" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J287" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="K287" t="s">
         <v>253</v>
       </c>
       <c r="L287" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M287" t="s">
         <v>541</v>
@@ -18019,7 +18022,7 @@
         <v>54</v>
       </c>
       <c r="P287" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18042,7 +18045,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>523</v>
+        <v>145</v>
       </c>
       <c r="F288" t="s">
         <v>249</v>
@@ -18051,19 +18054,19 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>348</v>
+        <v>449</v>
       </c>
       <c r="I288" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J288" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K288" t="s">
         <v>253</v>
       </c>
       <c r="L288" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M288" t="s">
         <v>541</v>
@@ -18075,7 +18078,7 @@
         <v>54</v>
       </c>
       <c r="P288" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18098,28 +18101,28 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="F289" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>550</v>
+        <v>481</v>
       </c>
       <c r="I289" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J289" t="s">
-        <v>517</v>
+        <v>480</v>
       </c>
       <c r="K289" t="s">
-        <v>253</v>
+        <v>480</v>
       </c>
       <c r="L289" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M289" t="s">
         <v>541</v>
@@ -18131,7 +18134,7 @@
         <v>54</v>
       </c>
       <c r="P289" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18163,10 +18166,10 @@
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I290" t="s">
-        <v>554</v>
+        <v>166</v>
       </c>
       <c r="J290" t="s">
         <v>517</v>
@@ -18175,7 +18178,7 @@
         <v>253</v>
       </c>
       <c r="L290" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M290" t="s">
         <v>541</v>
@@ -18187,7 +18190,7 @@
         <v>54</v>
       </c>
       <c r="P290" t="s">
-        <v>554</v>
+        <v>166</v>
       </c>
       <c r="Q290" t="s">
         <v>45</v>
@@ -18210,28 +18213,28 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="F291" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G291" t="s">
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>556</v>
+        <v>436</v>
       </c>
       <c r="I291" t="s">
-        <v>557</v>
+        <v>166</v>
       </c>
       <c r="J291" t="s">
-        <v>517</v>
+        <v>44</v>
       </c>
       <c r="K291" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="L291" t="s">
-        <v>558</v>
+        <v>34</v>
       </c>
       <c r="M291" t="s">
         <v>541</v>
@@ -18243,7 +18246,7 @@
         <v>54</v>
       </c>
       <c r="P291" t="s">
-        <v>557</v>
+        <v>166</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18266,7 +18269,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>145</v>
+        <v>523</v>
       </c>
       <c r="F292" t="s">
         <v>249</v>
@@ -18275,19 +18278,19 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="I292" t="s">
+        <v>558</v>
+      </c>
+      <c r="J292" t="s">
         <v>559</v>
-      </c>
-      <c r="J292" t="s">
-        <v>560</v>
       </c>
       <c r="K292" t="s">
         <v>253</v>
       </c>
       <c r="L292" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M292" t="s">
         <v>541</v>
@@ -18299,7 +18302,7 @@
         <v>54</v>
       </c>
       <c r="P292" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18331,10 +18334,10 @@
         <v>41</v>
       </c>
       <c r="H293" t="s">
+        <v>561</v>
+      </c>
+      <c r="I293" t="s">
         <v>562</v>
-      </c>
-      <c r="I293" t="s">
-        <v>563</v>
       </c>
       <c r="J293" t="s">
         <v>517</v>
@@ -18343,7 +18346,7 @@
         <v>253</v>
       </c>
       <c r="L293" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="M293" t="s">
         <v>541</v>
@@ -18355,7 +18358,7 @@
         <v>54</v>
       </c>
       <c r="P293" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Q293" t="s">
         <v>45</v>
@@ -18378,28 +18381,28 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
+        <v>514</v>
+      </c>
+      <c r="F294" t="s">
+        <v>249</v>
+      </c>
+      <c r="G294" t="s">
+        <v>41</v>
+      </c>
+      <c r="H294" t="s">
+        <v>564</v>
+      </c>
+      <c r="I294" t="s">
         <v>565</v>
       </c>
-      <c r="F294" t="s">
-        <v>244</v>
-      </c>
-      <c r="G294" t="s">
-        <v>41</v>
-      </c>
-      <c r="H294" t="s">
-        <v>479</v>
-      </c>
-      <c r="I294" t="s">
+      <c r="J294" t="s">
+        <v>517</v>
+      </c>
+      <c r="K294" t="s">
+        <v>253</v>
+      </c>
+      <c r="L294" t="s">
         <v>566</v>
-      </c>
-      <c r="J294" t="s">
-        <v>481</v>
-      </c>
-      <c r="K294" t="s">
-        <v>481</v>
-      </c>
-      <c r="L294" t="s">
-        <v>567</v>
       </c>
       <c r="M294" t="s">
         <v>541</v>
@@ -18411,7 +18414,7 @@
         <v>54</v>
       </c>
       <c r="P294" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q294" t="s">
         <v>45</v>
@@ -18434,7 +18437,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>145</v>
+        <v>514</v>
       </c>
       <c r="F295" t="s">
         <v>249</v>
@@ -18443,19 +18446,19 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>443</v>
+        <v>567</v>
       </c>
       <c r="I295" t="s">
         <v>568</v>
       </c>
       <c r="J295" t="s">
-        <v>569</v>
+        <v>517</v>
       </c>
       <c r="K295" t="s">
         <v>253</v>
       </c>
       <c r="L295" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M295" t="s">
         <v>541</v>
@@ -18490,28 +18493,28 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="F296" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G296" t="s">
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>387</v>
+        <v>570</v>
       </c>
       <c r="I296" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="J296" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
       <c r="K296" t="s">
-        <v>481</v>
+        <v>253</v>
       </c>
       <c r="L296" t="s">
-        <v>34</v>
+        <v>572</v>
       </c>
       <c r="M296" t="s">
         <v>541</v>
@@ -18523,7 +18526,7 @@
         <v>54</v>
       </c>
       <c r="P296" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18546,25 +18549,25 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>145</v>
+        <v>557</v>
       </c>
       <c r="F297" t="s">
-        <v>159</v>
+        <v>244</v>
       </c>
       <c r="G297" t="s">
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>571</v>
+        <v>387</v>
       </c>
       <c r="I297" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="J297" t="s">
-        <v>560</v>
+        <v>480</v>
       </c>
       <c r="K297" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -18576,13 +18579,13 @@
         <v>45</v>
       </c>
       <c r="O297" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P297" t="s">
-        <v>34</v>
+        <v>546</v>
       </c>
       <c r="Q297" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R297" t="s">
         <v>34</v>
@@ -18602,10 +18605,10 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>514</v>
+        <v>145</v>
       </c>
       <c r="F298" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="G298" t="s">
         <v>41</v>
@@ -18614,16 +18617,16 @@
         <v>573</v>
       </c>
       <c r="I298" t="s">
-        <v>166</v>
+        <v>546</v>
       </c>
       <c r="J298" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="K298" t="s">
-        <v>253</v>
+        <v>574</v>
       </c>
       <c r="L298" t="s">
-        <v>574</v>
+        <v>34</v>
       </c>
       <c r="M298" t="s">
         <v>541</v>
@@ -18632,13 +18635,13 @@
         <v>45</v>
       </c>
       <c r="O298" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P298" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="Q298" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R298" t="s">
         <v>34</v>
@@ -18838,7 +18841,7 @@
         <v>583</v>
       </c>
       <c r="I302" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="J302" t="s">
         <v>161</v>
@@ -19227,16 +19230,16 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>479</v>
+        <v>348</v>
       </c>
       <c r="I309" t="s">
         <v>598</v>
       </c>
       <c r="J309" t="s">
-        <v>44</v>
+        <v>599</v>
       </c>
       <c r="K309" t="s">
-        <v>44</v>
+        <v>480</v>
       </c>
       <c r="L309" t="s">
         <v>34</v>
@@ -19274,7 +19277,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F310" t="s">
         <v>244</v>
@@ -19283,16 +19286,16 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>348</v>
+        <v>481</v>
       </c>
       <c r="I310" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J310" t="s">
-        <v>601</v>
+        <v>44</v>
       </c>
       <c r="K310" t="s">
-        <v>481</v>
+        <v>44</v>
       </c>
       <c r="L310" t="s">
         <v>34</v>
@@ -19307,7 +19310,7 @@
         <v>54</v>
       </c>
       <c r="P310" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="Q310" t="s">
         <v>45</v>
@@ -19669,7 +19672,7 @@
         <v>621</v>
       </c>
       <c r="F317" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="G317" t="s">
         <v>41</v>
@@ -19687,7 +19690,7 @@
         <v>80</v>
       </c>
       <c r="L317" t="s">
-        <v>34</v>
+        <v>625</v>
       </c>
       <c r="M317" t="s">
         <v>620</v>
@@ -19696,13 +19699,13 @@
         <v>45</v>
       </c>
       <c r="O317" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P317" t="s">
-        <v>34</v>
+        <v>623</v>
       </c>
       <c r="Q317" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R317" t="s">
         <v>34</v>
@@ -19710,13 +19713,13 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="1">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B318" t="s" s="1">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C318" t="s" s="1">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D318" t="s" s="1">
         <v>33</v>
@@ -19766,13 +19769,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
+        <v>628</v>
+      </c>
+      <c r="B319" t="s">
         <v>627</v>
       </c>
-      <c r="B319" t="s">
-        <v>626</v>
-      </c>
       <c r="C319" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D319" t="s">
         <v>33</v>
@@ -19787,10 +19790,10 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I319" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J319" t="s">
         <v>517</v>
@@ -19799,10 +19802,10 @@
         <v>253</v>
       </c>
       <c r="L319" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M319" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N319" t="s">
         <v>45</v>
@@ -19811,7 +19814,7 @@
         <v>54</v>
       </c>
       <c r="P319" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Q319" t="s">
         <v>45</v>
@@ -19822,13 +19825,13 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="1">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B320" t="s" s="1">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C320" t="s" s="1">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D320" t="s" s="1">
         <v>33</v>
@@ -19878,13 +19881,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B321" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C321" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D321" t="s">
         <v>33</v>
@@ -19899,13 +19902,13 @@
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I321" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="J321" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K321" t="s">
         <v>91</v>
@@ -19914,7 +19917,7 @@
         <v>34</v>
       </c>
       <c r="M321" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N321" t="s">
         <v>45</v>
@@ -19934,13 +19937,13 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B322" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C322" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D322" t="s">
         <v>33</v>
@@ -19955,10 +19958,10 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I322" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J322" t="s">
         <v>517</v>
@@ -19967,10 +19970,10 @@
         <v>267</v>
       </c>
       <c r="L322" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M322" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N322" t="s">
         <v>45</v>
@@ -19979,7 +19982,7 @@
         <v>54</v>
       </c>
       <c r="P322" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Q322" t="s">
         <v>45</v>
@@ -19990,13 +19993,13 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="1">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B323" t="s" s="1">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C323" t="s" s="1">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D323" t="s" s="1">
         <v>33</v>
@@ -20046,13 +20049,13 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
+        <v>645</v>
+      </c>
+      <c r="B324" t="s">
         <v>644</v>
       </c>
-      <c r="B324" t="s">
-        <v>643</v>
-      </c>
       <c r="C324" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D324" t="s">
         <v>33</v>
@@ -20067,10 +20070,10 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="I324" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J324" t="s">
         <v>517</v>
@@ -20079,10 +20082,10 @@
         <v>261</v>
       </c>
       <c r="L324" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M324" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N324" t="s">
         <v>45</v>
@@ -20091,7 +20094,7 @@
         <v>54</v>
       </c>
       <c r="P324" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20102,13 +20105,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="1">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B325" t="s" s="1">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C325" t="s" s="1">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D325" t="s" s="1">
         <v>33</v>
@@ -20158,19 +20161,19 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
+        <v>651</v>
+      </c>
+      <c r="B326" t="s">
         <v>650</v>
       </c>
-      <c r="B326" t="s">
-        <v>649</v>
-      </c>
       <c r="C326" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D326" t="s">
         <v>33</v>
       </c>
       <c r="E326" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F326" t="s">
         <v>244</v>
@@ -20179,22 +20182,22 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>652</v>
+        <v>348</v>
       </c>
       <c r="I326" t="s">
         <v>653</v>
       </c>
       <c r="J326" t="s">
-        <v>257</v>
+        <v>654</v>
       </c>
       <c r="K326" t="s">
-        <v>481</v>
+        <v>63</v>
       </c>
       <c r="L326" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M326" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N326" t="s">
         <v>45</v>
@@ -20214,7 +20217,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B327" t="s">
         <v>34</v>
@@ -20226,7 +20229,7 @@
         <v>34</v>
       </c>
       <c r="E327" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F327" t="s">
         <v>244</v>
@@ -20235,10 +20238,10 @@
         <v>41</v>
       </c>
       <c r="H327" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I327" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J327" t="s">
         <v>52</v>
@@ -20247,10 +20250,10 @@
         <v>44</v>
       </c>
       <c r="L327" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M327" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N327" t="s">
         <v>45</v>
@@ -20259,7 +20262,7 @@
         <v>54</v>
       </c>
       <c r="P327" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q327" t="s">
         <v>45</v>
@@ -20270,7 +20273,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B328" t="s">
         <v>34</v>
@@ -20282,7 +20285,7 @@
         <v>34</v>
       </c>
       <c r="E328" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F328" t="s">
         <v>244</v>
@@ -20291,22 +20294,22 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>348</v>
+        <v>661</v>
       </c>
       <c r="I328" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J328" t="s">
-        <v>661</v>
+        <v>257</v>
       </c>
       <c r="K328" t="s">
-        <v>63</v>
+        <v>480</v>
       </c>
       <c r="L328" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M328" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N328" t="s">
         <v>45</v>
@@ -20315,7 +20318,7 @@
         <v>54</v>
       </c>
       <c r="P328" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Q328" t="s">
         <v>45</v>
@@ -20326,13 +20329,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="1">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B329" t="s" s="1">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C329" t="s" s="1">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D329" t="s" s="1">
         <v>33</v>
@@ -20382,13 +20385,13 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B330" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C330" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
@@ -20403,10 +20406,10 @@
         <v>41</v>
       </c>
       <c r="H330" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I330" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J330" t="s">
         <v>517</v>
@@ -20415,10 +20418,10 @@
         <v>253</v>
       </c>
       <c r="L330" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M330" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N330" t="s">
         <v>45</v>
@@ -20427,7 +20430,7 @@
         <v>54</v>
       </c>
       <c r="P330" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Q330" t="s">
         <v>45</v>
@@ -20438,13 +20441,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B331" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C331" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D331" t="s">
         <v>33</v>
@@ -20459,13 +20462,13 @@
         <v>41</v>
       </c>
       <c r="H331" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I331" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J331" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K331" t="s">
         <v>117</v>
@@ -20474,7 +20477,7 @@
         <v>34</v>
       </c>
       <c r="M331" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N331" t="s">
         <v>45</v>
@@ -20494,13 +20497,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="1">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B332" t="s" s="1">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C332" t="s" s="1">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D332" t="s" s="1">
         <v>33</v>
@@ -20550,22 +20553,22 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
+        <v>677</v>
+      </c>
+      <c r="B333" t="s">
         <v>676</v>
       </c>
-      <c r="B333" t="s">
-        <v>675</v>
-      </c>
       <c r="C333" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D333" t="s">
         <v>33</v>
       </c>
       <c r="E333" t="s">
-        <v>677</v>
+        <v>514</v>
       </c>
       <c r="F333" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
@@ -20577,16 +20580,16 @@
         <v>679</v>
       </c>
       <c r="J333" t="s">
-        <v>257</v>
+        <v>521</v>
       </c>
       <c r="K333" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="L333" t="s">
-        <v>34</v>
+        <v>680</v>
       </c>
       <c r="M333" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N333" t="s">
         <v>45</v>
@@ -20606,7 +20609,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B334" t="s">
         <v>34</v>
@@ -20618,7 +20621,7 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>514</v>
+        <v>681</v>
       </c>
       <c r="F334" t="s">
         <v>249</v>
@@ -20630,19 +20633,19 @@
         <v>678</v>
       </c>
       <c r="I334" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="J334" t="s">
-        <v>521</v>
+        <v>683</v>
       </c>
       <c r="K334" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="L334" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="M334" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N334" t="s">
         <v>45</v>
@@ -20651,7 +20654,7 @@
         <v>54</v>
       </c>
       <c r="P334" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="Q334" t="s">
         <v>45</v>
@@ -20662,7 +20665,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B335" t="s">
         <v>34</v>
@@ -20674,7 +20677,7 @@
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F335" t="s">
         <v>249</v>
@@ -20686,19 +20689,19 @@
         <v>678</v>
       </c>
       <c r="I335" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J335" t="s">
-        <v>684</v>
+        <v>63</v>
       </c>
       <c r="K335" t="s">
         <v>253</v>
       </c>
       <c r="L335" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M335" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N335" t="s">
         <v>45</v>
@@ -20707,7 +20710,7 @@
         <v>54</v>
       </c>
       <c r="P335" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="Q335" t="s">
         <v>45</v>
@@ -20718,7 +20721,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B336" t="s">
         <v>34</v>
@@ -20730,7 +20733,7 @@
         <v>34</v>
       </c>
       <c r="E336" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F336" t="s">
         <v>249</v>
@@ -20742,19 +20745,19 @@
         <v>678</v>
       </c>
       <c r="I336" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J336" t="s">
-        <v>63</v>
+        <v>683</v>
       </c>
       <c r="K336" t="s">
         <v>253</v>
       </c>
       <c r="L336" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M336" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N336" t="s">
         <v>45</v>
@@ -20763,7 +20766,7 @@
         <v>54</v>
       </c>
       <c r="P336" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="Q336" t="s">
         <v>45</v>
@@ -20774,7 +20777,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B337" t="s">
         <v>34</v>
@@ -20786,10 +20789,10 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F337" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G337" t="s">
         <v>41</v>
@@ -20798,19 +20801,19 @@
         <v>678</v>
       </c>
       <c r="I337" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J337" t="s">
-        <v>684</v>
+        <v>257</v>
       </c>
       <c r="K337" t="s">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L337" t="s">
-        <v>691</v>
+        <v>34</v>
       </c>
       <c r="M337" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N337" t="s">
         <v>45</v>
@@ -20819,7 +20822,7 @@
         <v>54</v>
       </c>
       <c r="P337" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Q337" t="s">
         <v>45</v>
@@ -20830,7 +20833,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B338" t="s">
         <v>34</v>
@@ -20842,7 +20845,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F338" t="s">
         <v>249</v>
@@ -20854,19 +20857,19 @@
         <v>678</v>
       </c>
       <c r="I338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J338" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K338" t="s">
         <v>253</v>
       </c>
       <c r="L338" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M338" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N338" t="s">
         <v>45</v>
@@ -20875,7 +20878,7 @@
         <v>54</v>
       </c>
       <c r="P338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q338" t="s">
         <v>45</v>
@@ -20886,7 +20889,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B339" t="s">
         <v>34</v>
@@ -20898,7 +20901,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>696</v>
+        <v>514</v>
       </c>
       <c r="F339" t="s">
         <v>249</v>
@@ -20913,16 +20916,16 @@
         <v>698</v>
       </c>
       <c r="J339" t="s">
-        <v>699</v>
+        <v>521</v>
       </c>
       <c r="K339" t="s">
         <v>253</v>
       </c>
       <c r="L339" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M339" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N339" t="s">
         <v>45</v>
@@ -20942,7 +20945,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B340" t="s">
         <v>34</v>
@@ -20954,7 +20957,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>514</v>
+        <v>700</v>
       </c>
       <c r="F340" t="s">
         <v>249</v>
@@ -20963,22 +20966,22 @@
         <v>41</v>
       </c>
       <c r="H340" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I340" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J340" t="s">
-        <v>521</v>
+        <v>703</v>
       </c>
       <c r="K340" t="s">
         <v>253</v>
       </c>
       <c r="L340" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M340" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N340" t="s">
         <v>45</v>
@@ -20987,7 +20990,7 @@
         <v>54</v>
       </c>
       <c r="P340" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Q340" t="s">
         <v>45</v>
@@ -20998,7 +21001,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B341" t="s">
         <v>34</v>
@@ -21010,7 +21013,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F341" t="s">
         <v>159</v>
@@ -21019,13 +21022,13 @@
         <v>41</v>
       </c>
       <c r="H341" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I341" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J341" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K341" t="s">
         <v>58</v>
@@ -21034,7 +21037,7 @@
         <v>34</v>
       </c>
       <c r="M341" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N341" t="s">
         <v>45</v>
@@ -21054,13 +21057,13 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="1">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B342" t="s" s="1">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C342" t="s" s="1">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D342" t="s" s="1">
         <v>33</v>
@@ -21110,13 +21113,13 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
+        <v>710</v>
+      </c>
+      <c r="B343" t="s">
         <v>709</v>
       </c>
-      <c r="B343" t="s">
-        <v>708</v>
-      </c>
       <c r="C343" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D343" t="s">
         <v>33</v>
@@ -21131,10 +21134,10 @@
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I343" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J343" t="s">
         <v>517</v>
@@ -21143,10 +21146,10 @@
         <v>253</v>
       </c>
       <c r="L343" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M343" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N343" t="s">
         <v>45</v>
@@ -21155,7 +21158,7 @@
         <v>54</v>
       </c>
       <c r="P343" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Q343" t="s">
         <v>45</v>
@@ -21166,13 +21169,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="1">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B344" t="s" s="1">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C344" t="s" s="1">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D344" t="s" s="1">
         <v>33</v>
@@ -21222,13 +21225,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B345" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C345" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D345" t="s">
         <v>33</v>
@@ -21243,10 +21246,10 @@
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I345" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J345" t="s">
         <v>161</v>
@@ -21255,10 +21258,10 @@
         <v>172</v>
       </c>
       <c r="L345" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M345" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N345" t="s">
         <v>45</v>
@@ -21267,7 +21270,7 @@
         <v>54</v>
       </c>
       <c r="P345" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q345" t="s">
         <v>45</v>
@@ -21278,19 +21281,19 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B346" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C346" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
       </c>
       <c r="E346" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F346" t="s">
         <v>249</v>
@@ -21299,22 +21302,22 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I346" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J346" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K346" t="s">
         <v>91</v>
       </c>
       <c r="L346" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M346" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N346" t="s">
         <v>45</v>
@@ -21323,7 +21326,7 @@
         <v>54</v>
       </c>
       <c r="P346" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="Q346" t="s">
         <v>45</v>
@@ -21334,13 +21337,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B347" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C347" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D347" t="s">
         <v>33</v>
@@ -21355,10 +21358,10 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I347" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="J347" t="s">
         <v>529</v>
@@ -21370,7 +21373,7 @@
         <v>34</v>
       </c>
       <c r="M347" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N347" t="s">
         <v>45</v>
@@ -21390,7 +21393,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B348" t="s">
         <v>34</v>
@@ -21411,10 +21414,10 @@
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I348" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J348" t="s">
         <v>517</v>
@@ -21423,10 +21426,10 @@
         <v>253</v>
       </c>
       <c r="L348" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M348" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N348" t="s">
         <v>45</v>
@@ -21435,7 +21438,7 @@
         <v>54</v>
       </c>
       <c r="P348" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Q348" t="s">
         <v>45</v>
@@ -21446,13 +21449,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B349" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C349" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D349" t="s">
         <v>33</v>
@@ -21467,13 +21470,13 @@
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I349" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J349" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K349" t="s">
         <v>253</v>
@@ -21482,7 +21485,7 @@
         <v>34</v>
       </c>
       <c r="M349" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N349" t="s">
         <v>45</v>
@@ -21502,13 +21505,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="1">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B350" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C350" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D350" t="s" s="1">
         <v>33</v>
@@ -21558,13 +21561,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="1">
+        <v>741</v>
+      </c>
+      <c r="B351" t="s" s="1">
         <v>740</v>
       </c>
-      <c r="B351" t="s" s="1">
-        <v>739</v>
-      </c>
       <c r="C351" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D351" t="s" s="1">
         <v>33</v>
@@ -21614,13 +21617,13 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="1">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B352" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C352" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D352" t="s" s="1">
         <v>33</v>
@@ -21670,19 +21673,19 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B353" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C353" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D353" t="s">
         <v>33</v>
       </c>
       <c r="E353" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F353" t="s">
         <v>244</v>
@@ -21691,22 +21694,22 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I353" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="J353" t="s">
         <v>257</v>
       </c>
       <c r="K353" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L353" t="s">
         <v>34</v>
       </c>
       <c r="M353" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N353" t="s">
         <v>45</v>
@@ -21715,7 +21718,7 @@
         <v>54</v>
       </c>
       <c r="P353" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="Q353" t="s">
         <v>45</v>
@@ -21726,13 +21729,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="1">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B354" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C354" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D354" t="s" s="1">
         <v>33</v>
@@ -21782,13 +21785,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="1">
+        <v>749</v>
+      </c>
+      <c r="B355" t="s" s="1">
         <v>748</v>
       </c>
-      <c r="B355" t="s" s="1">
-        <v>747</v>
-      </c>
       <c r="C355" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D355" t="s" s="1">
         <v>33</v>
@@ -21838,13 +21841,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="1">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B356" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C356" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D356" t="s" s="1">
         <v>33</v>
@@ -21894,13 +21897,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B357" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C357" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D357" t="s">
         <v>33</v>
@@ -21915,10 +21918,10 @@
         <v>41</v>
       </c>
       <c r="H357" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I357" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J357" t="s">
         <v>63</v>
@@ -21927,10 +21930,10 @@
         <v>63</v>
       </c>
       <c r="L357" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M357" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N357" t="s">
         <v>45</v>
@@ -21950,7 +21953,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B358" t="s">
         <v>34</v>
@@ -21971,10 +21974,10 @@
         <v>41</v>
       </c>
       <c r="H358" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I358" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J358" t="s">
         <v>44</v>
@@ -21983,10 +21986,10 @@
         <v>44</v>
       </c>
       <c r="L358" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M358" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N358" t="s">
         <v>45</v>
@@ -22006,7 +22009,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B359" t="s">
         <v>34</v>
@@ -22027,10 +22030,10 @@
         <v>41</v>
       </c>
       <c r="H359" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I359" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J359" t="s">
         <v>80</v>
@@ -22039,10 +22042,10 @@
         <v>80</v>
       </c>
       <c r="L359" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M359" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N359" t="s">
         <v>45</v>
@@ -22062,7 +22065,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B360" t="s">
         <v>34</v>
@@ -22083,10 +22086,10 @@
         <v>41</v>
       </c>
       <c r="H360" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I360" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J360" t="s">
         <v>63</v>
@@ -22095,10 +22098,10 @@
         <v>63</v>
       </c>
       <c r="L360" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M360" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N360" t="s">
         <v>45</v>
@@ -22118,7 +22121,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B361" t="s">
         <v>34</v>
@@ -22139,10 +22142,10 @@
         <v>41</v>
       </c>
       <c r="H361" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I361" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="J361" t="s">
         <v>91</v>
@@ -22151,10 +22154,10 @@
         <v>91</v>
       </c>
       <c r="L361" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M361" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N361" t="s">
         <v>45</v>
@@ -22174,7 +22177,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B362" t="s">
         <v>34</v>
@@ -22195,10 +22198,10 @@
         <v>41</v>
       </c>
       <c r="H362" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I362" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J362" t="s">
         <v>117</v>
@@ -22207,10 +22210,10 @@
         <v>117</v>
       </c>
       <c r="L362" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M362" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N362" t="s">
         <v>45</v>
@@ -22230,7 +22233,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B363" t="s">
         <v>34</v>
@@ -22251,10 +22254,10 @@
         <v>41</v>
       </c>
       <c r="H363" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I363" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J363" t="s">
         <v>90</v>
@@ -22263,10 +22266,10 @@
         <v>90</v>
       </c>
       <c r="L363" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M363" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N363" t="s">
         <v>45</v>
@@ -22286,7 +22289,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B364" t="s">
         <v>34</v>
@@ -22307,10 +22310,10 @@
         <v>41</v>
       </c>
       <c r="H364" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I364" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="J364" t="s">
         <v>104</v>
@@ -22319,10 +22322,10 @@
         <v>104</v>
       </c>
       <c r="L364" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M364" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N364" t="s">
         <v>45</v>
@@ -22342,7 +22345,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B365" t="s">
         <v>34</v>
@@ -22363,10 +22366,10 @@
         <v>41</v>
       </c>
       <c r="H365" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I365" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="J365" t="s">
         <v>117</v>
@@ -22375,10 +22378,10 @@
         <v>117</v>
       </c>
       <c r="L365" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M365" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N365" t="s">
         <v>45</v>
@@ -22398,7 +22401,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B366" t="s">
         <v>34</v>
@@ -22419,10 +22422,10 @@
         <v>41</v>
       </c>
       <c r="H366" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I366" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J366" t="s">
         <v>109</v>
@@ -22431,10 +22434,10 @@
         <v>109</v>
       </c>
       <c r="L366" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M366" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N366" t="s">
         <v>45</v>
@@ -22454,7 +22457,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B367" t="s">
         <v>34</v>
@@ -22475,10 +22478,10 @@
         <v>41</v>
       </c>
       <c r="H367" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I367" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J367" t="s">
         <v>99</v>
@@ -22487,10 +22490,10 @@
         <v>99</v>
       </c>
       <c r="L367" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M367" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N367" t="s">
         <v>45</v>
@@ -22510,7 +22513,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B368" t="s">
         <v>34</v>
@@ -22531,10 +22534,10 @@
         <v>41</v>
       </c>
       <c r="H368" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I368" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J368" t="s">
         <v>109</v>
@@ -22543,10 +22546,10 @@
         <v>109</v>
       </c>
       <c r="L368" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M368" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N368" t="s">
         <v>45</v>
@@ -22566,7 +22569,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B369" t="s">
         <v>34</v>
@@ -22587,10 +22590,10 @@
         <v>41</v>
       </c>
       <c r="H369" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I369" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J369" t="s">
         <v>91</v>
@@ -22599,10 +22602,10 @@
         <v>91</v>
       </c>
       <c r="L369" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M369" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N369" t="s">
         <v>45</v>
@@ -22622,7 +22625,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B370" t="s" s="1">
         <v>32</v>
@@ -22678,7 +22681,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B371" t="s" s="1">
         <v>32</v>
@@ -22734,7 +22737,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B372" t="s">
         <v>32</v>
@@ -22790,7 +22793,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>154</v>
@@ -22846,7 +22849,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B374" t="s">
         <v>154</v>
@@ -22902,13 +22905,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B375" t="s" s="1">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C375" t="s" s="1">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D375" t="s" s="1">
         <v>33</v>
@@ -22958,7 +22961,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B376" t="s" s="1">
         <v>174</v>
@@ -23014,7 +23017,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B377" t="s" s="1">
         <v>176</v>
@@ -23070,7 +23073,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B378" t="s">
         <v>176</v>
@@ -23126,7 +23129,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B379" t="s" s="1">
         <v>274</v>
@@ -23182,7 +23185,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B380" t="s">
         <v>274</v>
@@ -23238,13 +23241,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B381" t="s" s="1">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C381" t="s" s="1">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D381" t="s" s="1">
         <v>33</v>
@@ -23294,13 +23297,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B382" t="s" s="1">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C382" t="s" s="1">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D382" t="s" s="1">
         <v>33</v>
@@ -23350,7 +23353,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B383" t="s" s="1">
         <v>340</v>
@@ -23406,7 +23409,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>342</v>
@@ -23462,7 +23465,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B385" t="s">
         <v>342</v>
@@ -23518,7 +23521,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B386" t="s" s="1">
         <v>484</v>
@@ -23574,7 +23577,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B387" t="s">
         <v>486</v>
@@ -23630,7 +23633,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B388" t="s">
         <v>493</v>
@@ -23686,7 +23689,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B389" t="s">
         <v>500</v>
@@ -23742,7 +23745,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B390" t="s">
         <v>512</v>
@@ -23798,7 +23801,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B391" t="s" s="1">
         <v>531</v>
@@ -23854,7 +23857,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B392" t="s" s="1">
         <v>533</v>
@@ -23910,7 +23913,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B393" t="s">
         <v>164</v>
@@ -23966,7 +23969,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B394" t="s">
         <v>538</v>
@@ -24022,7 +24025,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B395" t="s">
         <v>585</v>
@@ -24078,7 +24081,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B396" t="s">
         <v>590</v>
@@ -24134,7 +24137,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B397" t="s">
         <v>594</v>
@@ -24190,7 +24193,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B398" t="s">
         <v>603</v>
@@ -24246,7 +24249,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B399" t="s" s="1">
         <v>610</v>
@@ -24302,7 +24305,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B400" t="s">
         <v>612</v>
@@ -24358,7 +24361,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B401" t="s">
         <v>619</v>
@@ -24414,13 +24417,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B402" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C402" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D402" t="s">
         <v>33</v>
@@ -24470,13 +24473,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B403" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C403" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D403" t="s">
         <v>33</v>
@@ -24526,13 +24529,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B404" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C404" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
@@ -24582,13 +24585,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B405" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C405" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D405" t="s">
         <v>33</v>
@@ -24638,13 +24641,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B406" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C406" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D406" t="s">
         <v>33</v>
@@ -24694,13 +24697,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B407" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C407" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D407" t="s">
         <v>33</v>
@@ -24750,13 +24753,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B408" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C408" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D408" t="s">
         <v>33</v>
@@ -24806,13 +24809,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B409" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C409" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D409" t="s">
         <v>33</v>
@@ -24862,13 +24865,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="1">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B410" t="s" s="1">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C410" t="s" s="1">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D410" t="s" s="1">
         <v>33</v>
@@ -24918,13 +24921,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B411" t="s" s="1">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C411" t="s" s="1">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D411" t="s" s="1">
         <v>33</v>
@@ -24974,13 +24977,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B412" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C412" t="s" s="1">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D412" t="s" s="1">
         <v>33</v>
@@ -25030,13 +25033,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B413" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C413" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D413" t="s">
         <v>33</v>
@@ -25086,13 +25089,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="1">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B414" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C414" t="s" s="1">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D414" t="s" s="1">
         <v>33</v>
@@ -25142,13 +25145,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B415" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C415" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D415" t="s">
         <v>33</v>
@@ -25198,13 +25201,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="1">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B416" t="s" s="1">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C416" t="s" s="1">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D416" t="s" s="1">
         <v>33</v>
@@ -25254,13 +25257,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="1">
+        <v>821</v>
+      </c>
+      <c r="B417" t="s" s="1">
         <v>820</v>
       </c>
-      <c r="B417" t="s" s="1">
-        <v>819</v>
-      </c>
       <c r="C417" t="s" s="1">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D417" t="s" s="1">
         <v>33</v>
@@ -25310,13 +25313,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="1">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B418" t="s" s="1">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C418" t="s" s="1">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D418" t="s" s="1">
         <v>33</v>
@@ -25366,7 +25369,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="1">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B419" t="s" s="1">
         <v>32</v>
@@ -25422,13 +25425,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="1">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B420" t="s" s="1">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C420" t="s" s="1">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D420" t="s" s="1">
         <v>33</v>
@@ -25478,7 +25481,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B421" t="s">
         <v>154</v>
@@ -25534,7 +25537,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B422" t="s">
         <v>174</v>
@@ -25590,7 +25593,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B423" t="s">
         <v>340</v>
@@ -25646,13 +25649,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B424" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C424" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D424" t="s">
         <v>33</v>
@@ -25702,13 +25705,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="1">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B425" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C425" t="s" s="1">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D425" t="s" s="1">
         <v>33</v>
@@ -25758,7 +25761,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B426" t="s">
         <v>531</v>
@@ -25814,13 +25817,13 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B427" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C427" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D427" t="s">
         <v>33</v>
@@ -25870,7 +25873,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B428" t="s">
         <v>32</v>
@@ -25926,13 +25929,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B429" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C429" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D429" t="s">
         <v>33</v>
@@ -25982,13 +25985,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
+        <v>837</v>
+      </c>
+      <c r="B430" t="s">
         <v>836</v>
       </c>
-      <c r="B430" t="s">
-        <v>835</v>
-      </c>
       <c r="C430" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D430" t="s">
         <v>33</v>
@@ -26038,7 +26041,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B431" t="s">
         <v>176</v>
@@ -26094,7 +26097,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B432" t="s">
         <v>342</v>
@@ -26150,7 +26153,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B433" t="s">
         <v>533</v>
@@ -26206,7 +26209,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B434" t="s">
         <v>612</v>
@@ -26262,7 +26265,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B435" t="s">
         <v>154</v>
@@ -26318,13 +26321,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B436" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C436" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D436" t="s">
         <v>33</v>
@@ -26374,13 +26377,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B437" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C437" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D437" t="s">
         <v>33</v>
@@ -26430,13 +26433,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B438" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C438" t="s" s="1">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D438" t="s" s="1">
         <v>33</v>
@@ -26486,16 +26489,16 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="1">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B439" t="s" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C439" t="s" s="1">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D439" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E439" t="s" s="1">
         <v>34</v>
@@ -26542,16 +26545,16 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="1">
+        <v>850</v>
+      </c>
+      <c r="B440" t="s" s="1">
+        <v>851</v>
+      </c>
+      <c r="C440" t="s" s="1">
+        <v>851</v>
+      </c>
+      <c r="D440" t="s" s="1">
         <v>849</v>
-      </c>
-      <c r="B440" t="s" s="1">
-        <v>850</v>
-      </c>
-      <c r="C440" t="s" s="1">
-        <v>850</v>
-      </c>
-      <c r="D440" t="s" s="1">
-        <v>848</v>
       </c>
       <c r="E440" t="s" s="1">
         <v>34</v>
@@ -26598,16 +26601,16 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="1">
+        <v>852</v>
+      </c>
+      <c r="B441" t="s" s="1">
         <v>851</v>
       </c>
-      <c r="B441" t="s" s="1">
-        <v>850</v>
-      </c>
       <c r="C441" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D441" t="s" s="1">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E441" t="s" s="1">
         <v>34</v>
@@ -26654,13 +26657,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B442" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C442" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D442" t="s">
         <v>33</v>
@@ -26710,19 +26713,19 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
+        <v>855</v>
+      </c>
+      <c r="B443" t="s">
         <v>854</v>
       </c>
-      <c r="B443" t="s">
-        <v>853</v>
-      </c>
       <c r="C443" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D443" t="s">
         <v>33</v>
       </c>
       <c r="E443" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F443" t="s">
         <v>48</v>
@@ -26743,10 +26746,10 @@
         <v>172</v>
       </c>
       <c r="L443" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M443" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N443" t="s">
         <v>45</v>
@@ -26766,7 +26769,7 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B444" t="s">
         <v>34</v>
@@ -26778,7 +26781,7 @@
         <v>34</v>
       </c>
       <c r="E444" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F444" t="s">
         <v>48</v>
@@ -26799,10 +26802,10 @@
         <v>172</v>
       </c>
       <c r="L444" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M444" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N444" t="s">
         <v>45</v>
@@ -26822,7 +26825,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B445" t="s">
         <v>34</v>
@@ -26834,7 +26837,7 @@
         <v>34</v>
       </c>
       <c r="E445" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F445" t="s">
         <v>244</v>
@@ -26846,7 +26849,7 @@
         <v>49</v>
       </c>
       <c r="I445" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J445" t="s">
         <v>121</v>
@@ -26855,10 +26858,10 @@
         <v>121</v>
       </c>
       <c r="L445" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M445" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N445" t="s">
         <v>45</v>
@@ -26867,7 +26870,7 @@
         <v>54</v>
       </c>
       <c r="P445" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="Q445" t="s">
         <v>45</v>
@@ -26878,7 +26881,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B446" t="s">
         <v>34</v>
@@ -26890,7 +26893,7 @@
         <v>34</v>
       </c>
       <c r="E446" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F446" t="s">
         <v>48</v>
@@ -26902,7 +26905,7 @@
         <v>49</v>
       </c>
       <c r="I446" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J446" t="s">
         <v>63</v>
@@ -26911,10 +26914,10 @@
         <v>252</v>
       </c>
       <c r="L446" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M446" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N446" t="s">
         <v>45</v>
@@ -26923,7 +26926,7 @@
         <v>54</v>
       </c>
       <c r="P446" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="Q446" t="s">
         <v>45</v>
@@ -26934,7 +26937,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B447" t="s">
         <v>34</v>
@@ -26946,7 +26949,7 @@
         <v>34</v>
       </c>
       <c r="E447" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F447" t="s">
         <v>48</v>
@@ -26955,10 +26958,10 @@
         <v>41</v>
       </c>
       <c r="H447" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I447" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="J447" t="s">
         <v>172</v>
@@ -26967,10 +26970,10 @@
         <v>252</v>
       </c>
       <c r="L447" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M447" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N447" t="s">
         <v>45</v>
@@ -26979,7 +26982,7 @@
         <v>54</v>
       </c>
       <c r="P447" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="Q447" t="s">
         <v>45</v>
@@ -26990,7 +26993,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B448" t="s">
         <v>34</v>
@@ -27002,7 +27005,7 @@
         <v>34</v>
       </c>
       <c r="E448" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F448" t="s">
         <v>244</v>
@@ -27011,22 +27014,22 @@
         <v>41</v>
       </c>
       <c r="H448" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I448" t="s">
         <v>116</v>
       </c>
       <c r="J448" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="K448" t="s">
         <v>150</v>
       </c>
       <c r="L448" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M448" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="N448" t="s">
         <v>45</v>

--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -1458,18 +1458,18 @@
     <t>DSR set26/1</t>
   </si>
   <si>
+    <t>Rosangela Pacheco</t>
+  </si>
+  <si>
+    <t>R$  1.046,14</t>
+  </si>
+  <si>
+    <t>07/09/26</t>
+  </si>
+  <si>
     <t>R$  592,53</t>
   </si>
   <si>
-    <t>07/09/26</t>
-  </si>
-  <si>
-    <t>Rosangela Pacheco</t>
-  </si>
-  <si>
-    <t>R$  1.046,14</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1539,21 +1539,21 @@
     <t>Brindes clientes</t>
   </si>
   <si>
+    <t>66/3</t>
+  </si>
+  <si>
+    <t>R$  159,96</t>
+  </si>
+  <si>
+    <t>Licoretto brinde clientes</t>
+  </si>
+  <si>
     <t>766/1</t>
   </si>
   <si>
     <t>vinho para clientes 1/3</t>
   </si>
   <si>
-    <t>66/3</t>
-  </si>
-  <si>
-    <t>R$  159,96</t>
-  </si>
-  <si>
-    <t>Licoretto brinde clientes</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1563,9 +1563,33 @@
     <t>4.03.03.09.04 Marketing - mídia veículos de comunicação (CV)</t>
   </si>
   <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>12/9</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1578,30 +1602,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/7</t>
   </si>
   <si>
@@ -1815,6 +1815,12 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT set 26/1</t>
+  </si>
+  <si>
+    <t>R$  413,84</t>
+  </si>
+  <si>
     <t>VT set26/1</t>
   </si>
   <si>
@@ -1824,12 +1830,6 @@
     <t>28/08/26</t>
   </si>
   <si>
-    <t>VT set 26/1</t>
-  </si>
-  <si>
-    <t>R$  413,84</t>
-  </si>
-  <si>
     <t>4.04.01.06 Assistência médica e hospitalar</t>
   </si>
   <si>
@@ -1981,30 +1981,6 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
-  </si>
-  <si>
-    <t>761/1</t>
-  </si>
-  <si>
-    <t>R$  31,70</t>
-  </si>
-  <si>
-    <t>02/10/26</t>
-  </si>
-  <si>
-    <t>águas</t>
-  </si>
-  <si>
-    <t>738/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  92,00</t>
-  </si>
-  <si>
-    <t>Bolo Rosangela</t>
   </si>
   <si>
     <t>768/1</t>
@@ -2022,6 +1998,30 @@
 </t>
   </si>
   <si>
+    <t>738/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  92,00</t>
+  </si>
+  <si>
+    <t>Bolo Rosangela</t>
+  </si>
+  <si>
+    <t>761/1</t>
+  </si>
+  <si>
+    <t>R$  31,70</t>
+  </si>
+  <si>
+    <t>02/10/26</t>
+  </si>
+  <si>
+    <t>águas</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2064,9 +2064,15 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>767/1</t>
+  </si>
+  <si>
     <t>Promob</t>
   </si>
   <si>
+    <t>R$  4.516,62</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
@@ -2103,12 +2109,6 @@
     <t>Promob 2026/3</t>
   </si>
   <si>
-    <t>767/1</t>
-  </si>
-  <si>
-    <t>R$  4.516,62</t>
-  </si>
-  <si>
     <t>3/8</t>
   </si>
   <si>
@@ -2121,6 +2121,18 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
+    <t>61/5</t>
+  </si>
+  <si>
+    <t>Pipefy</t>
+  </si>
+  <si>
+    <t>R$  97,37</t>
+  </si>
+  <si>
+    <t>21/05/26</t>
+  </si>
+  <si>
     <t>D4 sign</t>
   </si>
   <si>
@@ -2128,18 +2140,6 @@
   </si>
   <si>
     <t>D4 sign 2026</t>
-  </si>
-  <si>
-    <t>61/5</t>
-  </si>
-  <si>
-    <t>Pipefy</t>
-  </si>
-  <si>
-    <t>R$  97,37</t>
-  </si>
-  <si>
-    <t>21/05/26</t>
   </si>
   <si>
     <t>64/4</t>
@@ -15770,16 +15770,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
-        <v>351</v>
+        <v>481</v>
       </c>
       <c r="I247" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J247" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K247" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -15794,7 +15794,7 @@
         <v>54</v>
       </c>
       <c r="P247" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -15826,16 +15826,16 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>483</v>
+        <v>351</v>
       </c>
       <c r="I248" t="s">
         <v>484</v>
       </c>
       <c r="J248" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K248" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16041,10 +16041,10 @@
         <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F252" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
@@ -16056,10 +16056,10 @@
         <v>492</v>
       </c>
       <c r="J252" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="K252" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16071,13 +16071,13 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P252" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q252" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R252" t="s">
         <v>34</v>
@@ -16097,7 +16097,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="F253" t="s">
         <v>170</v>
@@ -16112,10 +16112,10 @@
         <v>492</v>
       </c>
       <c r="J253" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="K253" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16127,7 +16127,7 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="P253" t="s">
         <v>492</v>
@@ -16153,10 +16153,10 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F254" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
@@ -16168,10 +16168,10 @@
         <v>492</v>
       </c>
       <c r="J254" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="K254" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16183,7 +16183,7 @@
         <v>45</v>
       </c>
       <c r="O254" t="s">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="P254" t="s">
         <v>492</v>
@@ -16209,10 +16209,10 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="F255" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
@@ -16224,10 +16224,10 @@
         <v>492</v>
       </c>
       <c r="J255" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K255" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16239,13 +16239,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="P255" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q255" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16265,7 +16265,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="F256" t="s">
         <v>196</v>
@@ -16280,10 +16280,10 @@
         <v>492</v>
       </c>
       <c r="J256" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="K256" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16295,7 +16295,7 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="P256" t="s">
         <v>492</v>
@@ -16321,10 +16321,10 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="F257" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="G257" t="s">
         <v>41</v>
@@ -16336,10 +16336,10 @@
         <v>492</v>
       </c>
       <c r="J257" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="K257" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L257" t="s">
         <v>34</v>
@@ -16351,13 +16351,13 @@
         <v>45</v>
       </c>
       <c r="O257" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="P257" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q257" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R257" t="s">
         <v>34</v>
@@ -16377,10 +16377,10 @@
         <v>34</v>
       </c>
       <c r="E258" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="F258" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
@@ -16392,10 +16392,10 @@
         <v>492</v>
       </c>
       <c r="J258" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="K258" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="L258" t="s">
         <v>34</v>
@@ -16407,7 +16407,7 @@
         <v>45</v>
       </c>
       <c r="O258" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="P258" t="s">
         <v>492</v>
@@ -16433,10 +16433,10 @@
         <v>34</v>
       </c>
       <c r="E259" t="s">
-        <v>242</v>
+        <v>370</v>
       </c>
       <c r="F259" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -16448,10 +16448,10 @@
         <v>492</v>
       </c>
       <c r="J259" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K259" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L259" t="s">
         <v>34</v>
@@ -16463,13 +16463,13 @@
         <v>45</v>
       </c>
       <c r="O259" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="P259" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q259" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R259" t="s">
         <v>34</v>
@@ -16489,7 +16489,7 @@
         <v>34</v>
       </c>
       <c r="E260" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="F260" t="s">
         <v>159</v>
@@ -16504,10 +16504,10 @@
         <v>492</v>
       </c>
       <c r="J260" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="K260" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L260" t="s">
         <v>34</v>
@@ -16545,7 +16545,7 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F261" t="s">
         <v>159</v>
@@ -16560,10 +16560,10 @@
         <v>492</v>
       </c>
       <c r="J261" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="K261" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="L261" t="s">
         <v>34</v>
@@ -16601,7 +16601,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F262" t="s">
         <v>159</v>
@@ -16616,10 +16616,10 @@
         <v>492</v>
       </c>
       <c r="J262" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="K262" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="L262" t="s">
         <v>34</v>
@@ -16657,10 +16657,10 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>213</v>
+        <v>370</v>
       </c>
       <c r="F263" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
@@ -16669,13 +16669,13 @@
         <v>491</v>
       </c>
       <c r="I263" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J263" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="K263" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="L263" t="s">
         <v>34</v>
@@ -16687,13 +16687,13 @@
         <v>45</v>
       </c>
       <c r="O263" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="P263" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q263" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R263" t="s">
         <v>34</v>
@@ -16713,10 +16713,10 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="F264" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G264" t="s">
         <v>41</v>
@@ -16728,10 +16728,10 @@
         <v>492</v>
       </c>
       <c r="J264" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="K264" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -16743,13 +16743,13 @@
         <v>45</v>
       </c>
       <c r="O264" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="P264" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q264" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R264" t="s">
         <v>34</v>
@@ -16769,10 +16769,10 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>370</v>
+        <v>233</v>
       </c>
       <c r="F265" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="G265" t="s">
         <v>41</v>
@@ -16781,13 +16781,13 @@
         <v>491</v>
       </c>
       <c r="I265" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J265" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K265" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -16825,7 +16825,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F266" t="s">
         <v>159</v>
@@ -16840,10 +16840,10 @@
         <v>492</v>
       </c>
       <c r="J266" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="K266" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -16881,7 +16881,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F267" t="s">
         <v>159</v>
@@ -16896,10 +16896,10 @@
         <v>492</v>
       </c>
       <c r="J267" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="K267" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17164,7 +17164,7 @@
         <v>508</v>
       </c>
       <c r="F272" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
@@ -17173,16 +17173,16 @@
         <v>505</v>
       </c>
       <c r="I272" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J272" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K272" t="s">
-        <v>482</v>
+        <v>253</v>
       </c>
       <c r="L272" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M272" t="s">
         <v>503</v>
@@ -17194,7 +17194,7 @@
         <v>54</v>
       </c>
       <c r="P272" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17217,10 +17217,10 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F273" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17229,13 +17229,13 @@
         <v>505</v>
       </c>
       <c r="I273" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="J273" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K273" t="s">
-        <v>253</v>
+        <v>483</v>
       </c>
       <c r="L273" t="s">
         <v>512</v>
@@ -17250,7 +17250,7 @@
         <v>54</v>
       </c>
       <c r="P273" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17329,7 +17329,7 @@
         <v>33</v>
       </c>
       <c r="E275" t="s">
-        <v>516</v>
+        <v>145</v>
       </c>
       <c r="F275" t="s">
         <v>170</v>
@@ -17338,19 +17338,19 @@
         <v>41</v>
       </c>
       <c r="H275" t="s">
+        <v>516</v>
+      </c>
+      <c r="I275" t="s">
         <v>517</v>
       </c>
-      <c r="I275" t="s">
+      <c r="J275" t="s">
         <v>518</v>
       </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
+        <v>150</v>
+      </c>
+      <c r="L275" t="s">
         <v>519</v>
-      </c>
-      <c r="K275" t="s">
-        <v>272</v>
-      </c>
-      <c r="L275" t="s">
-        <v>520</v>
       </c>
       <c r="M275" t="s">
         <v>515</v>
@@ -17362,7 +17362,7 @@
         <v>54</v>
       </c>
       <c r="P275" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q275" t="s">
         <v>45</v>
@@ -17385,7 +17385,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F276" t="s">
         <v>170</v>
@@ -17441,7 +17441,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>145</v>
+        <v>520</v>
       </c>
       <c r="F277" t="s">
         <v>170</v>
@@ -17459,7 +17459,7 @@
         <v>527</v>
       </c>
       <c r="K277" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="L277" t="s">
         <v>528</v>
@@ -17721,7 +17721,7 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F282" t="s">
         <v>170</v>
@@ -17736,7 +17736,7 @@
         <v>166</v>
       </c>
       <c r="J282" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K282" t="s">
         <v>253</v>
@@ -17889,7 +17889,7 @@
         <v>33</v>
       </c>
       <c r="E285" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F285" t="s">
         <v>170</v>
@@ -17904,7 +17904,7 @@
         <v>546</v>
       </c>
       <c r="J285" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K285" t="s">
         <v>253</v>
@@ -17945,7 +17945,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F286" t="s">
         <v>170</v>
@@ -17960,7 +17960,7 @@
         <v>166</v>
       </c>
       <c r="J286" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K286" t="s">
         <v>253</v>
@@ -18057,7 +18057,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F288" t="s">
         <v>170</v>
@@ -18113,7 +18113,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F289" t="s">
         <v>170</v>
@@ -18128,7 +18128,7 @@
         <v>555</v>
       </c>
       <c r="J289" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K289" t="s">
         <v>253</v>
@@ -18178,16 +18178,16 @@
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I290" t="s">
         <v>558</v>
       </c>
       <c r="J290" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K290" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L290" t="s">
         <v>559</v>
@@ -18281,7 +18281,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F292" t="s">
         <v>170</v>
@@ -18296,7 +18296,7 @@
         <v>562</v>
       </c>
       <c r="J292" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K292" t="s">
         <v>253</v>
@@ -18337,7 +18337,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F293" t="s">
         <v>170</v>
@@ -18352,7 +18352,7 @@
         <v>565</v>
       </c>
       <c r="J293" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K293" t="s">
         <v>253</v>
@@ -18393,7 +18393,7 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F294" t="s">
         <v>170</v>
@@ -18408,7 +18408,7 @@
         <v>568</v>
       </c>
       <c r="J294" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K294" t="s">
         <v>253</v>
@@ -18520,10 +18520,10 @@
         <v>573</v>
       </c>
       <c r="J296" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K296" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L296" t="s">
         <v>34</v>
@@ -19242,16 +19242,16 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>351</v>
+        <v>481</v>
       </c>
       <c r="I309" t="s">
         <v>601</v>
       </c>
       <c r="J309" t="s">
-        <v>602</v>
+        <v>44</v>
       </c>
       <c r="K309" t="s">
-        <v>482</v>
+        <v>44</v>
       </c>
       <c r="L309" t="s">
         <v>34</v>
@@ -19289,7 +19289,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F310" t="s">
         <v>196</v>
@@ -19298,16 +19298,16 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
+        <v>351</v>
+      </c>
+      <c r="I310" t="s">
+        <v>603</v>
+      </c>
+      <c r="J310" t="s">
+        <v>604</v>
+      </c>
+      <c r="K310" t="s">
         <v>483</v>
-      </c>
-      <c r="I310" t="s">
-        <v>604</v>
-      </c>
-      <c r="J310" t="s">
-        <v>44</v>
-      </c>
-      <c r="K310" t="s">
-        <v>44</v>
       </c>
       <c r="L310" t="s">
         <v>34</v>
@@ -19322,7 +19322,7 @@
         <v>54</v>
       </c>
       <c r="P310" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q310" t="s">
         <v>45</v>
@@ -19584,7 +19584,7 @@
         <v>619</v>
       </c>
       <c r="J315" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K315" t="s">
         <v>272</v>
@@ -19793,7 +19793,7 @@
         <v>33</v>
       </c>
       <c r="E319" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F319" t="s">
         <v>170</v>
@@ -19808,7 +19808,7 @@
         <v>633</v>
       </c>
       <c r="J319" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K319" t="s">
         <v>253</v>
@@ -19961,7 +19961,7 @@
         <v>33</v>
       </c>
       <c r="E322" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F322" t="s">
         <v>170</v>
@@ -19976,7 +19976,7 @@
         <v>645</v>
       </c>
       <c r="J322" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K322" t="s">
         <v>275</v>
@@ -20088,7 +20088,7 @@
         <v>651</v>
       </c>
       <c r="J324" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K324" t="s">
         <v>272</v>
@@ -20194,16 +20194,16 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
-        <v>351</v>
+        <v>657</v>
       </c>
       <c r="I326" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J326" t="s">
-        <v>658</v>
+        <v>265</v>
       </c>
       <c r="K326" t="s">
-        <v>63</v>
+        <v>483</v>
       </c>
       <c r="L326" t="s">
         <v>659</v>
@@ -20218,7 +20218,7 @@
         <v>54</v>
       </c>
       <c r="P326" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20306,16 +20306,16 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
+        <v>351</v>
+      </c>
+      <c r="I328" t="s">
         <v>665</v>
       </c>
-      <c r="I328" t="s">
+      <c r="J328" t="s">
         <v>666</v>
       </c>
-      <c r="J328" t="s">
-        <v>265</v>
-      </c>
       <c r="K328" t="s">
-        <v>482</v>
+        <v>63</v>
       </c>
       <c r="L328" t="s">
         <v>667</v>
@@ -20330,7 +20330,7 @@
         <v>54</v>
       </c>
       <c r="P328" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="Q328" t="s">
         <v>45</v>
@@ -20409,7 +20409,7 @@
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F330" t="s">
         <v>170</v>
@@ -20424,7 +20424,7 @@
         <v>673</v>
       </c>
       <c r="J330" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K330" t="s">
         <v>253</v>
@@ -20577,28 +20577,28 @@
         <v>33</v>
       </c>
       <c r="E333" t="s">
-        <v>516</v>
+        <v>682</v>
       </c>
       <c r="F333" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G333" t="s">
         <v>41</v>
       </c>
       <c r="H333" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I333" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="J333" t="s">
-        <v>523</v>
+        <v>265</v>
       </c>
       <c r="K333" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L333" t="s">
-        <v>684</v>
+        <v>34</v>
       </c>
       <c r="M333" t="s">
         <v>681</v>
@@ -20610,7 +20610,7 @@
         <v>54</v>
       </c>
       <c r="P333" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Q333" t="s">
         <v>45</v>
@@ -20633,7 +20633,7 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>685</v>
+        <v>520</v>
       </c>
       <c r="F334" t="s">
         <v>170</v>
@@ -20642,19 +20642,19 @@
         <v>41</v>
       </c>
       <c r="H334" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I334" t="s">
+        <v>685</v>
+      </c>
+      <c r="J334" t="s">
+        <v>523</v>
+      </c>
+      <c r="K334" t="s">
+        <v>44</v>
+      </c>
+      <c r="L334" t="s">
         <v>686</v>
-      </c>
-      <c r="J334" t="s">
-        <v>687</v>
-      </c>
-      <c r="K334" t="s">
-        <v>253</v>
-      </c>
-      <c r="L334" t="s">
-        <v>688</v>
       </c>
       <c r="M334" t="s">
         <v>681</v>
@@ -20666,7 +20666,7 @@
         <v>54</v>
       </c>
       <c r="P334" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q334" t="s">
         <v>45</v>
@@ -20689,7 +20689,7 @@
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F335" t="s">
         <v>170</v>
@@ -20698,19 +20698,19 @@
         <v>41</v>
       </c>
       <c r="H335" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I335" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J335" t="s">
-        <v>63</v>
+        <v>689</v>
       </c>
       <c r="K335" t="s">
         <v>253</v>
       </c>
       <c r="L335" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M335" t="s">
         <v>681</v>
@@ -20722,7 +20722,7 @@
         <v>54</v>
       </c>
       <c r="P335" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="Q335" t="s">
         <v>45</v>
@@ -20745,7 +20745,7 @@
         <v>34</v>
       </c>
       <c r="E336" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F336" t="s">
         <v>170</v>
@@ -20754,19 +20754,19 @@
         <v>41</v>
       </c>
       <c r="H336" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I336" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J336" t="s">
-        <v>687</v>
+        <v>63</v>
       </c>
       <c r="K336" t="s">
         <v>253</v>
       </c>
       <c r="L336" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="M336" t="s">
         <v>681</v>
@@ -20778,7 +20778,7 @@
         <v>54</v>
       </c>
       <c r="P336" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="Q336" t="s">
         <v>45</v>
@@ -20801,28 +20801,28 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
+        <v>694</v>
+      </c>
+      <c r="F337" t="s">
+        <v>170</v>
+      </c>
+      <c r="G337" t="s">
+        <v>41</v>
+      </c>
+      <c r="H337" t="s">
+        <v>683</v>
+      </c>
+      <c r="I337" t="s">
         <v>695</v>
       </c>
-      <c r="F337" t="s">
-        <v>196</v>
-      </c>
-      <c r="G337" t="s">
-        <v>41</v>
-      </c>
-      <c r="H337" t="s">
-        <v>682</v>
-      </c>
-      <c r="I337" t="s">
+      <c r="J337" t="s">
+        <v>689</v>
+      </c>
+      <c r="K337" t="s">
+        <v>253</v>
+      </c>
+      <c r="L337" t="s">
         <v>696</v>
-      </c>
-      <c r="J337" t="s">
-        <v>265</v>
-      </c>
-      <c r="K337" t="s">
-        <v>79</v>
-      </c>
-      <c r="L337" t="s">
-        <v>34</v>
       </c>
       <c r="M337" t="s">
         <v>681</v>
@@ -20834,7 +20834,7 @@
         <v>54</v>
       </c>
       <c r="P337" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="Q337" t="s">
         <v>45</v>
@@ -20866,7 +20866,7 @@
         <v>41</v>
       </c>
       <c r="H338" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I338" t="s">
         <v>698</v>
@@ -20913,7 +20913,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>516</v>
+        <v>701</v>
       </c>
       <c r="F339" t="s">
         <v>170</v>
@@ -20922,19 +20922,19 @@
         <v>41</v>
       </c>
       <c r="H339" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I339" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J339" t="s">
-        <v>523</v>
+        <v>704</v>
       </c>
       <c r="K339" t="s">
         <v>253</v>
       </c>
       <c r="L339" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M339" t="s">
         <v>681</v>
@@ -20946,7 +20946,7 @@
         <v>54</v>
       </c>
       <c r="P339" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q339" t="s">
         <v>45</v>
@@ -20969,7 +20969,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>704</v>
+        <v>520</v>
       </c>
       <c r="F340" t="s">
         <v>170</v>
@@ -20984,13 +20984,13 @@
         <v>706</v>
       </c>
       <c r="J340" t="s">
-        <v>707</v>
+        <v>523</v>
       </c>
       <c r="K340" t="s">
         <v>253</v>
       </c>
       <c r="L340" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M340" t="s">
         <v>681</v>
@@ -21137,7 +21137,7 @@
         <v>33</v>
       </c>
       <c r="E343" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F343" t="s">
         <v>170</v>
@@ -21152,7 +21152,7 @@
         <v>716</v>
       </c>
       <c r="J343" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K343" t="s">
         <v>253</v>
@@ -21376,7 +21376,7 @@
         <v>735</v>
       </c>
       <c r="J347" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="K347" t="s">
         <v>150</v>
@@ -21417,7 +21417,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F348" t="s">
         <v>170</v>
@@ -21432,7 +21432,7 @@
         <v>737</v>
       </c>
       <c r="J348" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="K348" t="s">
         <v>253</v>
@@ -21715,7 +21715,7 @@
         <v>265</v>
       </c>
       <c r="K353" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L353" t="s">
         <v>34</v>

--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -762,31 +762,76 @@
     <t>R$ 1.962,58</t>
   </si>
   <si>
+    <t>765/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  1.020,04</t>
+  </si>
+  <si>
+    <t>13/10/26</t>
+  </si>
+  <si>
+    <t>71/1</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>R$  51,55</t>
+  </si>
+  <si>
+    <t>11/09/26</t>
+  </si>
+  <si>
+    <t>05/09/26</t>
+  </si>
+  <si>
+    <t>fita led Abrafoton</t>
+  </si>
+  <si>
+    <t>759/1</t>
+  </si>
+  <si>
+    <t>R$  216,50</t>
+  </si>
+  <si>
+    <t>05/10/26</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>757/1</t>
+  </si>
+  <si>
+    <t>R$  242,24</t>
+  </si>
+  <si>
+    <t>01/09/26</t>
+  </si>
+  <si>
     <t>72/1</t>
   </si>
   <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
     <t>R$  56,24</t>
   </si>
   <si>
-    <t>11/09/26</t>
-  </si>
-  <si>
-    <t>05/09/26</t>
-  </si>
-  <si>
     <t>Perfil Led Abrafoton</t>
   </si>
   <si>
-    <t>71/1</t>
-  </si>
-  <si>
-    <t>R$  51,55</t>
-  </si>
-  <si>
-    <t>fita led Abrafoton</t>
+    <t>737/1</t>
+  </si>
+  <si>
+    <t>R$  261,51</t>
+  </si>
+  <si>
+    <t>02/09/26</t>
+  </si>
+  <si>
+    <t>Estoque</t>
   </si>
   <si>
     <t>67/3</t>
@@ -801,51 +846,6 @@
     <t>Grapa</t>
   </si>
   <si>
-    <t>759/1</t>
-  </si>
-  <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
-    <t>R$  216,50</t>
-  </si>
-  <si>
-    <t>05/10/26</t>
-  </si>
-  <si>
-    <t>estoque</t>
-  </si>
-  <si>
-    <t>765/1</t>
-  </si>
-  <si>
-    <t>R$  1.020,04</t>
-  </si>
-  <si>
-    <t>13/10/26</t>
-  </si>
-  <si>
-    <t>757/1</t>
-  </si>
-  <si>
-    <t>R$  242,24</t>
-  </si>
-  <si>
-    <t>01/09/26</t>
-  </si>
-  <si>
-    <t>737/1</t>
-  </si>
-  <si>
-    <t>R$  261,51</t>
-  </si>
-  <si>
-    <t>02/09/26</t>
-  </si>
-  <si>
-    <t>Estoque</t>
-  </si>
-  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1068,72 +1068,72 @@
     <t>4.03.01.02.01.01 Comissões gerência de vendas</t>
   </si>
   <si>
+    <t>PPC</t>
+  </si>
+  <si>
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
+    <t>R$  626,41</t>
+  </si>
+  <si>
+    <t>R$  78,29</t>
+  </si>
+  <si>
+    <t>99401/1</t>
+  </si>
+  <si>
+    <t>R$  3,60</t>
+  </si>
+  <si>
     <t>R$  455,30</t>
   </si>
   <si>
+    <t>R$  746,53</t>
+  </si>
+  <si>
+    <t>R$  114,29</t>
+  </si>
+  <si>
+    <t>102501JULIOCP</t>
+  </si>
+  <si>
+    <t>R$  579,21</t>
+  </si>
+  <si>
+    <t>R$  278,06</t>
+  </si>
+  <si>
+    <t>R$  1.059,01</t>
+  </si>
+  <si>
+    <t>R$  417,61</t>
+  </si>
+  <si>
+    <t>R$  855,79</t>
+  </si>
+  <si>
+    <t>R$  505,49</t>
+  </si>
+  <si>
+    <t>100301TatianaWK</t>
+  </si>
+  <si>
+    <t>R$  288,85</t>
+  </si>
+  <si>
+    <t>R$  175,77</t>
+  </si>
+  <si>
+    <t>R$  714,34</t>
+  </si>
+  <si>
     <t>R$  52,19</t>
   </si>
   <si>
     <t>56101TadeuTM</t>
   </si>
   <si>
-    <t>R$  114,29</t>
-  </si>
-  <si>
-    <t>102501JULIOCP</t>
-  </si>
-  <si>
-    <t>R$  579,21</t>
-  </si>
-  <si>
-    <t>R$  278,06</t>
-  </si>
-  <si>
-    <t>R$  1.059,01</t>
-  </si>
-  <si>
-    <t>R$  417,61</t>
-  </si>
-  <si>
-    <t>R$  855,79</t>
-  </si>
-  <si>
-    <t>R$  505,49</t>
-  </si>
-  <si>
-    <t>100301TatianaWK</t>
-  </si>
-  <si>
-    <t>R$  288,85</t>
-  </si>
-  <si>
-    <t>R$  175,77</t>
-  </si>
-  <si>
-    <t>R$  714,34</t>
-  </si>
-  <si>
-    <t>PPC</t>
-  </si>
-  <si>
-    <t>R$  626,41</t>
-  </si>
-  <si>
-    <t>R$  78,29</t>
-  </si>
-  <si>
-    <t>99401/1</t>
-  </si>
-  <si>
-    <t>R$  3,60</t>
-  </si>
-  <si>
-    <t>R$  746,53</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1287,114 +1287,114 @@
     <t>R$ 14.181,19</t>
   </si>
   <si>
+    <t>R$  579,19</t>
+  </si>
+  <si>
+    <t>99401/2</t>
+  </si>
+  <si>
+    <t>R$  714,32</t>
+  </si>
+  <si>
+    <t>R$  746,58</t>
+  </si>
+  <si>
+    <t>R$  455,29</t>
+  </si>
+  <si>
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
     <t>R$  1.059,03</t>
   </si>
   <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  114,28</t>
+  </si>
+  <si>
+    <t>87601/1</t>
+  </si>
+  <si>
     <t>Rubens Felipe de Siqueira Costa</t>
   </si>
   <si>
+    <t>R$  620,43</t>
+  </si>
+  <si>
+    <t>87601CleitonS</t>
+  </si>
+  <si>
+    <t>87301/1</t>
+  </si>
+  <si>
+    <t>R$  469,36</t>
+  </si>
+  <si>
+    <t>87301PatriciaSS</t>
+  </si>
+  <si>
+    <t>92001/1</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>R$  346,86</t>
+  </si>
+  <si>
+    <t>92001LUCIANALS</t>
+  </si>
+  <si>
+    <t>56901/1</t>
+  </si>
+  <si>
+    <t>R$  170,33</t>
+  </si>
+  <si>
+    <t>56901BIANCARMS</t>
+  </si>
+  <si>
+    <t>83201/1</t>
+  </si>
+  <si>
+    <t>R$  4.535,18</t>
+  </si>
+  <si>
+    <t>83201ElaineMH</t>
+  </si>
+  <si>
+    <t>101701/2</t>
+  </si>
+  <si>
+    <t>97601/1</t>
+  </si>
+  <si>
+    <t>R$  146,38</t>
+  </si>
+  <si>
+    <t>97601FELIPEVS</t>
+  </si>
+  <si>
+    <t>96101/1</t>
+  </si>
+  <si>
+    <t>R$  400,33</t>
+  </si>
+  <si>
+    <t>96101ADRIANARBM</t>
+  </si>
+  <si>
+    <t>R$  285,72</t>
+  </si>
+  <si>
     <t>R$  505,46</t>
   </si>
   <si>
-    <t>56901/1</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>R$  170,33</t>
-  </si>
-  <si>
-    <t>56901BIANCARMS</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>87601/1</t>
-  </si>
-  <si>
-    <t>R$  620,43</t>
-  </si>
-  <si>
-    <t>87601CleitonS</t>
-  </si>
-  <si>
-    <t>87301/1</t>
-  </si>
-  <si>
-    <t>R$  469,36</t>
-  </si>
-  <si>
-    <t>87301PatriciaSS</t>
-  </si>
-  <si>
-    <t>92001/1</t>
-  </si>
-  <si>
-    <t>R$  346,86</t>
-  </si>
-  <si>
-    <t>92001LUCIANALS</t>
-  </si>
-  <si>
-    <t>101701/2</t>
-  </si>
-  <si>
-    <t>83201/1</t>
-  </si>
-  <si>
-    <t>R$  4.535,18</t>
-  </si>
-  <si>
-    <t>83201ElaineMH</t>
-  </si>
-  <si>
-    <t>97601/1</t>
-  </si>
-  <si>
-    <t>R$  146,38</t>
-  </si>
-  <si>
-    <t>97601FELIPEVS</t>
-  </si>
-  <si>
-    <t>96101/1</t>
-  </si>
-  <si>
-    <t>R$  400,33</t>
-  </si>
-  <si>
-    <t>96101ADRIANARBM</t>
-  </si>
-  <si>
-    <t>R$  114,28</t>
-  </si>
-  <si>
-    <t>R$  714,32</t>
-  </si>
-  <si>
-    <t>R$  285,72</t>
-  </si>
-  <si>
-    <t>99401/2</t>
-  </si>
-  <si>
-    <t>R$  455,29</t>
-  </si>
-  <si>
     <t>56102/2</t>
   </si>
   <si>
-    <t>R$  579,19</t>
-  </si>
-  <si>
-    <t>R$  746,58</t>
-  </si>
-  <si>
     <t>98701/2</t>
   </si>
   <si>
@@ -1458,18 +1458,18 @@
     <t>DSR set26/1</t>
   </si>
   <si>
+    <t>R$  592,53</t>
+  </si>
+  <si>
+    <t>07/09/26</t>
+  </si>
+  <si>
     <t>Rosangela Pacheco</t>
   </si>
   <si>
     <t>R$  1.046,14</t>
   </si>
   <si>
-    <t>07/09/26</t>
-  </si>
-  <si>
-    <t>R$  592,53</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1539,6 +1539,12 @@
     <t>Brindes clientes</t>
   </si>
   <si>
+    <t>766/1</t>
+  </si>
+  <si>
+    <t>vinho para clientes 1/3</t>
+  </si>
+  <si>
     <t>66/3</t>
   </si>
   <si>
@@ -1548,12 +1554,6 @@
     <t>Licoretto brinde clientes</t>
   </si>
   <si>
-    <t>766/1</t>
-  </si>
-  <si>
-    <t>vinho para clientes 1/3</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1563,6 +1563,33 @@
     <t>4.03.03.09.04 Marketing - mídia veículos de comunicação (CV)</t>
   </si>
   <si>
+    <t>12/9</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -1575,33 +1602,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>12/9</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/7</t>
   </si>
   <si>
@@ -1650,6 +1650,81 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Estorno emp set26/1</t>
+  </si>
+  <si>
+    <t>R$  282,79</t>
+  </si>
+  <si>
+    <t>Estorno desconto emprestimo</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Fixo set26/1</t>
+  </si>
+  <si>
+    <t>R$  1.720,72</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  3.276,49</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
     <t>GUTEMBERG DIAS GOMES</t>
   </si>
   <si>
@@ -1659,54 +1734,6 @@
     <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.720,72</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Estorno emp set26/1</t>
-  </si>
-  <si>
-    <t>R$  282,79</t>
-  </si>
-  <si>
-    <t>Estorno desconto emprestimo</t>
-  </si>
-  <si>
-    <t>Fixo set26/1</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  3.276,49</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -1716,39 +1743,12 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
     <t>Eric Kevin de Souza Serpa</t>
   </si>
   <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
     <t>19/09/26</t>
   </si>
   <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1815,21 +1815,21 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT set26/1</t>
+  </si>
+  <si>
+    <t>R$  287,31</t>
+  </si>
+  <si>
+    <t>28/08/26</t>
+  </si>
+  <si>
     <t>VT set 26/1</t>
   </si>
   <si>
     <t>R$  413,84</t>
   </si>
   <si>
-    <t>VT set26/1</t>
-  </si>
-  <si>
-    <t>R$  287,31</t>
-  </si>
-  <si>
-    <t>28/08/26</t>
-  </si>
-  <si>
     <t>4.04.01.06 Assistência médica e hospitalar</t>
   </si>
   <si>
@@ -1981,6 +1981,30 @@
   </si>
   <si>
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
+  </si>
+  <si>
+    <t>761/1</t>
+  </si>
+  <si>
+    <t>R$  31,70</t>
+  </si>
+  <si>
+    <t>02/10/26</t>
+  </si>
+  <si>
+    <t>águas</t>
+  </si>
+  <si>
+    <t>738/1</t>
+  </si>
+  <si>
+    <t>Casa de Bolos de Moema LTDA</t>
+  </si>
+  <si>
+    <t>R$  92,00</t>
+  </si>
+  <si>
+    <t>Bolo Rosangela</t>
   </si>
   <si>
     <t>768/1</t>
@@ -1998,30 +2022,6 @@
 </t>
   </si>
   <si>
-    <t>738/1</t>
-  </si>
-  <si>
-    <t>Casa de Bolos de Moema LTDA</t>
-  </si>
-  <si>
-    <t>R$  92,00</t>
-  </si>
-  <si>
-    <t>Bolo Rosangela</t>
-  </si>
-  <si>
-    <t>761/1</t>
-  </si>
-  <si>
-    <t>R$  31,70</t>
-  </si>
-  <si>
-    <t>02/10/26</t>
-  </si>
-  <si>
-    <t>águas</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2064,51 +2064,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>Promob</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>63/4</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>70/1</t>
+  </si>
+  <si>
+    <t>R$  188,19</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>62/4</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
     <t>767/1</t>
   </si>
   <si>
-    <t>Promob</t>
-  </si>
-  <si>
     <t>R$  4.516,62</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>63/4</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/1</t>
-  </si>
-  <si>
-    <t>R$  188,19</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
-  </si>
-  <si>
-    <t>62/4</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
     <t>3/8</t>
   </si>
   <si>
@@ -2121,6 +2121,15 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
     <t>61/5</t>
   </si>
   <si>
@@ -2131,15 +2140,6 @@
   </si>
   <si>
     <t>21/05/26</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
   </si>
   <si>
     <t>64/4</t>
@@ -7084,7 +7084,7 @@
         <v>249</v>
       </c>
       <c r="F92" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G92" t="s">
         <v>41</v>
@@ -7099,10 +7099,10 @@
         <v>252</v>
       </c>
       <c r="K92" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="L92" t="s">
-        <v>254</v>
+        <v>34</v>
       </c>
       <c r="M92" t="s">
         <v>247</v>
@@ -7137,7 +7137,7 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F93" t="s">
         <v>170</v>
@@ -7146,19 +7146,19 @@
         <v>41</v>
       </c>
       <c r="H93" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I93" t="s">
+        <v>255</v>
+      </c>
+      <c r="J93" t="s">
         <v>256</v>
       </c>
-      <c r="J93" t="s">
-        <v>252</v>
-      </c>
       <c r="K93" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L93" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M93" t="s">
         <v>247</v>
@@ -7170,7 +7170,7 @@
         <v>54</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q93" t="s">
         <v>45</v>
@@ -7193,10 +7193,10 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F94" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G94" t="s">
         <v>41</v>
@@ -7205,16 +7205,16 @@
         <v>250</v>
       </c>
       <c r="I94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K94" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="L94" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M94" t="s">
         <v>247</v>
@@ -7226,7 +7226,7 @@
         <v>54</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q94" t="s">
         <v>45</v>
@@ -7249,7 +7249,7 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F95" t="s">
         <v>196</v>
@@ -7258,19 +7258,19 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="I95" t="s">
         <v>264</v>
       </c>
       <c r="J95" t="s">
+        <v>121</v>
+      </c>
+      <c r="K95" t="s">
         <v>265</v>
       </c>
-      <c r="K95" t="s">
-        <v>75</v>
-      </c>
       <c r="L95" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M95" t="s">
         <v>247</v>
@@ -7305,28 +7305,28 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
+        <v>266</v>
+      </c>
+      <c r="F96" t="s">
+        <v>170</v>
+      </c>
+      <c r="G96" t="s">
+        <v>41</v>
+      </c>
+      <c r="H96" t="s">
+        <v>254</v>
+      </c>
+      <c r="I96" t="s">
         <v>267</v>
       </c>
-      <c r="F96" t="s">
-        <v>196</v>
-      </c>
-      <c r="G96" t="s">
-        <v>41</v>
-      </c>
-      <c r="H96" t="s">
-        <v>263</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
+        <v>256</v>
+      </c>
+      <c r="K96" t="s">
+        <v>257</v>
+      </c>
+      <c r="L96" t="s">
         <v>268</v>
-      </c>
-      <c r="J96" t="s">
-        <v>269</v>
-      </c>
-      <c r="K96" t="s">
-        <v>67</v>
-      </c>
-      <c r="L96" t="s">
-        <v>34</v>
       </c>
       <c r="M96" t="s">
         <v>247</v>
@@ -7338,7 +7338,7 @@
         <v>54</v>
       </c>
       <c r="P96" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q96" t="s">
         <v>45</v>
@@ -7361,7 +7361,7 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F97" t="s">
         <v>196</v>
@@ -7370,19 +7370,19 @@
         <v>41</v>
       </c>
       <c r="H97" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="I97" t="s">
+        <v>270</v>
+      </c>
+      <c r="J97" t="s">
         <v>271</v>
       </c>
-      <c r="J97" t="s">
-        <v>121</v>
-      </c>
       <c r="K97" t="s">
+        <v>271</v>
+      </c>
+      <c r="L97" t="s">
         <v>272</v>
-      </c>
-      <c r="L97" t="s">
-        <v>266</v>
       </c>
       <c r="M97" t="s">
         <v>247</v>
@@ -7394,7 +7394,7 @@
         <v>54</v>
       </c>
       <c r="P97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q97" t="s">
         <v>45</v>
@@ -7420,13 +7420,13 @@
         <v>273</v>
       </c>
       <c r="F98" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G98" t="s">
         <v>41</v>
       </c>
       <c r="H98" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="I98" t="s">
         <v>274</v>
@@ -7435,7 +7435,7 @@
         <v>275</v>
       </c>
       <c r="K98" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L98" t="s">
         <v>276</v>
@@ -9489,25 +9489,25 @@
         <v>33</v>
       </c>
       <c r="E135" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="F135" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G135" t="s">
         <v>41</v>
       </c>
       <c r="H135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I135" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J135" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="K135" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
@@ -9519,13 +9519,13 @@
         <v>45</v>
       </c>
       <c r="O135" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="P135" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="Q135" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R135" t="s">
         <v>34</v>
@@ -9548,22 +9548,22 @@
         <v>203</v>
       </c>
       <c r="F136" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G136" t="s">
         <v>41</v>
       </c>
       <c r="H136" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I136" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J136" t="s">
-        <v>265</v>
+        <v>44</v>
       </c>
       <c r="K136" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L136" t="s">
         <v>34</v>
@@ -9575,13 +9575,13 @@
         <v>45</v>
       </c>
       <c r="O136" t="s">
-        <v>354</v>
+        <v>34</v>
       </c>
       <c r="P136" t="s">
-        <v>353</v>
+        <v>34</v>
       </c>
       <c r="Q136" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R136" t="s">
         <v>34</v>
@@ -9601,25 +9601,25 @@
         <v>34</v>
       </c>
       <c r="E137" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="F137" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G137" t="s">
         <v>41</v>
       </c>
       <c r="H137" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I137" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J137" t="s">
-        <v>265</v>
+        <v>44</v>
       </c>
       <c r="K137" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L137" t="s">
         <v>34</v>
@@ -9631,13 +9631,13 @@
         <v>45</v>
       </c>
       <c r="O137" t="s">
-        <v>356</v>
+        <v>34</v>
       </c>
       <c r="P137" t="s">
-        <v>355</v>
+        <v>34</v>
       </c>
       <c r="Q137" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R137" t="s">
         <v>34</v>
@@ -9657,7 +9657,7 @@
         <v>34</v>
       </c>
       <c r="E138" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F138" t="s">
         <v>183</v>
@@ -9666,13 +9666,13 @@
         <v>41</v>
       </c>
       <c r="H138" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I138" t="s">
         <v>357</v>
       </c>
       <c r="J138" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K138" t="s">
         <v>52</v>
@@ -9687,7 +9687,7 @@
         <v>45</v>
       </c>
       <c r="O138" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="P138" t="s">
         <v>357</v>
@@ -9713,7 +9713,7 @@
         <v>34</v>
       </c>
       <c r="E139" t="s">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="F139" t="s">
         <v>183</v>
@@ -9722,13 +9722,13 @@
         <v>41</v>
       </c>
       <c r="H139" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I139" t="s">
         <v>358</v>
       </c>
       <c r="J139" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K139" t="s">
         <v>52</v>
@@ -9743,7 +9743,7 @@
         <v>45</v>
       </c>
       <c r="O139" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="P139" t="s">
         <v>358</v>
@@ -9769,7 +9769,7 @@
         <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F140" t="s">
         <v>183</v>
@@ -9778,13 +9778,13 @@
         <v>41</v>
       </c>
       <c r="H140" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I140" t="s">
         <v>359</v>
       </c>
       <c r="J140" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K140" t="s">
         <v>52</v>
@@ -9799,7 +9799,7 @@
         <v>45</v>
       </c>
       <c r="O140" t="s">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="P140" t="s">
         <v>359</v>
@@ -9825,7 +9825,7 @@
         <v>34</v>
       </c>
       <c r="E141" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="F141" t="s">
         <v>183</v>
@@ -9834,13 +9834,13 @@
         <v>41</v>
       </c>
       <c r="H141" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I141" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J141" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K141" t="s">
         <v>52</v>
@@ -9855,10 +9855,10 @@
         <v>45</v>
       </c>
       <c r="O141" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="P141" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q141" t="s">
         <v>45</v>
@@ -9881,7 +9881,7 @@
         <v>34</v>
       </c>
       <c r="E142" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F142" t="s">
         <v>183</v>
@@ -9890,13 +9890,13 @@
         <v>41</v>
       </c>
       <c r="H142" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I142" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J142" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K142" t="s">
         <v>52</v>
@@ -9911,10 +9911,10 @@
         <v>45</v>
       </c>
       <c r="O142" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="P142" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q142" t="s">
         <v>45</v>
@@ -9937,7 +9937,7 @@
         <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="F143" t="s">
         <v>183</v>
@@ -9946,13 +9946,13 @@
         <v>41</v>
       </c>
       <c r="H143" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I143" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J143" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K143" t="s">
         <v>52</v>
@@ -9967,10 +9967,10 @@
         <v>45</v>
       </c>
       <c r="O143" t="s">
+        <v>105</v>
+      </c>
+      <c r="P143" t="s">
         <v>363</v>
-      </c>
-      <c r="P143" t="s">
-        <v>362</v>
       </c>
       <c r="Q143" t="s">
         <v>45</v>
@@ -9993,7 +9993,7 @@
         <v>34</v>
       </c>
       <c r="E144" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="F144" t="s">
         <v>183</v>
@@ -10002,13 +10002,13 @@
         <v>41</v>
       </c>
       <c r="H144" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I144" t="s">
         <v>364</v>
       </c>
       <c r="J144" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K144" t="s">
         <v>52</v>
@@ -10023,7 +10023,7 @@
         <v>45</v>
       </c>
       <c r="O144" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="P144" t="s">
         <v>364</v>
@@ -10049,7 +10049,7 @@
         <v>34</v>
       </c>
       <c r="E145" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F145" t="s">
         <v>183</v>
@@ -10058,13 +10058,13 @@
         <v>41</v>
       </c>
       <c r="H145" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I145" t="s">
         <v>365</v>
       </c>
       <c r="J145" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K145" t="s">
         <v>52</v>
@@ -10079,7 +10079,7 @@
         <v>45</v>
       </c>
       <c r="O145" t="s">
-        <v>199</v>
+        <v>64</v>
       </c>
       <c r="P145" t="s">
         <v>365</v>
@@ -10105,7 +10105,7 @@
         <v>34</v>
       </c>
       <c r="E146" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F146" t="s">
         <v>183</v>
@@ -10114,13 +10114,13 @@
         <v>41</v>
       </c>
       <c r="H146" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I146" t="s">
         <v>366</v>
       </c>
       <c r="J146" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K146" t="s">
         <v>52</v>
@@ -10135,7 +10135,7 @@
         <v>45</v>
       </c>
       <c r="O146" t="s">
-        <v>113</v>
+        <v>367</v>
       </c>
       <c r="P146" t="s">
         <v>366</v>
@@ -10161,25 +10161,25 @@
         <v>34</v>
       </c>
       <c r="E147" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="F147" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G147" t="s">
         <v>41</v>
       </c>
       <c r="H147" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I147" t="s">
         <v>368</v>
       </c>
       <c r="J147" t="s">
-        <v>58</v>
+        <v>261</v>
       </c>
       <c r="K147" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L147" t="s">
         <v>34</v>
@@ -10191,13 +10191,13 @@
         <v>45</v>
       </c>
       <c r="O147" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="P147" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
       <c r="Q147" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R147" t="s">
         <v>34</v>
@@ -10217,25 +10217,25 @@
         <v>34</v>
       </c>
       <c r="E148" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F148" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G148" t="s">
         <v>41</v>
       </c>
       <c r="H148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I148" t="s">
         <v>369</v>
       </c>
       <c r="J148" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="K148" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L148" t="s">
         <v>34</v>
@@ -10247,13 +10247,13 @@
         <v>45</v>
       </c>
       <c r="O148" t="s">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>34</v>
+        <v>369</v>
       </c>
       <c r="Q148" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R148" t="s">
         <v>34</v>
@@ -10273,25 +10273,25 @@
         <v>34</v>
       </c>
       <c r="E149" t="s">
+        <v>235</v>
+      </c>
+      <c r="F149" t="s">
+        <v>183</v>
+      </c>
+      <c r="G149" t="s">
+        <v>41</v>
+      </c>
+      <c r="H149" t="s">
+        <v>352</v>
+      </c>
+      <c r="I149" t="s">
         <v>370</v>
       </c>
-      <c r="F149" t="s">
-        <v>367</v>
-      </c>
-      <c r="G149" t="s">
-        <v>41</v>
-      </c>
-      <c r="H149" t="s">
-        <v>351</v>
-      </c>
-      <c r="I149" t="s">
-        <v>371</v>
-      </c>
       <c r="J149" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="K149" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L149" t="s">
         <v>34</v>
@@ -10303,13 +10303,13 @@
         <v>45</v>
       </c>
       <c r="O149" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="P149" t="s">
-        <v>34</v>
+        <v>370</v>
       </c>
       <c r="Q149" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R149" t="s">
         <v>34</v>
@@ -10329,7 +10329,7 @@
         <v>34</v>
       </c>
       <c r="E150" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F150" t="s">
         <v>183</v>
@@ -10338,13 +10338,13 @@
         <v>41</v>
       </c>
       <c r="H150" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I150" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J150" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K150" t="s">
         <v>52</v>
@@ -10359,10 +10359,10 @@
         <v>45</v>
       </c>
       <c r="O150" t="s">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="P150" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q150" t="s">
         <v>45</v>
@@ -10456,7 +10456,7 @@
         <v>377</v>
       </c>
       <c r="J152" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K152" t="s">
         <v>52</v>
@@ -10512,7 +10512,7 @@
         <v>378</v>
       </c>
       <c r="J153" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K153" t="s">
         <v>52</v>
@@ -10568,7 +10568,7 @@
         <v>379</v>
       </c>
       <c r="J154" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K154" t="s">
         <v>52</v>
@@ -10624,7 +10624,7 @@
         <v>381</v>
       </c>
       <c r="J155" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K155" t="s">
         <v>52</v>
@@ -10674,13 +10674,13 @@
         <v>41</v>
       </c>
       <c r="H156" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I156" t="s">
         <v>382</v>
       </c>
       <c r="J156" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K156" t="s">
         <v>52</v>
@@ -10736,7 +10736,7 @@
         <v>384</v>
       </c>
       <c r="J157" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K157" t="s">
         <v>52</v>
@@ -10792,7 +10792,7 @@
         <v>385</v>
       </c>
       <c r="J158" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K158" t="s">
         <v>52</v>
@@ -10807,7 +10807,7 @@
         <v>45</v>
       </c>
       <c r="O158" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P158" t="s">
         <v>385</v>
@@ -10848,7 +10848,7 @@
         <v>386</v>
       </c>
       <c r="J159" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K159" t="s">
         <v>52</v>
@@ -10904,7 +10904,7 @@
         <v>387</v>
       </c>
       <c r="J160" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K160" t="s">
         <v>52</v>
@@ -10960,7 +10960,7 @@
         <v>388</v>
       </c>
       <c r="J161" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K161" t="s">
         <v>52</v>
@@ -11016,7 +11016,7 @@
         <v>389</v>
       </c>
       <c r="J162" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K162" t="s">
         <v>52</v>
@@ -11031,7 +11031,7 @@
         <v>45</v>
       </c>
       <c r="O162" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="P162" t="s">
         <v>389</v>
@@ -11072,7 +11072,7 @@
         <v>390</v>
       </c>
       <c r="J163" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K163" t="s">
         <v>52</v>
@@ -11128,7 +11128,7 @@
         <v>392</v>
       </c>
       <c r="J164" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K164" t="s">
         <v>52</v>
@@ -11184,7 +11184,7 @@
         <v>393</v>
       </c>
       <c r="J165" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K165" t="s">
         <v>52</v>
@@ -11240,7 +11240,7 @@
         <v>394</v>
       </c>
       <c r="J166" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K166" t="s">
         <v>52</v>
@@ -11255,7 +11255,7 @@
         <v>45</v>
       </c>
       <c r="O166" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="P166" t="s">
         <v>394</v>
@@ -11296,7 +11296,7 @@
         <v>396</v>
       </c>
       <c r="J167" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K167" t="s">
         <v>52</v>
@@ -11311,7 +11311,7 @@
         <v>45</v>
       </c>
       <c r="O167" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="P167" t="s">
         <v>396</v>
@@ -11352,7 +11352,7 @@
         <v>397</v>
       </c>
       <c r="J168" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K168" t="s">
         <v>52</v>
@@ -11408,7 +11408,7 @@
         <v>398</v>
       </c>
       <c r="J169" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K169" t="s">
         <v>52</v>
@@ -11464,7 +11464,7 @@
         <v>399</v>
       </c>
       <c r="J170" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K170" t="s">
         <v>52</v>
@@ -11520,7 +11520,7 @@
         <v>400</v>
       </c>
       <c r="J171" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K171" t="s">
         <v>52</v>
@@ -11576,7 +11576,7 @@
         <v>401</v>
       </c>
       <c r="J172" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K172" t="s">
         <v>52</v>
@@ -11591,7 +11591,7 @@
         <v>45</v>
       </c>
       <c r="O172" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P172" t="s">
         <v>401</v>
@@ -11632,7 +11632,7 @@
         <v>402</v>
       </c>
       <c r="J173" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K173" t="s">
         <v>52</v>
@@ -11688,7 +11688,7 @@
         <v>403</v>
       </c>
       <c r="J174" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K174" t="s">
         <v>52</v>
@@ -11744,7 +11744,7 @@
         <v>405</v>
       </c>
       <c r="J175" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K175" t="s">
         <v>52</v>
@@ -11797,10 +11797,10 @@
         <v>404</v>
       </c>
       <c r="I176" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="J176" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K176" t="s">
         <v>52</v>
@@ -11818,7 +11818,7 @@
         <v>406</v>
       </c>
       <c r="P176" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="Q176" t="s">
         <v>45</v>
@@ -11853,10 +11853,10 @@
         <v>404</v>
       </c>
       <c r="I177" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J177" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K177" t="s">
         <v>52</v>
@@ -11874,7 +11874,7 @@
         <v>199</v>
       </c>
       <c r="P177" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q177" t="s">
         <v>45</v>
@@ -11909,10 +11909,10 @@
         <v>404</v>
       </c>
       <c r="I178" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="J178" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K178" t="s">
         <v>52</v>
@@ -11930,7 +11930,7 @@
         <v>113</v>
       </c>
       <c r="P178" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q178" t="s">
         <v>45</v>
@@ -11965,10 +11965,10 @@
         <v>404</v>
       </c>
       <c r="I179" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J179" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K179" t="s">
         <v>52</v>
@@ -11986,7 +11986,7 @@
         <v>83</v>
       </c>
       <c r="P179" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q179" t="s">
         <v>45</v>
@@ -12021,10 +12021,10 @@
         <v>404</v>
       </c>
       <c r="I180" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="J180" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K180" t="s">
         <v>52</v>
@@ -12039,10 +12039,10 @@
         <v>45</v>
       </c>
       <c r="O180" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P180" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q180" t="s">
         <v>45</v>
@@ -12080,7 +12080,7 @@
         <v>407</v>
       </c>
       <c r="J181" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K181" t="s">
         <v>52</v>
@@ -12136,7 +12136,7 @@
         <v>408</v>
       </c>
       <c r="J182" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K182" t="s">
         <v>52</v>
@@ -12192,7 +12192,7 @@
         <v>409</v>
       </c>
       <c r="J183" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K183" t="s">
         <v>52</v>
@@ -12248,7 +12248,7 @@
         <v>410</v>
       </c>
       <c r="J184" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K184" t="s">
         <v>52</v>
@@ -12304,7 +12304,7 @@
         <v>411</v>
       </c>
       <c r="J185" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K185" t="s">
         <v>52</v>
@@ -12360,7 +12360,7 @@
         <v>412</v>
       </c>
       <c r="J186" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K186" t="s">
         <v>52</v>
@@ -12375,7 +12375,7 @@
         <v>45</v>
       </c>
       <c r="O186" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="P186" t="s">
         <v>412</v>
@@ -12416,7 +12416,7 @@
         <v>413</v>
       </c>
       <c r="J187" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K187" t="s">
         <v>52</v>
@@ -12469,10 +12469,10 @@
         <v>404</v>
       </c>
       <c r="I188" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J188" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K188" t="s">
         <v>52</v>
@@ -12490,7 +12490,7 @@
         <v>105</v>
       </c>
       <c r="P188" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q188" t="s">
         <v>45</v>
@@ -12525,10 +12525,10 @@
         <v>404</v>
       </c>
       <c r="I189" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J189" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K189" t="s">
         <v>52</v>
@@ -12546,7 +12546,7 @@
         <v>118</v>
       </c>
       <c r="P189" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q189" t="s">
         <v>45</v>
@@ -12581,10 +12581,10 @@
         <v>404</v>
       </c>
       <c r="I190" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J190" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K190" t="s">
         <v>52</v>
@@ -12602,7 +12602,7 @@
         <v>110</v>
       </c>
       <c r="P190" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q190" t="s">
         <v>45</v>
@@ -12640,7 +12640,7 @@
         <v>414</v>
       </c>
       <c r="J191" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K191" t="s">
         <v>52</v>
@@ -12693,10 +12693,10 @@
         <v>404</v>
       </c>
       <c r="I192" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J192" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K192" t="s">
         <v>52</v>
@@ -12714,7 +12714,7 @@
         <v>95</v>
       </c>
       <c r="P192" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q192" t="s">
         <v>45</v>
@@ -12749,10 +12749,10 @@
         <v>404</v>
       </c>
       <c r="I193" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="J193" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K193" t="s">
         <v>52</v>
@@ -12770,7 +12770,7 @@
         <v>100</v>
       </c>
       <c r="P193" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="Q193" t="s">
         <v>45</v>
@@ -12805,10 +12805,10 @@
         <v>404</v>
       </c>
       <c r="I194" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J194" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K194" t="s">
         <v>52</v>
@@ -12823,10 +12823,10 @@
         <v>45</v>
       </c>
       <c r="O194" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="P194" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q194" t="s">
         <v>45</v>
@@ -12849,10 +12849,10 @@
         <v>34</v>
       </c>
       <c r="E195" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="F195" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G195" t="s">
         <v>41</v>
@@ -12905,10 +12905,10 @@
         <v>34</v>
       </c>
       <c r="E196" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="F196" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G196" t="s">
         <v>41</v>
@@ -12961,10 +12961,10 @@
         <v>34</v>
       </c>
       <c r="E197" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="F197" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G197" t="s">
         <v>41</v>
@@ -13020,7 +13020,7 @@
         <v>200</v>
       </c>
       <c r="F198" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G198" t="s">
         <v>41</v>
@@ -13076,7 +13076,7 @@
         <v>200</v>
       </c>
       <c r="F199" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G199" t="s">
         <v>41</v>
@@ -13132,7 +13132,7 @@
         <v>200</v>
       </c>
       <c r="F200" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G200" t="s">
         <v>41</v>
@@ -13188,7 +13188,7 @@
         <v>203</v>
       </c>
       <c r="F201" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G201" t="s">
         <v>41</v>
@@ -13244,7 +13244,7 @@
         <v>186</v>
       </c>
       <c r="F202" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G202" t="s">
         <v>41</v>
@@ -13300,7 +13300,7 @@
         <v>205</v>
       </c>
       <c r="F203" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G203" t="s">
         <v>41</v>
@@ -13356,7 +13356,7 @@
         <v>205</v>
       </c>
       <c r="F204" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G204" t="s">
         <v>41</v>
@@ -13412,7 +13412,7 @@
         <v>205</v>
       </c>
       <c r="F205" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G205" t="s">
         <v>41</v>
@@ -13465,10 +13465,10 @@
         <v>33</v>
       </c>
       <c r="E206" t="s">
-        <v>323</v>
+        <v>238</v>
       </c>
       <c r="F206" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G206" t="s">
         <v>41</v>
@@ -13477,13 +13477,13 @@
         <v>184</v>
       </c>
       <c r="I206" t="s">
-        <v>358</v>
+        <v>424</v>
       </c>
       <c r="J206" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K206" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13521,25 +13521,25 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>312</v>
+        <v>425</v>
       </c>
       <c r="F207" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G207" t="s">
         <v>41</v>
       </c>
       <c r="H207" t="s">
-        <v>424</v>
+        <v>184</v>
       </c>
       <c r="I207" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="J207" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="K207" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="L207" t="s">
         <v>34</v>
@@ -13577,25 +13577,25 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="F208" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G208" t="s">
         <v>41</v>
       </c>
       <c r="H208" t="s">
+        <v>184</v>
+      </c>
+      <c r="I208" t="s">
         <v>426</v>
       </c>
-      <c r="I208" t="s">
-        <v>427</v>
-      </c>
       <c r="J208" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="K208" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="L208" t="s">
         <v>34</v>
@@ -13633,10 +13633,10 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="F209" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G209" t="s">
         <v>41</v>
@@ -13645,13 +13645,13 @@
         <v>184</v>
       </c>
       <c r="I209" t="s">
-        <v>382</v>
+        <v>427</v>
       </c>
       <c r="J209" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="K209" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="L209" t="s">
         <v>34</v>
@@ -13689,25 +13689,25 @@
         <v>34</v>
       </c>
       <c r="E210" t="s">
+        <v>304</v>
+      </c>
+      <c r="F210" t="s">
+        <v>351</v>
+      </c>
+      <c r="G210" t="s">
+        <v>41</v>
+      </c>
+      <c r="H210" t="s">
+        <v>184</v>
+      </c>
+      <c r="I210" t="s">
         <v>428</v>
       </c>
-      <c r="F210" t="s">
-        <v>183</v>
-      </c>
-      <c r="G210" t="s">
-        <v>41</v>
-      </c>
-      <c r="H210" t="s">
-        <v>429</v>
-      </c>
-      <c r="I210" t="s">
-        <v>430</v>
-      </c>
       <c r="J210" t="s">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="K210" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L210" t="s">
         <v>34</v>
@@ -13719,13 +13719,13 @@
         <v>45</v>
       </c>
       <c r="O210" t="s">
-        <v>431</v>
+        <v>34</v>
       </c>
       <c r="P210" t="s">
-        <v>430</v>
+        <v>34</v>
       </c>
       <c r="Q210" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R210" t="s">
         <v>34</v>
@@ -13745,25 +13745,25 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="F211" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G211" t="s">
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>432</v>
+        <v>184</v>
       </c>
       <c r="I211" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J211" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="K211" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="L211" t="s">
         <v>34</v>
@@ -13775,13 +13775,13 @@
         <v>45</v>
       </c>
       <c r="O211" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="P211" t="s">
-        <v>365</v>
+        <v>34</v>
       </c>
       <c r="Q211" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R211" t="s">
         <v>34</v>
@@ -13801,25 +13801,25 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>433</v>
+        <v>312</v>
       </c>
       <c r="F212" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G212" t="s">
         <v>41</v>
       </c>
       <c r="H212" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I212" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J212" t="s">
-        <v>265</v>
+        <v>104</v>
       </c>
       <c r="K212" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="L212" t="s">
         <v>34</v>
@@ -13831,13 +13831,13 @@
         <v>45</v>
       </c>
       <c r="O212" t="s">
-        <v>435</v>
+        <v>34</v>
       </c>
       <c r="P212" t="s">
-        <v>434</v>
+        <v>34</v>
       </c>
       <c r="Q212" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R212" t="s">
         <v>34</v>
@@ -13857,25 +13857,25 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>436</v>
+        <v>323</v>
       </c>
       <c r="F213" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G213" t="s">
         <v>41</v>
       </c>
       <c r="H213" t="s">
-        <v>426</v>
+        <v>184</v>
       </c>
       <c r="I213" t="s">
-        <v>437</v>
+        <v>362</v>
       </c>
       <c r="J213" t="s">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="K213" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="L213" t="s">
         <v>34</v>
@@ -13887,13 +13887,13 @@
         <v>45</v>
       </c>
       <c r="O213" t="s">
-        <v>438</v>
+        <v>34</v>
       </c>
       <c r="P213" t="s">
-        <v>437</v>
+        <v>34</v>
       </c>
       <c r="Q213" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R213" t="s">
         <v>34</v>
@@ -13913,25 +13913,25 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>439</v>
+        <v>339</v>
       </c>
       <c r="F214" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G214" t="s">
         <v>41</v>
       </c>
       <c r="H214" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I214" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="J214" t="s">
-        <v>265</v>
+        <v>90</v>
       </c>
       <c r="K214" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="L214" t="s">
         <v>34</v>
@@ -13943,13 +13943,13 @@
         <v>45</v>
       </c>
       <c r="O214" t="s">
-        <v>441</v>
+        <v>34</v>
       </c>
       <c r="P214" t="s">
-        <v>440</v>
+        <v>34</v>
       </c>
       <c r="Q214" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R214" t="s">
         <v>34</v>
@@ -13969,25 +13969,25 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F215" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G215" t="s">
         <v>41</v>
       </c>
       <c r="H215" t="s">
-        <v>184</v>
+        <v>434</v>
       </c>
       <c r="I215" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="J215" t="s">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="K215" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="L215" t="s">
         <v>34</v>
@@ -13999,13 +13999,13 @@
         <v>45</v>
       </c>
       <c r="O215" t="s">
-        <v>34</v>
+        <v>436</v>
       </c>
       <c r="P215" t="s">
-        <v>34</v>
+        <v>435</v>
       </c>
       <c r="Q215" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R215" t="s">
         <v>34</v>
@@ -14025,7 +14025,7 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F216" t="s">
         <v>183</v>
@@ -14034,13 +14034,13 @@
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="I216" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="J216" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K216" t="s">
         <v>52</v>
@@ -14055,10 +14055,10 @@
         <v>45</v>
       </c>
       <c r="O216" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="P216" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Q216" t="s">
         <v>45</v>
@@ -14081,7 +14081,7 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F217" t="s">
         <v>183</v>
@@ -14090,13 +14090,13 @@
         <v>41</v>
       </c>
       <c r="H217" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="I217" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="J217" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K217" t="s">
         <v>52</v>
@@ -14111,10 +14111,10 @@
         <v>45</v>
       </c>
       <c r="O217" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="P217" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="Q217" t="s">
         <v>45</v>
@@ -14137,7 +14137,7 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F218" t="s">
         <v>183</v>
@@ -14146,13 +14146,13 @@
         <v>41</v>
       </c>
       <c r="H218" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="I218" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J218" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K218" t="s">
         <v>52</v>
@@ -14167,10 +14167,10 @@
         <v>45</v>
       </c>
       <c r="O218" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P218" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="Q218" t="s">
         <v>45</v>
@@ -14193,25 +14193,25 @@
         <v>34</v>
       </c>
       <c r="E219" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="F219" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G219" t="s">
         <v>41</v>
       </c>
       <c r="H219" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="I219" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J219" t="s">
-        <v>90</v>
+        <v>261</v>
       </c>
       <c r="K219" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="L219" t="s">
         <v>34</v>
@@ -14223,13 +14223,13 @@
         <v>45</v>
       </c>
       <c r="O219" t="s">
-        <v>34</v>
+        <v>449</v>
       </c>
       <c r="P219" t="s">
-        <v>34</v>
+        <v>448</v>
       </c>
       <c r="Q219" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R219" t="s">
         <v>34</v>
@@ -14249,25 +14249,25 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>207</v>
+        <v>450</v>
       </c>
       <c r="F220" t="s">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="G220" t="s">
         <v>41</v>
       </c>
       <c r="H220" t="s">
-        <v>424</v>
+        <v>184</v>
       </c>
       <c r="I220" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="J220" t="s">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="K220" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="L220" t="s">
         <v>34</v>
@@ -14279,13 +14279,13 @@
         <v>45</v>
       </c>
       <c r="O220" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P220" t="s">
-        <v>361</v>
+        <v>34</v>
       </c>
       <c r="Q220" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R220" t="s">
         <v>34</v>
@@ -14305,25 +14305,25 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="F221" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G221" t="s">
         <v>41</v>
       </c>
       <c r="H221" t="s">
-        <v>184</v>
+        <v>434</v>
       </c>
       <c r="I221" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J221" t="s">
-        <v>109</v>
+        <v>261</v>
       </c>
       <c r="K221" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="L221" t="s">
         <v>34</v>
@@ -14335,13 +14335,13 @@
         <v>45</v>
       </c>
       <c r="O221" t="s">
-        <v>34</v>
+        <v>453</v>
       </c>
       <c r="P221" t="s">
-        <v>34</v>
+        <v>452</v>
       </c>
       <c r="Q221" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R221" t="s">
         <v>34</v>
@@ -14361,25 +14361,25 @@
         <v>34</v>
       </c>
       <c r="E222" t="s">
-        <v>288</v>
+        <v>454</v>
       </c>
       <c r="F222" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G222" t="s">
         <v>41</v>
       </c>
       <c r="H222" t="s">
-        <v>184</v>
+        <v>431</v>
       </c>
       <c r="I222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J222" t="s">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="K222" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="L222" t="s">
         <v>34</v>
@@ -14391,13 +14391,13 @@
         <v>45</v>
       </c>
       <c r="O222" t="s">
-        <v>34</v>
+        <v>456</v>
       </c>
       <c r="P222" t="s">
-        <v>34</v>
+        <v>455</v>
       </c>
       <c r="Q222" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R222" t="s">
         <v>34</v>
@@ -14417,25 +14417,25 @@
         <v>34</v>
       </c>
       <c r="E223" t="s">
-        <v>455</v>
+        <v>207</v>
       </c>
       <c r="F223" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G223" t="s">
         <v>41</v>
       </c>
       <c r="H223" t="s">
-        <v>184</v>
+        <v>429</v>
       </c>
       <c r="I223" t="s">
-        <v>417</v>
+        <v>365</v>
       </c>
       <c r="J223" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="K223" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L223" t="s">
         <v>34</v>
@@ -14447,13 +14447,13 @@
         <v>45</v>
       </c>
       <c r="O223" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="P223" t="s">
-        <v>34</v>
+        <v>365</v>
       </c>
       <c r="Q223" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R223" t="s">
         <v>34</v>
@@ -14473,25 +14473,25 @@
         <v>34</v>
       </c>
       <c r="E224" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="F224" t="s">
-        <v>367</v>
+        <v>183</v>
       </c>
       <c r="G224" t="s">
         <v>41</v>
       </c>
       <c r="H224" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="I224" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="J224" t="s">
-        <v>63</v>
+        <v>261</v>
       </c>
       <c r="K224" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L224" t="s">
         <v>34</v>
@@ -14503,13 +14503,13 @@
         <v>45</v>
       </c>
       <c r="O224" t="s">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="P224" t="s">
-        <v>34</v>
+        <v>369</v>
       </c>
       <c r="Q224" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R224" t="s">
         <v>34</v>
@@ -14529,25 +14529,25 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="F225" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G225" t="s">
         <v>41</v>
       </c>
       <c r="H225" t="s">
-        <v>184</v>
+        <v>429</v>
       </c>
       <c r="I225" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="J225" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K225" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L225" t="s">
         <v>34</v>
@@ -14585,10 +14585,10 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="F226" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G226" t="s">
         <v>41</v>
@@ -14597,13 +14597,13 @@
         <v>184</v>
       </c>
       <c r="I226" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J226" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K226" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L226" t="s">
         <v>34</v>
@@ -14641,25 +14641,25 @@
         <v>34</v>
       </c>
       <c r="E227" t="s">
-        <v>457</v>
+        <v>296</v>
       </c>
       <c r="F227" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G227" t="s">
         <v>41</v>
       </c>
       <c r="H227" t="s">
-        <v>184</v>
+        <v>434</v>
       </c>
       <c r="I227" t="s">
-        <v>353</v>
+        <v>458</v>
       </c>
       <c r="J227" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K227" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L227" t="s">
         <v>34</v>
@@ -14697,10 +14697,10 @@
         <v>34</v>
       </c>
       <c r="E228" t="s">
-        <v>238</v>
+        <v>459</v>
       </c>
       <c r="F228" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G228" t="s">
         <v>41</v>
@@ -14709,13 +14709,13 @@
         <v>184</v>
       </c>
       <c r="I228" t="s">
-        <v>458</v>
+        <v>371</v>
       </c>
       <c r="J228" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="K228" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="L228" t="s">
         <v>34</v>
@@ -14753,10 +14753,10 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="F229" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G229" t="s">
         <v>41</v>
@@ -14765,13 +14765,13 @@
         <v>184</v>
       </c>
       <c r="I229" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="J229" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="K229" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="L229" t="s">
         <v>34</v>
@@ -14809,10 +14809,10 @@
         <v>34</v>
       </c>
       <c r="E230" t="s">
-        <v>460</v>
+        <v>300</v>
       </c>
       <c r="F230" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G230" t="s">
         <v>41</v>
@@ -14821,13 +14821,13 @@
         <v>184</v>
       </c>
       <c r="I230" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="J230" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="K230" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L230" t="s">
         <v>34</v>
@@ -14865,10 +14865,10 @@
         <v>33</v>
       </c>
       <c r="E231" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="F231" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G231" t="s">
         <v>41</v>
@@ -14924,7 +14924,7 @@
         <v>205</v>
       </c>
       <c r="F232" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G232" t="s">
         <v>41</v>
@@ -14980,7 +14980,7 @@
         <v>203</v>
       </c>
       <c r="F233" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
@@ -15036,7 +15036,7 @@
         <v>242</v>
       </c>
       <c r="F234" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
@@ -15092,7 +15092,7 @@
         <v>213</v>
       </c>
       <c r="F235" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G235" t="s">
         <v>41</v>
@@ -15148,7 +15148,7 @@
         <v>207</v>
       </c>
       <c r="F236" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G236" t="s">
         <v>41</v>
@@ -15204,7 +15204,7 @@
         <v>327</v>
       </c>
       <c r="F237" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
@@ -15260,7 +15260,7 @@
         <v>219</v>
       </c>
       <c r="F238" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
@@ -15316,7 +15316,7 @@
         <v>235</v>
       </c>
       <c r="F239" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G239" t="s">
         <v>41</v>
@@ -15372,7 +15372,7 @@
         <v>182</v>
       </c>
       <c r="F240" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G240" t="s">
         <v>41</v>
@@ -15428,7 +15428,7 @@
         <v>233</v>
       </c>
       <c r="F241" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
@@ -15484,7 +15484,7 @@
         <v>186</v>
       </c>
       <c r="F242" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -15540,7 +15540,7 @@
         <v>189</v>
       </c>
       <c r="F243" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
@@ -15596,7 +15596,7 @@
         <v>230</v>
       </c>
       <c r="F244" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
@@ -15652,7 +15652,7 @@
         <v>192</v>
       </c>
       <c r="F245" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G245" t="s">
         <v>41</v>
@@ -15708,7 +15708,7 @@
         <v>200</v>
       </c>
       <c r="F246" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G246" t="s">
         <v>41</v>
@@ -15770,16 +15770,16 @@
         <v>41</v>
       </c>
       <c r="H247" t="s">
+        <v>352</v>
+      </c>
+      <c r="I247" t="s">
         <v>481</v>
       </c>
-      <c r="I247" t="s">
+      <c r="J247" t="s">
         <v>482</v>
       </c>
-      <c r="J247" t="s">
-        <v>483</v>
-      </c>
       <c r="K247" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L247" t="s">
         <v>34</v>
@@ -15794,7 +15794,7 @@
         <v>54</v>
       </c>
       <c r="P247" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q247" t="s">
         <v>45</v>
@@ -15826,16 +15826,16 @@
         <v>41</v>
       </c>
       <c r="H248" t="s">
-        <v>351</v>
+        <v>483</v>
       </c>
       <c r="I248" t="s">
         <v>484</v>
       </c>
       <c r="J248" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K248" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L248" t="s">
         <v>34</v>
@@ -16041,10 +16041,10 @@
         <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="F252" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
@@ -16056,10 +16056,10 @@
         <v>492</v>
       </c>
       <c r="J252" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="K252" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="L252" t="s">
         <v>34</v>
@@ -16071,13 +16071,13 @@
         <v>45</v>
       </c>
       <c r="O252" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="P252" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q252" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R252" t="s">
         <v>34</v>
@@ -16097,7 +16097,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>207</v>
+        <v>355</v>
       </c>
       <c r="F253" t="s">
         <v>170</v>
@@ -16112,10 +16112,10 @@
         <v>492</v>
       </c>
       <c r="J253" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K253" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="L253" t="s">
         <v>34</v>
@@ -16127,7 +16127,7 @@
         <v>45</v>
       </c>
       <c r="O253" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="P253" t="s">
         <v>492</v>
@@ -16153,10 +16153,10 @@
         <v>34</v>
       </c>
       <c r="E254" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="F254" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G254" t="s">
         <v>41</v>
@@ -16168,10 +16168,10 @@
         <v>492</v>
       </c>
       <c r="J254" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="K254" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="L254" t="s">
         <v>34</v>
@@ -16183,7 +16183,7 @@
         <v>45</v>
       </c>
       <c r="O254" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="P254" t="s">
         <v>492</v>
@@ -16209,10 +16209,10 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="F255" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="G255" t="s">
         <v>41</v>
@@ -16224,10 +16224,10 @@
         <v>492</v>
       </c>
       <c r="J255" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K255" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="L255" t="s">
         <v>34</v>
@@ -16239,13 +16239,13 @@
         <v>45</v>
       </c>
       <c r="O255" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="P255" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q255" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R255" t="s">
         <v>34</v>
@@ -16265,7 +16265,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F256" t="s">
         <v>196</v>
@@ -16280,10 +16280,10 @@
         <v>492</v>
       </c>
       <c r="J256" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="K256" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="L256" t="s">
         <v>34</v>
@@ -16295,7 +16295,7 @@
         <v>45</v>
       </c>
       <c r="O256" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="P256" t="s">
         <v>492</v>
@@ -16321,10 +16321,10 @@
         <v>34</v>
       </c>
       <c r="E257" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="F257" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="G257" t="s">
         <v>41</v>
@@ -16336,10 +16336,10 @@
         <v>492</v>
       </c>
       <c r="J257" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="K257" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="L257" t="s">
         <v>34</v>
@@ -16351,13 +16351,13 @@
         <v>45</v>
       </c>
       <c r="O257" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="P257" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q257" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R257" t="s">
         <v>34</v>
@@ -16377,10 +16377,10 @@
         <v>34</v>
       </c>
       <c r="E258" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="F258" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G258" t="s">
         <v>41</v>
@@ -16392,10 +16392,10 @@
         <v>492</v>
       </c>
       <c r="J258" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="K258" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="L258" t="s">
         <v>34</v>
@@ -16407,7 +16407,7 @@
         <v>45</v>
       </c>
       <c r="O258" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="P258" t="s">
         <v>492</v>
@@ -16433,10 +16433,10 @@
         <v>34</v>
       </c>
       <c r="E259" t="s">
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="F259" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
@@ -16448,10 +16448,10 @@
         <v>492</v>
       </c>
       <c r="J259" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="K259" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="L259" t="s">
         <v>34</v>
@@ -16463,13 +16463,13 @@
         <v>45</v>
       </c>
       <c r="O259" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P259" t="s">
-        <v>492</v>
+        <v>34</v>
       </c>
       <c r="Q259" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R259" t="s">
         <v>34</v>
@@ -16489,7 +16489,7 @@
         <v>34</v>
       </c>
       <c r="E260" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="F260" t="s">
         <v>159</v>
@@ -16504,10 +16504,10 @@
         <v>492</v>
       </c>
       <c r="J260" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K260" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L260" t="s">
         <v>34</v>
@@ -16545,7 +16545,7 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F261" t="s">
         <v>159</v>
@@ -16560,10 +16560,10 @@
         <v>492</v>
       </c>
       <c r="J261" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="K261" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="L261" t="s">
         <v>34</v>
@@ -16601,7 +16601,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F262" t="s">
         <v>159</v>
@@ -16616,10 +16616,10 @@
         <v>492</v>
       </c>
       <c r="J262" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="K262" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="L262" t="s">
         <v>34</v>
@@ -16657,10 +16657,10 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>370</v>
+        <v>213</v>
       </c>
       <c r="F263" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
@@ -16669,13 +16669,13 @@
         <v>491</v>
       </c>
       <c r="I263" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J263" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="K263" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="L263" t="s">
         <v>34</v>
@@ -16687,13 +16687,13 @@
         <v>45</v>
       </c>
       <c r="O263" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="P263" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q263" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R263" t="s">
         <v>34</v>
@@ -16713,10 +16713,10 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F264" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G264" t="s">
         <v>41</v>
@@ -16728,10 +16728,10 @@
         <v>492</v>
       </c>
       <c r="J264" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="K264" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="L264" t="s">
         <v>34</v>
@@ -16743,13 +16743,13 @@
         <v>45</v>
       </c>
       <c r="O264" t="s">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="P264" t="s">
-        <v>34</v>
+        <v>492</v>
       </c>
       <c r="Q264" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R264" t="s">
         <v>34</v>
@@ -16769,10 +16769,10 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>233</v>
+        <v>355</v>
       </c>
       <c r="F265" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="G265" t="s">
         <v>41</v>
@@ -16781,13 +16781,13 @@
         <v>491</v>
       </c>
       <c r="I265" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J265" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="K265" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="L265" t="s">
         <v>34</v>
@@ -16825,7 +16825,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F266" t="s">
         <v>159</v>
@@ -16840,10 +16840,10 @@
         <v>492</v>
       </c>
       <c r="J266" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="K266" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L266" t="s">
         <v>34</v>
@@ -16881,7 +16881,7 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F267" t="s">
         <v>159</v>
@@ -16896,10 +16896,10 @@
         <v>492</v>
       </c>
       <c r="J267" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="K267" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L267" t="s">
         <v>34</v>
@@ -17120,7 +17120,7 @@
         <v>506</v>
       </c>
       <c r="J271" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="K271" t="s">
         <v>63</v>
@@ -17164,7 +17164,7 @@
         <v>508</v>
       </c>
       <c r="F272" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
@@ -17173,16 +17173,16 @@
         <v>505</v>
       </c>
       <c r="I272" t="s">
+        <v>506</v>
+      </c>
+      <c r="J272" t="s">
+        <v>261</v>
+      </c>
+      <c r="K272" t="s">
+        <v>482</v>
+      </c>
+      <c r="L272" t="s">
         <v>509</v>
-      </c>
-      <c r="J272" t="s">
-        <v>260</v>
-      </c>
-      <c r="K272" t="s">
-        <v>253</v>
-      </c>
-      <c r="L272" t="s">
-        <v>510</v>
       </c>
       <c r="M272" t="s">
         <v>503</v>
@@ -17194,7 +17194,7 @@
         <v>54</v>
       </c>
       <c r="P272" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="Q272" t="s">
         <v>45</v>
@@ -17217,10 +17217,10 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F273" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
@@ -17229,13 +17229,13 @@
         <v>505</v>
       </c>
       <c r="I273" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="J273" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="K273" t="s">
-        <v>483</v>
+        <v>257</v>
       </c>
       <c r="L273" t="s">
         <v>512</v>
@@ -17250,7 +17250,7 @@
         <v>54</v>
       </c>
       <c r="P273" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="Q273" t="s">
         <v>45</v>
@@ -17329,7 +17329,7 @@
         <v>33</v>
       </c>
       <c r="E275" t="s">
-        <v>145</v>
+        <v>516</v>
       </c>
       <c r="F275" t="s">
         <v>170</v>
@@ -17338,19 +17338,19 @@
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I275" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J275" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K275" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="L275" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M275" t="s">
         <v>515</v>
@@ -17362,7 +17362,7 @@
         <v>54</v>
       </c>
       <c r="P275" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Q275" t="s">
         <v>45</v>
@@ -17385,7 +17385,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F276" t="s">
         <v>170</v>
@@ -17403,7 +17403,7 @@
         <v>523</v>
       </c>
       <c r="K276" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L276" t="s">
         <v>524</v>
@@ -17441,7 +17441,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>520</v>
+        <v>145</v>
       </c>
       <c r="F277" t="s">
         <v>170</v>
@@ -17459,7 +17459,7 @@
         <v>527</v>
       </c>
       <c r="K277" t="s">
-        <v>272</v>
+        <v>150</v>
       </c>
       <c r="L277" t="s">
         <v>528</v>
@@ -17721,7 +17721,7 @@
         <v>33</v>
       </c>
       <c r="E282" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F282" t="s">
         <v>170</v>
@@ -17736,10 +17736,10 @@
         <v>166</v>
       </c>
       <c r="J282" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K282" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L282" t="s">
         <v>539</v>
@@ -17889,7 +17889,7 @@
         <v>33</v>
       </c>
       <c r="E285" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F285" t="s">
         <v>170</v>
@@ -17898,19 +17898,19 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
+        <v>434</v>
+      </c>
+      <c r="I285" t="s">
+        <v>166</v>
+      </c>
+      <c r="J285" t="s">
+        <v>523</v>
+      </c>
+      <c r="K285" t="s">
+        <v>257</v>
+      </c>
+      <c r="L285" t="s">
         <v>545</v>
-      </c>
-      <c r="I285" t="s">
-        <v>546</v>
-      </c>
-      <c r="J285" t="s">
-        <v>527</v>
-      </c>
-      <c r="K285" t="s">
-        <v>253</v>
-      </c>
-      <c r="L285" t="s">
-        <v>547</v>
       </c>
       <c r="M285" t="s">
         <v>544</v>
@@ -17922,7 +17922,7 @@
         <v>54</v>
       </c>
       <c r="P285" t="s">
-        <v>546</v>
+        <v>166</v>
       </c>
       <c r="Q285" t="s">
         <v>45</v>
@@ -17945,7 +17945,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F286" t="s">
         <v>170</v>
@@ -17954,19 +17954,19 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
+        <v>546</v>
+      </c>
+      <c r="I286" t="s">
+        <v>547</v>
+      </c>
+      <c r="J286" t="s">
+        <v>519</v>
+      </c>
+      <c r="K286" t="s">
+        <v>257</v>
+      </c>
+      <c r="L286" t="s">
         <v>548</v>
-      </c>
-      <c r="I286" t="s">
-        <v>166</v>
-      </c>
-      <c r="J286" t="s">
-        <v>527</v>
-      </c>
-      <c r="K286" t="s">
-        <v>253</v>
-      </c>
-      <c r="L286" t="s">
-        <v>549</v>
       </c>
       <c r="M286" t="s">
         <v>544</v>
@@ -17978,7 +17978,7 @@
         <v>54</v>
       </c>
       <c r="P286" t="s">
-        <v>166</v>
+        <v>547</v>
       </c>
       <c r="Q286" t="s">
         <v>45</v>
@@ -18001,7 +18001,7 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>529</v>
+        <v>145</v>
       </c>
       <c r="F287" t="s">
         <v>170</v>
@@ -18010,19 +18010,19 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="I287" t="s">
+        <v>549</v>
+      </c>
+      <c r="J287" t="s">
         <v>550</v>
       </c>
-      <c r="J287" t="s">
+      <c r="K287" t="s">
+        <v>257</v>
+      </c>
+      <c r="L287" t="s">
         <v>551</v>
-      </c>
-      <c r="K287" t="s">
-        <v>253</v>
-      </c>
-      <c r="L287" t="s">
-        <v>552</v>
       </c>
       <c r="M287" t="s">
         <v>544</v>
@@ -18034,7 +18034,7 @@
         <v>54</v>
       </c>
       <c r="P287" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q287" t="s">
         <v>45</v>
@@ -18057,7 +18057,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>520</v>
+        <v>145</v>
       </c>
       <c r="F288" t="s">
         <v>170</v>
@@ -18066,19 +18066,19 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I288" t="s">
-        <v>166</v>
+        <v>552</v>
       </c>
       <c r="J288" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="K288" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L288" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M288" t="s">
         <v>544</v>
@@ -18090,7 +18090,7 @@
         <v>54</v>
       </c>
       <c r="P288" t="s">
-        <v>166</v>
+        <v>552</v>
       </c>
       <c r="Q288" t="s">
         <v>45</v>
@@ -18113,28 +18113,28 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>520</v>
+        <v>555</v>
       </c>
       <c r="F289" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G289" t="s">
         <v>41</v>
       </c>
       <c r="H289" t="s">
-        <v>554</v>
+        <v>483</v>
       </c>
       <c r="I289" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J289" t="s">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="K289" t="s">
-        <v>253</v>
+        <v>482</v>
       </c>
       <c r="L289" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M289" t="s">
         <v>544</v>
@@ -18146,7 +18146,7 @@
         <v>54</v>
       </c>
       <c r="P289" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q289" t="s">
         <v>45</v>
@@ -18169,25 +18169,25 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="F290" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G290" t="s">
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>481</v>
+        <v>558</v>
       </c>
       <c r="I290" t="s">
-        <v>558</v>
+        <v>166</v>
       </c>
       <c r="J290" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="K290" t="s">
-        <v>483</v>
+        <v>257</v>
       </c>
       <c r="L290" t="s">
         <v>559</v>
@@ -18202,7 +18202,7 @@
         <v>54</v>
       </c>
       <c r="P290" t="s">
-        <v>558</v>
+        <v>166</v>
       </c>
       <c r="Q290" t="s">
         <v>45</v>
@@ -18234,7 +18234,7 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="I291" t="s">
         <v>166</v>
@@ -18281,7 +18281,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F292" t="s">
         <v>170</v>
@@ -18290,16 +18290,16 @@
         <v>41</v>
       </c>
       <c r="H292" t="s">
+        <v>352</v>
+      </c>
+      <c r="I292" t="s">
         <v>561</v>
       </c>
-      <c r="I292" t="s">
+      <c r="J292" t="s">
         <v>562</v>
       </c>
-      <c r="J292" t="s">
-        <v>527</v>
-      </c>
       <c r="K292" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L292" t="s">
         <v>563</v>
@@ -18314,7 +18314,7 @@
         <v>54</v>
       </c>
       <c r="P292" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Q292" t="s">
         <v>45</v>
@@ -18337,7 +18337,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F293" t="s">
         <v>170</v>
@@ -18352,10 +18352,10 @@
         <v>565</v>
       </c>
       <c r="J293" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K293" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L293" t="s">
         <v>566</v>
@@ -18393,7 +18393,7 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F294" t="s">
         <v>170</v>
@@ -18408,10 +18408,10 @@
         <v>568</v>
       </c>
       <c r="J294" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K294" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L294" t="s">
         <v>569</v>
@@ -18449,7 +18449,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>145</v>
+        <v>516</v>
       </c>
       <c r="F295" t="s">
         <v>170</v>
@@ -18458,16 +18458,16 @@
         <v>41</v>
       </c>
       <c r="H295" t="s">
-        <v>424</v>
+        <v>570</v>
       </c>
       <c r="I295" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J295" t="s">
-        <v>571</v>
+        <v>519</v>
       </c>
       <c r="K295" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L295" t="s">
         <v>572</v>
@@ -18482,7 +18482,7 @@
         <v>54</v>
       </c>
       <c r="P295" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q295" t="s">
         <v>45</v>
@@ -18505,28 +18505,28 @@
         <v>34</v>
       </c>
       <c r="E296" t="s">
-        <v>560</v>
+        <v>516</v>
       </c>
       <c r="F296" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="G296" t="s">
         <v>41</v>
       </c>
       <c r="H296" t="s">
-        <v>391</v>
+        <v>573</v>
       </c>
       <c r="I296" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J296" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="K296" t="s">
-        <v>483</v>
+        <v>257</v>
       </c>
       <c r="L296" t="s">
-        <v>34</v>
+        <v>575</v>
       </c>
       <c r="M296" t="s">
         <v>544</v>
@@ -18538,7 +18538,7 @@
         <v>54</v>
       </c>
       <c r="P296" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q296" t="s">
         <v>45</v>
@@ -18561,25 +18561,25 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>145</v>
+        <v>560</v>
       </c>
       <c r="F297" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="G297" t="s">
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>574</v>
+        <v>391</v>
       </c>
       <c r="I297" t="s">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="J297" t="s">
-        <v>575</v>
+        <v>482</v>
       </c>
       <c r="K297" t="s">
-        <v>576</v>
+        <v>482</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -18591,13 +18591,13 @@
         <v>45</v>
       </c>
       <c r="O297" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P297" t="s">
-        <v>34</v>
+        <v>549</v>
       </c>
       <c r="Q297" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R297" t="s">
         <v>34</v>
@@ -18620,25 +18620,25 @@
         <v>145</v>
       </c>
       <c r="F298" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G298" t="s">
         <v>41</v>
       </c>
       <c r="H298" t="s">
-        <v>383</v>
+        <v>576</v>
       </c>
       <c r="I298" t="s">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="J298" t="s">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="K298" t="s">
-        <v>253</v>
+        <v>577</v>
       </c>
       <c r="L298" t="s">
-        <v>577</v>
+        <v>34</v>
       </c>
       <c r="M298" t="s">
         <v>544</v>
@@ -18647,13 +18647,13 @@
         <v>45</v>
       </c>
       <c r="O298" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P298" t="s">
-        <v>573</v>
+        <v>34</v>
       </c>
       <c r="Q298" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R298" t="s">
         <v>34</v>
@@ -18853,7 +18853,7 @@
         <v>586</v>
       </c>
       <c r="I302" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="J302" t="s">
         <v>161</v>
@@ -19242,16 +19242,16 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>481</v>
+        <v>352</v>
       </c>
       <c r="I309" t="s">
         <v>601</v>
       </c>
       <c r="J309" t="s">
-        <v>44</v>
+        <v>602</v>
       </c>
       <c r="K309" t="s">
-        <v>44</v>
+        <v>482</v>
       </c>
       <c r="L309" t="s">
         <v>34</v>
@@ -19289,7 +19289,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F310" t="s">
         <v>196</v>
@@ -19298,16 +19298,16 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>351</v>
+        <v>483</v>
       </c>
       <c r="I310" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J310" t="s">
-        <v>604</v>
+        <v>44</v>
       </c>
       <c r="K310" t="s">
-        <v>483</v>
+        <v>44</v>
       </c>
       <c r="L310" t="s">
         <v>34</v>
@@ -19322,7 +19322,7 @@
         <v>54</v>
       </c>
       <c r="P310" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q310" t="s">
         <v>45</v>
@@ -19416,7 +19416,7 @@
         <v>610</v>
       </c>
       <c r="J312" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K312" t="s">
         <v>75</v>
@@ -19584,10 +19584,10 @@
         <v>619</v>
       </c>
       <c r="J315" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K315" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="L315" t="s">
         <v>620</v>
@@ -19793,7 +19793,7 @@
         <v>33</v>
       </c>
       <c r="E319" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F319" t="s">
         <v>170</v>
@@ -19808,10 +19808,10 @@
         <v>633</v>
       </c>
       <c r="J319" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K319" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L319" t="s">
         <v>634</v>
@@ -19961,7 +19961,7 @@
         <v>33</v>
       </c>
       <c r="E322" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F322" t="s">
         <v>170</v>
@@ -19976,10 +19976,10 @@
         <v>645</v>
       </c>
       <c r="J322" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K322" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L322" t="s">
         <v>646</v>
@@ -20088,10 +20088,10 @@
         <v>651</v>
       </c>
       <c r="J324" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K324" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="L324" t="s">
         <v>652</v>
@@ -20194,16 +20194,16 @@
         <v>41</v>
       </c>
       <c r="H326" t="s">
+        <v>352</v>
+      </c>
+      <c r="I326" t="s">
         <v>657</v>
       </c>
-      <c r="I326" t="s">
+      <c r="J326" t="s">
         <v>658</v>
       </c>
-      <c r="J326" t="s">
-        <v>265</v>
-      </c>
       <c r="K326" t="s">
-        <v>483</v>
+        <v>63</v>
       </c>
       <c r="L326" t="s">
         <v>659</v>
@@ -20218,7 +20218,7 @@
         <v>54</v>
       </c>
       <c r="P326" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q326" t="s">
         <v>45</v>
@@ -20306,16 +20306,16 @@
         <v>41</v>
       </c>
       <c r="H328" t="s">
-        <v>351</v>
+        <v>665</v>
       </c>
       <c r="I328" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J328" t="s">
-        <v>666</v>
+        <v>261</v>
       </c>
       <c r="K328" t="s">
-        <v>63</v>
+        <v>482</v>
       </c>
       <c r="L328" t="s">
         <v>667</v>
@@ -20330,7 +20330,7 @@
         <v>54</v>
       </c>
       <c r="P328" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Q328" t="s">
         <v>45</v>
@@ -20409,7 +20409,7 @@
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F330" t="s">
         <v>170</v>
@@ -20424,10 +20424,10 @@
         <v>673</v>
       </c>
       <c r="J330" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K330" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L330" t="s">
         <v>674</v>
@@ -20577,28 +20577,28 @@
         <v>33</v>
       </c>
       <c r="E333" t="s">
+        <v>516</v>
+      </c>
+      <c r="F333" t="s">
+        <v>170</v>
+      </c>
+      <c r="G333" t="s">
+        <v>41</v>
+      </c>
+      <c r="H333" t="s">
         <v>682</v>
       </c>
-      <c r="F333" t="s">
-        <v>196</v>
-      </c>
-      <c r="G333" t="s">
-        <v>41</v>
-      </c>
-      <c r="H333" t="s">
+      <c r="I333" t="s">
         <v>683</v>
       </c>
-      <c r="I333" t="s">
+      <c r="J333" t="s">
+        <v>523</v>
+      </c>
+      <c r="K333" t="s">
+        <v>44</v>
+      </c>
+      <c r="L333" t="s">
         <v>684</v>
-      </c>
-      <c r="J333" t="s">
-        <v>265</v>
-      </c>
-      <c r="K333" t="s">
-        <v>79</v>
-      </c>
-      <c r="L333" t="s">
-        <v>34</v>
       </c>
       <c r="M333" t="s">
         <v>681</v>
@@ -20610,7 +20610,7 @@
         <v>54</v>
       </c>
       <c r="P333" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q333" t="s">
         <v>45</v>
@@ -20633,7 +20633,7 @@
         <v>34</v>
       </c>
       <c r="E334" t="s">
-        <v>520</v>
+        <v>685</v>
       </c>
       <c r="F334" t="s">
         <v>170</v>
@@ -20642,19 +20642,19 @@
         <v>41</v>
       </c>
       <c r="H334" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I334" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J334" t="s">
-        <v>523</v>
+        <v>687</v>
       </c>
       <c r="K334" t="s">
-        <v>44</v>
+        <v>257</v>
       </c>
       <c r="L334" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M334" t="s">
         <v>681</v>
@@ -20666,7 +20666,7 @@
         <v>54</v>
       </c>
       <c r="P334" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Q334" t="s">
         <v>45</v>
@@ -20689,7 +20689,7 @@
         <v>34</v>
       </c>
       <c r="E335" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F335" t="s">
         <v>170</v>
@@ -20698,19 +20698,19 @@
         <v>41</v>
       </c>
       <c r="H335" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I335" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="J335" t="s">
-        <v>689</v>
+        <v>63</v>
       </c>
       <c r="K335" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L335" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M335" t="s">
         <v>681</v>
@@ -20722,7 +20722,7 @@
         <v>54</v>
       </c>
       <c r="P335" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="Q335" t="s">
         <v>45</v>
@@ -20745,7 +20745,7 @@
         <v>34</v>
       </c>
       <c r="E336" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F336" t="s">
         <v>170</v>
@@ -20754,19 +20754,19 @@
         <v>41</v>
       </c>
       <c r="H336" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I336" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="J336" t="s">
-        <v>63</v>
+        <v>687</v>
       </c>
       <c r="K336" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L336" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M336" t="s">
         <v>681</v>
@@ -20778,7 +20778,7 @@
         <v>54</v>
       </c>
       <c r="P336" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Q336" t="s">
         <v>45</v>
@@ -20801,28 +20801,28 @@
         <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F337" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G337" t="s">
         <v>41</v>
       </c>
       <c r="H337" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I337" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J337" t="s">
-        <v>689</v>
+        <v>261</v>
       </c>
       <c r="K337" t="s">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L337" t="s">
-        <v>696</v>
+        <v>34</v>
       </c>
       <c r="M337" t="s">
         <v>681</v>
@@ -20834,7 +20834,7 @@
         <v>54</v>
       </c>
       <c r="P337" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="Q337" t="s">
         <v>45</v>
@@ -20866,7 +20866,7 @@
         <v>41</v>
       </c>
       <c r="H338" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I338" t="s">
         <v>698</v>
@@ -20875,7 +20875,7 @@
         <v>699</v>
       </c>
       <c r="K338" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L338" t="s">
         <v>700</v>
@@ -20913,7 +20913,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>701</v>
+        <v>516</v>
       </c>
       <c r="F339" t="s">
         <v>170</v>
@@ -20922,19 +20922,19 @@
         <v>41</v>
       </c>
       <c r="H339" t="s">
+        <v>701</v>
+      </c>
+      <c r="I339" t="s">
         <v>702</v>
       </c>
-      <c r="I339" t="s">
+      <c r="J339" t="s">
+        <v>523</v>
+      </c>
+      <c r="K339" t="s">
+        <v>257</v>
+      </c>
+      <c r="L339" t="s">
         <v>703</v>
-      </c>
-      <c r="J339" t="s">
-        <v>704</v>
-      </c>
-      <c r="K339" t="s">
-        <v>253</v>
-      </c>
-      <c r="L339" t="s">
-        <v>702</v>
       </c>
       <c r="M339" t="s">
         <v>681</v>
@@ -20946,7 +20946,7 @@
         <v>54</v>
       </c>
       <c r="P339" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q339" t="s">
         <v>45</v>
@@ -20969,7 +20969,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>520</v>
+        <v>704</v>
       </c>
       <c r="F340" t="s">
         <v>170</v>
@@ -20984,13 +20984,13 @@
         <v>706</v>
       </c>
       <c r="J340" t="s">
-        <v>523</v>
+        <v>707</v>
       </c>
       <c r="K340" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L340" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="M340" t="s">
         <v>681</v>
@@ -21137,7 +21137,7 @@
         <v>33</v>
       </c>
       <c r="E343" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F343" t="s">
         <v>170</v>
@@ -21152,10 +21152,10 @@
         <v>716</v>
       </c>
       <c r="J343" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K343" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L343" t="s">
         <v>717</v>
@@ -21376,7 +21376,7 @@
         <v>735</v>
       </c>
       <c r="J347" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="K347" t="s">
         <v>150</v>
@@ -21417,7 +21417,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F348" t="s">
         <v>170</v>
@@ -21432,10 +21432,10 @@
         <v>737</v>
       </c>
       <c r="J348" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K348" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L348" t="s">
         <v>738</v>
@@ -21491,7 +21491,7 @@
         <v>699</v>
       </c>
       <c r="K349" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -21712,10 +21712,10 @@
         <v>750</v>
       </c>
       <c r="J353" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K353" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L353" t="s">
         <v>34</v>
@@ -26923,7 +26923,7 @@
         <v>63</v>
       </c>
       <c r="K446" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L446" t="s">
         <v>869</v>
@@ -26979,7 +26979,7 @@
         <v>173</v>
       </c>
       <c r="K447" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L447" t="s">
         <v>873</v>

--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -429,6 +429,21 @@
     <t>R$ 2.075,44</t>
   </si>
   <si>
+    <t>41/1</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>R$  606,88</t>
+  </si>
+  <si>
+    <t>20/10/26</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
     <t>40/1</t>
   </si>
   <si>
@@ -438,25 +453,10 @@
     <t>R$  1.468,56</t>
   </si>
   <si>
-    <t>20/10/26</t>
-  </si>
-  <si>
-    <t>ADM</t>
-  </si>
-  <si>
-    <t>41/1</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>R$  606,88</t>
-  </si>
-  <si>
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 377.705,50</t>
+    <t>R$ 376.177,70</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -537,7 +537,7 @@
     <t>4.02 CUSTOS</t>
   </si>
   <si>
-    <t>R$ 161.505,67</t>
+    <t>R$ 161.828,63</t>
   </si>
   <si>
     <t>4.02.01 CUSTO DAS MERCADORIAS VENDIDAS e SERVIÇOS</t>
@@ -858,7 +858,7 @@
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>R$ 21.597,27</t>
+    <t>R$ 21.920,23</t>
   </si>
   <si>
     <t>4.02.02.01 Fretes sobre compras</t>
@@ -906,13 +906,13 @@
     <t>95401/2</t>
   </si>
   <si>
-    <t>R$  1.330,51</t>
+    <t>R$  1.467,79</t>
   </si>
   <si>
     <t>95401/3</t>
   </si>
   <si>
-    <t>R$  1.355,35</t>
+    <t>R$  1.495,15</t>
   </si>
   <si>
     <t>100301/2</t>
@@ -942,13 +942,13 @@
     <t>102101/2</t>
   </si>
   <si>
-    <t>R$  764,90</t>
+    <t>R$  787,61</t>
   </si>
   <si>
     <t>102101/3</t>
   </si>
   <si>
-    <t>R$  779,41</t>
+    <t>R$  802,58</t>
   </si>
   <si>
     <t>100501/2</t>
@@ -1401,15 +1401,15 @@
     <t>DSR set26/1</t>
   </si>
   <si>
+    <t>R$  592,53</t>
+  </si>
+  <si>
     <t>Rosangela Pacheco</t>
   </si>
   <si>
     <t>R$  1.046,14</t>
   </si>
   <si>
-    <t>R$  592,53</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1479,6 +1479,12 @@
     <t>Brindes clientes</t>
   </si>
   <si>
+    <t>766/1</t>
+  </si>
+  <si>
+    <t>vinho para clientes 1/3</t>
+  </si>
+  <si>
     <t>66/3</t>
   </si>
   <si>
@@ -1488,12 +1494,6 @@
     <t>Licoretto brinde clientes</t>
   </si>
   <si>
-    <t>766/1</t>
-  </si>
-  <si>
-    <t>vinho para clientes 1/3</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1503,6 +1503,33 @@
     <t>4.03.03.09.04 Marketing - mídia veículos de comunicação (CV)</t>
   </si>
   <si>
+    <t>12/9</t>
+  </si>
+  <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
   </si>
   <si>
@@ -1518,33 +1545,6 @@
     <t>Webgiga 2026</t>
   </si>
   <si>
-    <t>12/9</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
     <t>1/7</t>
   </si>
   <si>
@@ -1791,21 +1791,21 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT set26/1</t>
+  </si>
+  <si>
+    <t>R$  287,31</t>
+  </si>
+  <si>
+    <t>28/08/26</t>
+  </si>
+  <si>
     <t>VT set 26/1</t>
   </si>
   <si>
     <t>R$  413,84</t>
   </si>
   <si>
-    <t>VT set26/1</t>
-  </si>
-  <si>
-    <t>R$  287,31</t>
-  </si>
-  <si>
-    <t>28/08/26</t>
-  </si>
-  <si>
     <t>4.04.01.06 Assistência médica e hospitalar</t>
   </si>
   <si>
@@ -1974,16 +1974,31 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>773/1</t>
+    <t>761/1</t>
+  </si>
+  <si>
+    <t>R$  31,70</t>
+  </si>
+  <si>
+    <t>02/10/26</t>
+  </si>
+  <si>
+    <t>águas</t>
+  </si>
+  <si>
+    <t>772/1</t>
+  </si>
+  <si>
+    <t>Ifood</t>
+  </si>
+  <si>
+    <t>R$  5,95</t>
+  </si>
+  <si>
+    <t>768/1</t>
   </si>
   <si>
     <t>Shopee</t>
-  </si>
-  <si>
-    <t>R$  51,33</t>
-  </si>
-  <si>
-    <t>768/1</t>
   </si>
   <si>
     <t>R$  193,87</t>
@@ -2007,25 +2022,10 @@
     <t>Bolo Rosangela</t>
   </si>
   <si>
-    <t>772/1</t>
-  </si>
-  <si>
-    <t>Ifood</t>
-  </si>
-  <si>
-    <t>R$  5,95</t>
-  </si>
-  <si>
-    <t>761/1</t>
-  </si>
-  <si>
-    <t>R$  31,70</t>
-  </si>
-  <si>
-    <t>02/10/26</t>
-  </si>
-  <si>
-    <t>águas</t>
+    <t>773/1</t>
+  </si>
+  <si>
+    <t>R$  51,33</t>
   </si>
   <si>
     <t>4.04.02.07 Informática</t>
@@ -2070,51 +2070,51 @@
     <t>4.04.02.08.03 Mensalidades e assinaturas - outros gastos</t>
   </si>
   <si>
+    <t>Promob</t>
+  </si>
+  <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
+    <t>63/4</t>
+  </si>
+  <si>
+    <t>R$  376,38</t>
+  </si>
+  <si>
+    <t>11/06/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/4</t>
+  </si>
+  <si>
+    <t>70/1</t>
+  </si>
+  <si>
+    <t>R$  188,19</t>
+  </si>
+  <si>
+    <t>Promob 26/5</t>
+  </si>
+  <si>
+    <t>62/4</t>
+  </si>
+  <si>
+    <t>R$  293,21</t>
+  </si>
+  <si>
+    <t>Promob 2026/3</t>
+  </si>
+  <si>
     <t>767/1</t>
   </si>
   <si>
-    <t>Promob</t>
-  </si>
-  <si>
     <t>R$  4.516,62</t>
   </si>
   <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>63/4</t>
-  </si>
-  <si>
-    <t>R$  376,38</t>
-  </si>
-  <si>
-    <t>11/06/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/4</t>
-  </si>
-  <si>
-    <t>70/1</t>
-  </si>
-  <si>
-    <t>R$  188,19</t>
-  </si>
-  <si>
-    <t>Promob 26/5</t>
-  </si>
-  <si>
-    <t>62/4</t>
-  </si>
-  <si>
-    <t>R$  293,21</t>
-  </si>
-  <si>
-    <t>Promob 2026/3</t>
-  </si>
-  <si>
     <t>3/8</t>
   </si>
   <si>
@@ -2127,6 +2127,30 @@
     <t>Promob 2026/2</t>
   </si>
   <si>
+    <t>D4 sign</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4 sign 2026</t>
+  </si>
+  <si>
+    <t>64/4</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>24/06/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
     <t>61/5</t>
   </si>
   <si>
@@ -2139,30 +2163,6 @@
     <t>21/05/26</t>
   </si>
   <si>
-    <t>64/4</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>24/06/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>D4 sign</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4 sign 2026</t>
-  </si>
-  <si>
     <t>4.04.02.13 Impostos e taxas</t>
   </si>
   <si>
@@ -2286,7 +2286,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 23.615,38</t>
+    <t>R$ 21.764,62</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -2298,54 +2298,54 @@
     <t>4.07.01.01.01 Operações financeiras - desconto de cheques (financeiras)</t>
   </si>
   <si>
+    <t>Italíneacredi</t>
+  </si>
+  <si>
+    <t>R$  2.998,42</t>
+  </si>
+  <si>
+    <t>Título referente a Valor da Taxa Financeira</t>
+  </si>
+  <si>
+    <t>R$  2.633,83</t>
+  </si>
+  <si>
+    <t>R$  1.644,76</t>
+  </si>
+  <si>
+    <t>R$  2.057,10</t>
+  </si>
+  <si>
+    <t>R$  842,10</t>
+  </si>
+  <si>
+    <t>R$  694,52</t>
+  </si>
+  <si>
+    <t>R$  1.454,91</t>
+  </si>
+  <si>
+    <t>R$  631,10</t>
+  </si>
+  <si>
+    <t>R$  3.331,98</t>
+  </si>
+  <si>
+    <t>R$  345,24</t>
+  </si>
+  <si>
+    <t>R$  103,38</t>
+  </si>
+  <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
+    <t>R$  4.153,06</t>
+  </si>
+  <si>
     <t>R$  874,22</t>
   </si>
   <si>
-    <t>Título referente a Valor da Taxa Financeira</t>
-  </si>
-  <si>
-    <t>Italíneacredi</t>
-  </si>
-  <si>
-    <t>R$  143,49</t>
-  </si>
-  <si>
-    <t>R$  800,25</t>
-  </si>
-  <si>
-    <t>R$  2.546,64</t>
-  </si>
-  <si>
-    <t>R$  3.178,28</t>
-  </si>
-  <si>
-    <t>R$  4.153,06</t>
-  </si>
-  <si>
-    <t>R$  820,28</t>
-  </si>
-  <si>
-    <t>R$  2.201,56</t>
-  </si>
-  <si>
-    <t>R$  360,92</t>
-  </si>
-  <si>
-    <t>R$  2.699,79</t>
-  </si>
-  <si>
-    <t>R$  1.504,40</t>
-  </si>
-  <si>
-    <t>R$  3.415,17</t>
-  </si>
-  <si>
-    <t>R$  917,32</t>
-  </si>
-  <si>
     <t>7.01 RECEITAS</t>
   </si>
   <si>
@@ -2385,7 +2385,7 @@
     <t>7.05 = RESULTADO BRUTO</t>
   </si>
   <si>
-    <t>R$ 200.865,20</t>
+    <t>R$ 200.542,24</t>
   </si>
   <si>
     <t>7.06 (-) DESPESAS REGULARES</t>
@@ -2478,13 +2478,13 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 22.864,80</t>
+    <t>R$ 22.541,84</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 23.622,20</t>
+    <t>R$ 21.771,44</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -2502,7 +2502,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ -757,40</t>
+    <t>R$ 770,40</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2517,7 +2517,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 290.269,31</t>
+    <t>R$ 288.741,51</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2550,7 +2550,7 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 353.332,72</t>
+    <t>R$ 355.183,48</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
@@ -2580,7 +2580,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 380.241,88</t>
+    <t>R$ 373.655,82</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -2595,7 +2595,7 @@
     <t>7.80.02 Mark Up à Vista</t>
   </si>
   <si>
-    <t>2,53</t>
+    <t>2,54</t>
   </si>
   <si>
     <t>7.80.03 Mark Up Líquido</t>
@@ -4497,7 +4497,7 @@
         <v>141</v>
       </c>
       <c r="K45" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="L45" t="s">
         <v>34</v>
@@ -4553,7 +4553,7 @@
         <v>141</v>
       </c>
       <c r="K46" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="L46" t="s">
         <v>34</v>
@@ -13000,7 +13000,7 @@
         <v>41</v>
       </c>
       <c r="H197" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I197" t="s">
         <v>428</v>
@@ -14624,10 +14624,10 @@
         <v>41</v>
       </c>
       <c r="H226" t="s">
+        <v>348</v>
+      </c>
+      <c r="I226" t="s">
         <v>461</v>
-      </c>
-      <c r="I226" t="s">
-        <v>462</v>
       </c>
       <c r="J226" t="s">
         <v>270</v>
@@ -14648,7 +14648,7 @@
         <v>142</v>
       </c>
       <c r="P226" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q226" t="s">
         <v>45</v>
@@ -14680,7 +14680,7 @@
         <v>41</v>
       </c>
       <c r="H227" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="I227" t="s">
         <v>463</v>
@@ -14895,10 +14895,10 @@
         <v>33</v>
       </c>
       <c r="E231" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="F231" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G231" t="s">
         <v>41</v>
@@ -14910,10 +14910,10 @@
         <v>471</v>
       </c>
       <c r="J231" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="K231" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="L231" t="s">
         <v>34</v>
@@ -14925,13 +14925,13 @@
         <v>45</v>
       </c>
       <c r="O231" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="P231" t="s">
-        <v>34</v>
+        <v>471</v>
       </c>
       <c r="Q231" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R231" t="s">
         <v>34</v>
@@ -14951,7 +14951,7 @@
         <v>34</v>
       </c>
       <c r="E232" t="s">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="F232" t="s">
         <v>154</v>
@@ -14966,10 +14966,10 @@
         <v>471</v>
       </c>
       <c r="J232" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K232" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L232" t="s">
         <v>34</v>
@@ -14981,7 +14981,7 @@
         <v>45</v>
       </c>
       <c r="O232" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="P232" t="s">
         <v>471</v>
@@ -15007,10 +15007,10 @@
         <v>34</v>
       </c>
       <c r="E233" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="F233" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="G233" t="s">
         <v>41</v>
@@ -15022,10 +15022,10 @@
         <v>471</v>
       </c>
       <c r="J233" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="K233" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="L233" t="s">
         <v>34</v>
@@ -15037,7 +15037,7 @@
         <v>45</v>
       </c>
       <c r="O233" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="P233" t="s">
         <v>471</v>
@@ -15063,10 +15063,10 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="F234" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G234" t="s">
         <v>41</v>
@@ -15078,10 +15078,10 @@
         <v>471</v>
       </c>
       <c r="J234" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K234" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15093,13 +15093,13 @@
         <v>45</v>
       </c>
       <c r="O234" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="P234" t="s">
-        <v>471</v>
+        <v>34</v>
       </c>
       <c r="Q234" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R234" t="s">
         <v>34</v>
@@ -15119,7 +15119,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="F235" t="s">
         <v>181</v>
@@ -15134,10 +15134,10 @@
         <v>471</v>
       </c>
       <c r="J235" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="K235" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15149,7 +15149,7 @@
         <v>45</v>
       </c>
       <c r="O235" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="P235" t="s">
         <v>471</v>
@@ -15175,10 +15175,10 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="F236" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G236" t="s">
         <v>41</v>
@@ -15190,10 +15190,10 @@
         <v>471</v>
       </c>
       <c r="J236" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="K236" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15205,13 +15205,13 @@
         <v>45</v>
       </c>
       <c r="O236" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P236" t="s">
-        <v>471</v>
+        <v>34</v>
       </c>
       <c r="Q236" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R236" t="s">
         <v>34</v>
@@ -15231,10 +15231,10 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="F237" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="G237" t="s">
         <v>41</v>
@@ -15246,10 +15246,10 @@
         <v>471</v>
       </c>
       <c r="J237" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="K237" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15261,7 +15261,7 @@
         <v>45</v>
       </c>
       <c r="O237" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="P237" t="s">
         <v>471</v>
@@ -15287,10 +15287,10 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="F238" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G238" t="s">
         <v>41</v>
@@ -15302,10 +15302,10 @@
         <v>471</v>
       </c>
       <c r="J238" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="K238" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15317,13 +15317,13 @@
         <v>45</v>
       </c>
       <c r="O238" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="P238" t="s">
-        <v>471</v>
+        <v>34</v>
       </c>
       <c r="Q238" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R238" t="s">
         <v>34</v>
@@ -15343,7 +15343,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F239" t="s">
         <v>163</v>
@@ -15358,10 +15358,10 @@
         <v>471</v>
       </c>
       <c r="J239" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="K239" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15399,7 +15399,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F240" t="s">
         <v>163</v>
@@ -15414,10 +15414,10 @@
         <v>471</v>
       </c>
       <c r="J240" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="K240" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15455,7 +15455,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F241" t="s">
         <v>163</v>
@@ -15470,10 +15470,10 @@
         <v>471</v>
       </c>
       <c r="J241" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="K241" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15511,10 +15511,10 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>352</v>
+        <v>192</v>
       </c>
       <c r="F242" t="s">
-        <v>284</v>
+        <v>154</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -15523,13 +15523,13 @@
         <v>470</v>
       </c>
       <c r="I242" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J242" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="K242" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15541,13 +15541,13 @@
         <v>45</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>471</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15567,10 +15567,10 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="F243" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
@@ -15582,10 +15582,10 @@
         <v>471</v>
       </c>
       <c r="J243" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="K243" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15597,13 +15597,13 @@
         <v>45</v>
       </c>
       <c r="O243" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="P243" t="s">
-        <v>34</v>
+        <v>471</v>
       </c>
       <c r="Q243" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -15623,10 +15623,10 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>209</v>
+        <v>352</v>
       </c>
       <c r="F244" t="s">
-        <v>163</v>
+        <v>284</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
@@ -15635,13 +15635,13 @@
         <v>470</v>
       </c>
       <c r="I244" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J244" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="K244" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15679,7 +15679,7 @@
         <v>34</v>
       </c>
       <c r="E245" t="s">
-        <v>350</v>
+        <v>197</v>
       </c>
       <c r="F245" t="s">
         <v>163</v>
@@ -15694,10 +15694,10 @@
         <v>471</v>
       </c>
       <c r="J245" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="K245" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="L245" t="s">
         <v>34</v>
@@ -15735,7 +15735,7 @@
         <v>34</v>
       </c>
       <c r="E246" t="s">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="F246" t="s">
         <v>163</v>
@@ -15750,10 +15750,10 @@
         <v>471</v>
       </c>
       <c r="J246" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="K246" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="L246" t="s">
         <v>34</v>
@@ -16018,7 +16018,7 @@
         <v>487</v>
       </c>
       <c r="F251" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="G251" t="s">
         <v>41</v>
@@ -16027,16 +16027,16 @@
         <v>484</v>
       </c>
       <c r="I251" t="s">
+        <v>485</v>
+      </c>
+      <c r="J251" t="s">
+        <v>237</v>
+      </c>
+      <c r="K251" t="s">
+        <v>270</v>
+      </c>
+      <c r="L251" t="s">
         <v>488</v>
-      </c>
-      <c r="J251" t="s">
-        <v>264</v>
-      </c>
-      <c r="K251" t="s">
-        <v>257</v>
-      </c>
-      <c r="L251" t="s">
-        <v>489</v>
       </c>
       <c r="M251" t="s">
         <v>482</v>
@@ -16048,7 +16048,7 @@
         <v>142</v>
       </c>
       <c r="P251" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="Q251" t="s">
         <v>45</v>
@@ -16071,10 +16071,10 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F252" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="G252" t="s">
         <v>41</v>
@@ -16083,13 +16083,13 @@
         <v>484</v>
       </c>
       <c r="I252" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="J252" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="K252" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="L252" t="s">
         <v>491</v>
@@ -16104,7 +16104,7 @@
         <v>142</v>
       </c>
       <c r="P252" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="Q252" t="s">
         <v>45</v>
@@ -16183,7 +16183,7 @@
         <v>33</v>
       </c>
       <c r="E254" t="s">
-        <v>162</v>
+        <v>495</v>
       </c>
       <c r="F254" t="s">
         <v>154</v>
@@ -16192,16 +16192,16 @@
         <v>41</v>
       </c>
       <c r="H254" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I254" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J254" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K254" t="s">
-        <v>498</v>
+        <v>238</v>
       </c>
       <c r="L254" t="s">
         <v>499</v>
@@ -16216,7 +16216,7 @@
         <v>142</v>
       </c>
       <c r="P254" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q254" t="s">
         <v>45</v>
@@ -16239,7 +16239,7 @@
         <v>34</v>
       </c>
       <c r="E255" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F255" t="s">
         <v>154</v>
@@ -16248,19 +16248,19 @@
         <v>41</v>
       </c>
       <c r="H255" t="s">
+        <v>500</v>
+      </c>
+      <c r="I255" t="s">
         <v>501</v>
       </c>
-      <c r="I255" t="s">
+      <c r="J255" t="s">
         <v>502</v>
-      </c>
-      <c r="J255" t="s">
-        <v>503</v>
       </c>
       <c r="K255" t="s">
         <v>257</v>
       </c>
       <c r="L255" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M255" t="s">
         <v>494</v>
@@ -16272,7 +16272,7 @@
         <v>142</v>
       </c>
       <c r="P255" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q255" t="s">
         <v>45</v>
@@ -16295,7 +16295,7 @@
         <v>34</v>
       </c>
       <c r="E256" t="s">
-        <v>500</v>
+        <v>162</v>
       </c>
       <c r="F256" t="s">
         <v>154</v>
@@ -16304,16 +16304,16 @@
         <v>41</v>
       </c>
       <c r="H256" t="s">
+        <v>504</v>
+      </c>
+      <c r="I256" t="s">
         <v>505</v>
       </c>
-      <c r="I256" t="s">
+      <c r="J256" t="s">
         <v>506</v>
       </c>
-      <c r="J256" t="s">
+      <c r="K256" t="s">
         <v>507</v>
-      </c>
-      <c r="K256" t="s">
-        <v>238</v>
       </c>
       <c r="L256" t="s">
         <v>508</v>
@@ -16328,7 +16328,7 @@
         <v>142</v>
       </c>
       <c r="P256" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q256" t="s">
         <v>45</v>
@@ -16575,7 +16575,7 @@
         <v>33</v>
       </c>
       <c r="E261" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F261" t="s">
         <v>154</v>
@@ -16590,7 +16590,7 @@
         <v>165</v>
       </c>
       <c r="J261" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K261" t="s">
         <v>257</v>
@@ -16752,7 +16752,7 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I264" t="s">
         <v>526</v>
@@ -17135,7 +17135,7 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F271" t="s">
         <v>154</v>
@@ -17150,7 +17150,7 @@
         <v>548</v>
       </c>
       <c r="J271" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K271" t="s">
         <v>257</v>
@@ -17191,7 +17191,7 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F272" t="s">
         <v>154</v>
@@ -17206,7 +17206,7 @@
         <v>165</v>
       </c>
       <c r="J272" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K272" t="s">
         <v>257</v>
@@ -17247,7 +17247,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F273" t="s">
         <v>154</v>
@@ -17262,7 +17262,7 @@
         <v>165</v>
       </c>
       <c r="J273" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K273" t="s">
         <v>257</v>
@@ -17415,7 +17415,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F276" t="s">
         <v>154</v>
@@ -17430,7 +17430,7 @@
         <v>558</v>
       </c>
       <c r="J276" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K276" t="s">
         <v>257</v>
@@ -17471,7 +17471,7 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F277" t="s">
         <v>154</v>
@@ -17486,7 +17486,7 @@
         <v>561</v>
       </c>
       <c r="J277" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K277" t="s">
         <v>257</v>
@@ -17527,7 +17527,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F278" t="s">
         <v>154</v>
@@ -17542,7 +17542,7 @@
         <v>564</v>
       </c>
       <c r="J278" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K278" t="s">
         <v>257</v>
@@ -17583,7 +17583,7 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F279" t="s">
         <v>154</v>
@@ -17598,7 +17598,7 @@
         <v>567</v>
       </c>
       <c r="J279" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K279" t="s">
         <v>257</v>
@@ -17704,10 +17704,10 @@
         <v>41</v>
       </c>
       <c r="H281" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I281" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J281" t="s">
         <v>157</v>
@@ -17728,7 +17728,7 @@
         <v>142</v>
       </c>
       <c r="P281" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="Q281" t="s">
         <v>45</v>
@@ -17816,10 +17816,10 @@
         <v>41</v>
       </c>
       <c r="H283" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I283" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J283" t="s">
         <v>157</v>
@@ -17840,7 +17840,7 @@
         <v>142</v>
       </c>
       <c r="P283" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Q283" t="s">
         <v>45</v>
@@ -18208,16 +18208,16 @@
         <v>41</v>
       </c>
       <c r="H290" t="s">
-        <v>461</v>
+        <v>348</v>
       </c>
       <c r="I290" t="s">
         <v>592</v>
       </c>
       <c r="J290" t="s">
-        <v>44</v>
+        <v>593</v>
       </c>
       <c r="K290" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -18255,7 +18255,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F291" t="s">
         <v>181</v>
@@ -18264,16 +18264,16 @@
         <v>41</v>
       </c>
       <c r="H291" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="I291" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J291" t="s">
-        <v>595</v>
+        <v>44</v>
       </c>
       <c r="K291" t="s">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -18288,7 +18288,7 @@
         <v>142</v>
       </c>
       <c r="P291" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Q291" t="s">
         <v>45</v>
@@ -18550,7 +18550,7 @@
         <v>611</v>
       </c>
       <c r="J296" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K296" t="s">
         <v>238</v>
@@ -18600,7 +18600,7 @@
         <v>41</v>
       </c>
       <c r="H297" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I297" t="s">
         <v>616</v>
@@ -18815,7 +18815,7 @@
         <v>33</v>
       </c>
       <c r="E301" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F301" t="s">
         <v>154</v>
@@ -18830,7 +18830,7 @@
         <v>629</v>
       </c>
       <c r="J301" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K301" t="s">
         <v>257</v>
@@ -18983,7 +18983,7 @@
         <v>33</v>
       </c>
       <c r="E304" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F304" t="s">
         <v>154</v>
@@ -18998,7 +18998,7 @@
         <v>641</v>
       </c>
       <c r="J304" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K304" t="s">
         <v>274</v>
@@ -19110,7 +19110,7 @@
         <v>647</v>
       </c>
       <c r="J306" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K306" t="s">
         <v>238</v>
@@ -19216,19 +19216,19 @@
         <v>41</v>
       </c>
       <c r="H308" t="s">
+        <v>348</v>
+      </c>
+      <c r="I308" t="s">
         <v>653</v>
       </c>
-      <c r="I308" t="s">
+      <c r="J308" t="s">
         <v>654</v>
       </c>
-      <c r="J308" t="s">
-        <v>237</v>
-      </c>
       <c r="K308" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L308" t="s">
-        <v>34</v>
+        <v>655</v>
       </c>
       <c r="M308" t="s">
         <v>651</v>
@@ -19240,7 +19240,7 @@
         <v>142</v>
       </c>
       <c r="P308" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q308" t="s">
         <v>45</v>
@@ -19263,7 +19263,7 @@
         <v>34</v>
       </c>
       <c r="E309" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F309" t="s">
         <v>181</v>
@@ -19272,19 +19272,19 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="I309" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="J309" t="s">
         <v>237</v>
       </c>
       <c r="K309" t="s">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L309" t="s">
-        <v>657</v>
+        <v>34</v>
       </c>
       <c r="M309" t="s">
         <v>651</v>
@@ -19296,7 +19296,7 @@
         <v>142</v>
       </c>
       <c r="P309" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="Q309" t="s">
         <v>45</v>
@@ -19319,7 +19319,7 @@
         <v>34</v>
       </c>
       <c r="E310" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F310" t="s">
         <v>181</v>
@@ -19328,19 +19328,19 @@
         <v>41</v>
       </c>
       <c r="H310" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I310" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J310" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="K310" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="L310" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M310" t="s">
         <v>651</v>
@@ -19352,7 +19352,7 @@
         <v>142</v>
       </c>
       <c r="P310" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Q310" t="s">
         <v>45</v>
@@ -19375,7 +19375,7 @@
         <v>34</v>
       </c>
       <c r="E311" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F311" t="s">
         <v>181</v>
@@ -19384,19 +19384,19 @@
         <v>41</v>
       </c>
       <c r="H311" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I311" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J311" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="K311" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="L311" t="s">
-        <v>34</v>
+        <v>666</v>
       </c>
       <c r="M311" t="s">
         <v>651</v>
@@ -19408,7 +19408,7 @@
         <v>142</v>
       </c>
       <c r="P311" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="Q311" t="s">
         <v>45</v>
@@ -19431,7 +19431,7 @@
         <v>34</v>
       </c>
       <c r="E312" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F312" t="s">
         <v>181</v>
@@ -19440,19 +19440,19 @@
         <v>41</v>
       </c>
       <c r="H312" t="s">
-        <v>348</v>
+        <v>660</v>
       </c>
       <c r="I312" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J312" t="s">
-        <v>667</v>
+        <v>237</v>
       </c>
       <c r="K312" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L312" t="s">
-        <v>668</v>
+        <v>34</v>
       </c>
       <c r="M312" t="s">
         <v>651</v>
@@ -19464,7 +19464,7 @@
         <v>142</v>
       </c>
       <c r="P312" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="Q312" t="s">
         <v>45</v>
@@ -19543,7 +19543,7 @@
         <v>33</v>
       </c>
       <c r="E314" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F314" t="s">
         <v>154</v>
@@ -19558,7 +19558,7 @@
         <v>674</v>
       </c>
       <c r="J314" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K314" t="s">
         <v>257</v>
@@ -19711,28 +19711,28 @@
         <v>33</v>
       </c>
       <c r="E317" t="s">
+        <v>495</v>
+      </c>
+      <c r="F317" t="s">
+        <v>154</v>
+      </c>
+      <c r="G317" t="s">
+        <v>41</v>
+      </c>
+      <c r="H317" t="s">
         <v>683</v>
       </c>
-      <c r="F317" t="s">
-        <v>181</v>
-      </c>
-      <c r="G317" t="s">
-        <v>41</v>
-      </c>
-      <c r="H317" t="s">
+      <c r="I317" t="s">
         <v>684</v>
       </c>
-      <c r="I317" t="s">
+      <c r="J317" t="s">
+        <v>502</v>
+      </c>
+      <c r="K317" t="s">
+        <v>44</v>
+      </c>
+      <c r="L317" t="s">
         <v>685</v>
-      </c>
-      <c r="J317" t="s">
-        <v>237</v>
-      </c>
-      <c r="K317" t="s">
-        <v>72</v>
-      </c>
-      <c r="L317" t="s">
-        <v>34</v>
       </c>
       <c r="M317" t="s">
         <v>682</v>
@@ -19744,7 +19744,7 @@
         <v>142</v>
       </c>
       <c r="P317" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q317" t="s">
         <v>45</v>
@@ -19767,7 +19767,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>500</v>
+        <v>686</v>
       </c>
       <c r="F318" t="s">
         <v>154</v>
@@ -19776,19 +19776,19 @@
         <v>41</v>
       </c>
       <c r="H318" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I318" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="J318" t="s">
-        <v>503</v>
+        <v>688</v>
       </c>
       <c r="K318" t="s">
-        <v>44</v>
+        <v>257</v>
       </c>
       <c r="L318" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M318" t="s">
         <v>682</v>
@@ -19800,7 +19800,7 @@
         <v>142</v>
       </c>
       <c r="P318" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Q318" t="s">
         <v>45</v>
@@ -19823,7 +19823,7 @@
         <v>34</v>
       </c>
       <c r="E319" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F319" t="s">
         <v>154</v>
@@ -19832,19 +19832,19 @@
         <v>41</v>
       </c>
       <c r="H319" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I319" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J319" t="s">
-        <v>690</v>
+        <v>55</v>
       </c>
       <c r="K319" t="s">
         <v>257</v>
       </c>
       <c r="L319" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M319" t="s">
         <v>682</v>
@@ -19856,7 +19856,7 @@
         <v>142</v>
       </c>
       <c r="P319" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="Q319" t="s">
         <v>45</v>
@@ -19879,7 +19879,7 @@
         <v>34</v>
       </c>
       <c r="E320" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F320" t="s">
         <v>154</v>
@@ -19888,19 +19888,19 @@
         <v>41</v>
       </c>
       <c r="H320" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I320" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J320" t="s">
-        <v>55</v>
+        <v>688</v>
       </c>
       <c r="K320" t="s">
         <v>257</v>
       </c>
       <c r="L320" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M320" t="s">
         <v>682</v>
@@ -19912,7 +19912,7 @@
         <v>142</v>
       </c>
       <c r="P320" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Q320" t="s">
         <v>45</v>
@@ -19935,28 +19935,28 @@
         <v>34</v>
       </c>
       <c r="E321" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F321" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="G321" t="s">
         <v>41</v>
       </c>
       <c r="H321" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I321" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J321" t="s">
-        <v>690</v>
+        <v>237</v>
       </c>
       <c r="K321" t="s">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="L321" t="s">
-        <v>697</v>
+        <v>34</v>
       </c>
       <c r="M321" t="s">
         <v>682</v>
@@ -19968,7 +19968,7 @@
         <v>142</v>
       </c>
       <c r="P321" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Q321" t="s">
         <v>45</v>
@@ -20000,7 +20000,7 @@
         <v>41</v>
       </c>
       <c r="H322" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I322" t="s">
         <v>699</v>
@@ -20047,7 +20047,7 @@
         <v>34</v>
       </c>
       <c r="E323" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F323" t="s">
         <v>154</v>
@@ -20056,19 +20056,19 @@
         <v>41</v>
       </c>
       <c r="H323" t="s">
+        <v>702</v>
+      </c>
+      <c r="I323" t="s">
         <v>703</v>
       </c>
-      <c r="I323" t="s">
-        <v>704</v>
-      </c>
       <c r="J323" t="s">
-        <v>705</v>
+        <v>502</v>
       </c>
       <c r="K323" t="s">
         <v>257</v>
       </c>
       <c r="L323" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M323" t="s">
         <v>682</v>
@@ -20080,7 +20080,7 @@
         <v>142</v>
       </c>
       <c r="P323" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="Q323" t="s">
         <v>45</v>
@@ -20103,7 +20103,7 @@
         <v>34</v>
       </c>
       <c r="E324" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F324" t="s">
         <v>154</v>
@@ -20112,19 +20112,19 @@
         <v>41</v>
       </c>
       <c r="H324" t="s">
+        <v>706</v>
+      </c>
+      <c r="I324" t="s">
         <v>707</v>
       </c>
-      <c r="I324" t="s">
+      <c r="J324" t="s">
         <v>708</v>
-      </c>
-      <c r="J324" t="s">
-        <v>709</v>
       </c>
       <c r="K324" t="s">
         <v>50</v>
       </c>
       <c r="L324" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M324" t="s">
         <v>682</v>
@@ -20136,7 +20136,7 @@
         <v>142</v>
       </c>
       <c r="P324" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="Q324" t="s">
         <v>45</v>
@@ -20159,7 +20159,7 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="F325" t="s">
         <v>154</v>
@@ -20174,13 +20174,13 @@
         <v>712</v>
       </c>
       <c r="J325" t="s">
-        <v>503</v>
+        <v>713</v>
       </c>
       <c r="K325" t="s">
         <v>257</v>
       </c>
       <c r="L325" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M325" t="s">
         <v>682</v>
@@ -20271,7 +20271,7 @@
         <v>33</v>
       </c>
       <c r="E327" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F327" t="s">
         <v>154</v>
@@ -20286,7 +20286,7 @@
         <v>718</v>
       </c>
       <c r="J327" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K327" t="s">
         <v>257</v>
@@ -20510,10 +20510,10 @@
         <v>737</v>
       </c>
       <c r="J331" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="K331" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="L331" t="s">
         <v>738</v>
@@ -20551,7 +20551,7 @@
         <v>34</v>
       </c>
       <c r="E332" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F332" t="s">
         <v>154</v>
@@ -20566,7 +20566,7 @@
         <v>740</v>
       </c>
       <c r="J332" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="K332" t="s">
         <v>257</v>
@@ -21055,10 +21055,10 @@
         <v>33</v>
       </c>
       <c r="E341" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="F341" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G341" t="s">
         <v>41</v>
@@ -21070,10 +21070,10 @@
         <v>760</v>
       </c>
       <c r="J341" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="K341" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="L341" t="s">
         <v>761</v>
@@ -21085,13 +21085,13 @@
         <v>45</v>
       </c>
       <c r="O341" t="s">
-        <v>34</v>
+        <v>363</v>
       </c>
       <c r="P341" t="s">
-        <v>34</v>
+        <v>760</v>
       </c>
       <c r="Q341" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R341" t="s">
         <v>34</v>
@@ -21111,25 +21111,25 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>350</v>
+        <v>213</v>
       </c>
       <c r="F342" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G342" t="s">
         <v>41</v>
       </c>
       <c r="H342" t="s">
+        <v>759</v>
+      </c>
+      <c r="I342" t="s">
         <v>762</v>
       </c>
-      <c r="I342" t="s">
-        <v>763</v>
-      </c>
       <c r="J342" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="K342" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="L342" t="s">
         <v>761</v>
@@ -21141,13 +21141,13 @@
         <v>45</v>
       </c>
       <c r="O342" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="P342" t="s">
-        <v>34</v>
+        <v>762</v>
       </c>
       <c r="Q342" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R342" t="s">
         <v>34</v>
@@ -21167,25 +21167,25 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F343" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G343" t="s">
         <v>41</v>
       </c>
       <c r="H343" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I343" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="J343" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="K343" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="L343" t="s">
         <v>761</v>
@@ -21197,13 +21197,13 @@
         <v>45</v>
       </c>
       <c r="O343" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="P343" t="s">
-        <v>34</v>
+        <v>763</v>
       </c>
       <c r="Q343" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R343" t="s">
         <v>34</v>
@@ -21223,25 +21223,25 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="F344" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G344" t="s">
         <v>41</v>
       </c>
       <c r="H344" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I344" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J344" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="K344" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="L344" t="s">
         <v>761</v>
@@ -21253,13 +21253,13 @@
         <v>45</v>
       </c>
       <c r="O344" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="P344" t="s">
-        <v>34</v>
+        <v>764</v>
       </c>
       <c r="Q344" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R344" t="s">
         <v>34</v>
@@ -21279,19 +21279,19 @@
         <v>34</v>
       </c>
       <c r="E345" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F345" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G345" t="s">
         <v>41</v>
       </c>
       <c r="H345" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I345" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J345" t="s">
         <v>84</v>
@@ -21309,13 +21309,13 @@
         <v>45</v>
       </c>
       <c r="O345" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="P345" t="s">
-        <v>34</v>
+        <v>765</v>
       </c>
       <c r="Q345" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R345" t="s">
         <v>34</v>
@@ -21335,10 +21335,10 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F346" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G346" t="s">
         <v>41</v>
@@ -21347,13 +21347,13 @@
         <v>759</v>
       </c>
       <c r="I346" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="J346" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="K346" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="L346" t="s">
         <v>761</v>
@@ -21365,13 +21365,13 @@
         <v>45</v>
       </c>
       <c r="O346" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="P346" t="s">
-        <v>34</v>
+        <v>766</v>
       </c>
       <c r="Q346" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R346" t="s">
         <v>34</v>
@@ -21391,25 +21391,25 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F347" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G347" t="s">
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I347" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J347" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K347" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L347" t="s">
         <v>761</v>
@@ -21421,13 +21421,13 @@
         <v>45</v>
       </c>
       <c r="O347" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="P347" t="s">
-        <v>34</v>
+        <v>767</v>
       </c>
       <c r="Q347" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R347" t="s">
         <v>34</v>
@@ -21447,25 +21447,25 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="F348" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G348" t="s">
         <v>41</v>
       </c>
       <c r="H348" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I348" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="J348" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K348" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L348" t="s">
         <v>761</v>
@@ -21477,13 +21477,13 @@
         <v>45</v>
       </c>
       <c r="O348" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="P348" t="s">
-        <v>34</v>
+        <v>768</v>
       </c>
       <c r="Q348" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R348" t="s">
         <v>34</v>
@@ -21503,25 +21503,25 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F349" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G349" t="s">
         <v>41</v>
       </c>
       <c r="H349" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I349" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="J349" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K349" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L349" t="s">
         <v>761</v>
@@ -21533,13 +21533,13 @@
         <v>45</v>
       </c>
       <c r="O349" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="P349" t="s">
-        <v>34</v>
+        <v>769</v>
       </c>
       <c r="Q349" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R349" t="s">
         <v>34</v>
@@ -21559,25 +21559,25 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F350" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G350" t="s">
         <v>41</v>
       </c>
       <c r="H350" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I350" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="J350" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K350" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L350" t="s">
         <v>761</v>
@@ -21589,13 +21589,13 @@
         <v>45</v>
       </c>
       <c r="O350" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="P350" t="s">
-        <v>34</v>
+        <v>770</v>
       </c>
       <c r="Q350" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R350" t="s">
         <v>34</v>
@@ -21615,25 +21615,25 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>219</v>
+        <v>350</v>
       </c>
       <c r="F351" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G351" t="s">
         <v>41</v>
       </c>
       <c r="H351" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I351" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="J351" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="K351" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="L351" t="s">
         <v>761</v>
@@ -21645,13 +21645,13 @@
         <v>45</v>
       </c>
       <c r="O351" t="s">
-        <v>34</v>
+        <v>402</v>
       </c>
       <c r="P351" t="s">
-        <v>34</v>
+        <v>771</v>
       </c>
       <c r="Q351" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R351" t="s">
         <v>34</v>
@@ -21671,7 +21671,7 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F352" t="s">
         <v>284</v>
@@ -21680,16 +21680,16 @@
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="I352" t="s">
         <v>773</v>
       </c>
       <c r="J352" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K352" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="L352" t="s">
         <v>761</v>
@@ -21727,7 +21727,7 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="F353" t="s">
         <v>284</v>
@@ -21736,16 +21736,16 @@
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="I353" t="s">
         <v>774</v>
       </c>
       <c r="J353" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="K353" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="L353" t="s">
         <v>761</v>
@@ -26169,7 +26169,7 @@
         <v>881</v>
       </c>
       <c r="K432" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="L432" t="s">
         <v>878</v>

--- a/xlsx/dre/DRE_09_2026.xlsx
+++ b/xlsx/dre/DRE_09_2026.xlsx
@@ -456,7 +456,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 376.177,70</t>
+    <t>R$ 374.372,86</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -537,7 +537,7 @@
     <t>4.02 CUSTOS</t>
   </si>
   <si>
-    <t>R$ 161.828,63</t>
+    <t>R$ 161.751,75</t>
   </si>
   <si>
     <t>4.02.01 CUSTO DAS MERCADORIAS VENDIDAS e SERVIÇOS</t>
@@ -858,7 +858,7 @@
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>R$ 21.920,23</t>
+    <t>R$ 21.843,35</t>
   </si>
   <si>
     <t>4.02.02.01 Fretes sobre compras</t>
@@ -918,13 +918,13 @@
     <t>100301/2</t>
   </si>
   <si>
-    <t>R$  700,72</t>
+    <t>R$  738,01</t>
   </si>
   <si>
     <t>100301/3</t>
   </si>
   <si>
-    <t>R$  714,08</t>
+    <t>R$  751,98</t>
   </si>
   <si>
     <t>101801/2</t>
@@ -966,13 +966,13 @@
     <t>101101/2</t>
   </si>
   <si>
-    <t>R$  1.718,89</t>
+    <t>R$  1.643,57</t>
   </si>
   <si>
     <t>101101/3</t>
   </si>
   <si>
-    <t>R$  1.751,00</t>
+    <t>R$  1.674,25</t>
   </si>
   <si>
     <t>101201/2</t>
@@ -2286,7 +2286,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 21.764,62</t>
+    <t>R$ 20.036,66</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -2319,6 +2319,15 @@
     <t>R$  842,10</t>
   </si>
   <si>
+    <t>PAGSEGURO</t>
+  </si>
+  <si>
+    <t>R$  2.752,50</t>
+  </si>
+  <si>
+    <t>R$  546,82</t>
+  </si>
+  <si>
     <t>R$  694,52</t>
   </si>
   <si>
@@ -2337,15 +2346,6 @@
     <t>R$  103,38</t>
   </si>
   <si>
-    <t>PAGSEGURO</t>
-  </si>
-  <si>
-    <t>R$  4.153,06</t>
-  </si>
-  <si>
-    <t>R$  874,22</t>
-  </si>
-  <si>
     <t>7.01 RECEITAS</t>
   </si>
   <si>
@@ -2385,7 +2385,7 @@
     <t>7.05 = RESULTADO BRUTO</t>
   </si>
   <si>
-    <t>R$ 200.542,24</t>
+    <t>R$ 200.619,12</t>
   </si>
   <si>
     <t>7.06 (-) DESPESAS REGULARES</t>
@@ -2478,13 +2478,13 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 22.541,84</t>
+    <t>R$ 22.618,72</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 21.771,44</t>
+    <t>R$ 20.043,48</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -2502,7 +2502,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ 770,40</t>
+    <t>R$ 2.575,24</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -2517,7 +2517,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 288.741,51</t>
+    <t>R$ 286.936,67</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -2550,7 +2550,7 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 355.183,48</t>
+    <t>R$ 356.911,44</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
@@ -2580,7 +2580,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 373.655,82</t>
+    <t>R$ 366.163,56</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -2595,7 +2595,7 @@
     <t>7.80.02 Mark Up à Vista</t>
   </si>
   <si>
-    <t>2,54</t>
+    <t>2,55</t>
   </si>
   <si>
     <t>7.80.03 Mark Up Líquido</t>
@@ -12944,7 +12944,7 @@
         <v>41</v>
       </c>
       <c r="H196" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I196" t="s">
         <v>427</v>
@@ -21335,7 +21335,7 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F346" t="s">
         <v>186</v>
@@ -21344,16 +21344,16 @@
         <v>41</v>
       </c>
       <c r="H346" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="I346" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J346" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="K346" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="L346" t="s">
         <v>761</v>
@@ -21365,10 +21365,10 @@
         <v>45</v>
       </c>
       <c r="O346" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="P346" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="Q346" t="s">
         <v>45</v>
@@ -21391,7 +21391,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="F347" t="s">
         <v>186</v>
@@ -21400,16 +21400,16 @@
         <v>41</v>
       </c>
       <c r="H347" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="I347" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J347" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="K347" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="L347" t="s">
         <v>761</v>
@@ -21421,10 +21421,10 @@
         <v>45</v>
       </c>
       <c r="O347" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="P347" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q347" t="s">
         <v>45</v>
@@ -21447,7 +21447,7 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F348" t="s">
         <v>186</v>
@@ -21459,13 +21459,13 @@
         <v>759</v>
       </c>
       <c r="I348" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J348" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K348" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L348" t="s">
         <v>761</v>
@@ -21477,10 +21477,10 @@
         <v>45</v>
       </c>
       <c r="O348" t="s">
-        <v>76</v>
+        <v>184</v>
       </c>
       <c r="P348" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Q348" t="s">
         <v>45</v>
@@ -21503,7 +21503,7 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F349" t="s">
         <v>186</v>
@@ -21515,13 +21515,13 @@
         <v>759</v>
       </c>
       <c r="I349" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J349" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K349" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L349" t="s">
         <v>761</v>
@@ -21533,10 +21533,10 @@
         <v>45</v>
       </c>
       <c r="O349" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="P349" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q349" t="s">
         <v>45</v>
@@ -21559,7 +21559,7 @@
         <v>34</v>
       </c>
       <c r="E350" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="F350" t="s">
         <v>186</v>
@@ -21571,13 +21571,13 @@
         <v>759</v>
       </c>
       <c r="I350" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J350" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="K350" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="L350" t="s">
         <v>761</v>
@@ -21589,10 +21589,10 @@
         <v>45</v>
       </c>
       <c r="O350" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="P350" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="Q350" t="s">
         <v>45</v>
@@ -21615,7 +21615,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>350</v>
+        <v>211</v>
       </c>
       <c r="F351" t="s">
         <v>186</v>
@@ -21627,13 +21627,13 @@
         <v>759</v>
       </c>
       <c r="I351" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J351" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="K351" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="L351" t="s">
         <v>761</v>
@@ -21645,10 +21645,10 @@
         <v>45</v>
       </c>
       <c r="O351" t="s">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="P351" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Q351" t="s">
         <v>45</v>
@@ -21671,16 +21671,16 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F352" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G352" t="s">
         <v>41</v>
       </c>
       <c r="H352" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="I352" t="s">
         <v>773</v>
@@ -21701,13 +21701,13 @@
         <v>45</v>
       </c>
       <c r="O352" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="P352" t="s">
-        <v>34</v>
+        <v>773</v>
       </c>
       <c r="Q352" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R352" t="s">
         <v>34</v>
@@ -21727,25 +21727,25 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="F353" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="G353" t="s">
         <v>41</v>
       </c>
       <c r="H353" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="I353" t="s">
         <v>774</v>
       </c>
       <c r="J353" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K353" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L353" t="s">
         <v>761</v>
@@ -21757,13 +21757,13 @@
         <v>45</v>
       </c>
       <c r="O353" t="s">
-        <v>34</v>
+        <v>402</v>
       </c>
       <c r="P353" t="s">
-        <v>34</v>
+        <v>774</v>
       </c>
       <c r="Q353" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="R353" t="s">
         <v>34</v>
